--- a/data/input/OthoDataset.xlsx
+++ b/data/input/OthoDataset.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nw\Otho\data\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/i833032/DevResearch/Otho/data/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB827551-3DF9-4E1B-A0E6-B9958D4A833E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADFBA894-E6C9-594E-B62D-3194C12A29F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-43404" yWindow="-888" windowWidth="26112" windowHeight="15348" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CQs" sheetId="1" r:id="rId1"/>
@@ -375,24 +375,28 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -478,10 +482,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -752,21 +756,21 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:R1042"/>
-  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="50.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="50.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="94.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.140625" customWidth="1"/>
-    <col min="5" max="5" width="6.7109375" customWidth="1"/>
-    <col min="7" max="7" width="17.7109375" customWidth="1"/>
-    <col min="8" max="8" width="11.28515625" customWidth="1"/>
-    <col min="10" max="10" width="17.28515625" customWidth="1"/>
-    <col min="11" max="11" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="94.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.1640625" customWidth="1"/>
+    <col min="5" max="5" width="6.6640625" customWidth="1"/>
+    <col min="7" max="7" width="17.6640625" customWidth="1"/>
+    <col min="8" max="8" width="11.33203125" customWidth="1"/>
+    <col min="10" max="10" width="17.33203125" customWidth="1"/>
+    <col min="11" max="11" width="16.83203125" customWidth="1"/>
     <col min="13" max="13" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -794,7 +798,7 @@
       <c r="Q1" s="2"/>
       <c r="R1" s="2"/>
     </row>
-    <row r="2" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
@@ -816,7 +820,7 @@
       <c r="Q2" s="4"/>
       <c r="R2" s="4"/>
     </row>
-    <row r="3" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A3" s="5" t="s">
         <v>7</v>
       </c>
@@ -841,7 +845,7 @@
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
     </row>
-    <row r="4" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A4" s="6" t="s">
         <v>7</v>
       </c>
@@ -866,7 +870,7 @@
       <c r="Q4" s="4"/>
       <c r="R4" s="4"/>
     </row>
-    <row r="5" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A5" s="5" t="s">
         <v>7</v>
       </c>
@@ -894,7 +898,7 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
     </row>
-    <row r="6" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A6" s="6" t="s">
         <v>7</v>
       </c>
@@ -921,7 +925,7 @@
       <c r="Q6" s="4"/>
       <c r="R6" s="4"/>
     </row>
-    <row r="7" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
@@ -949,7 +953,7 @@
       <c r="Q7" s="3"/>
       <c r="R7" s="3"/>
     </row>
-    <row r="8" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A8" s="6" t="s">
         <v>7</v>
       </c>
@@ -977,7 +981,7 @@
       <c r="Q8" s="4"/>
       <c r="R8" s="4"/>
     </row>
-    <row r="9" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A9" s="5" t="s">
         <v>7</v>
       </c>
@@ -1004,7 +1008,7 @@
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
     </row>
-    <row r="10" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A10" s="6" t="s">
         <v>7</v>
       </c>
@@ -1028,7 +1032,7 @@
       <c r="Q10" s="4"/>
       <c r="R10" s="4"/>
     </row>
-    <row r="11" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A11" s="5" t="s">
         <v>7</v>
       </c>
@@ -1052,7 +1056,7 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
     </row>
-    <row r="12" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A12" s="6" t="s">
         <v>7</v>
       </c>
@@ -1075,7 +1079,7 @@
       <c r="Q12" s="4"/>
       <c r="R12" s="4"/>
     </row>
-    <row r="13" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A13" s="5" t="s">
         <v>7</v>
       </c>
@@ -1101,7 +1105,7 @@
       <c r="Q13" s="3"/>
       <c r="R13" s="3"/>
     </row>
-    <row r="14" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A14" s="6" t="s">
         <v>7</v>
       </c>
@@ -1121,15 +1125,15 @@
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
       <c r="K14" s="4"/>
-      <c r="L14" s="18"/>
-      <c r="M14" s="18"/>
+      <c r="L14" s="19"/>
+      <c r="M14" s="19"/>
       <c r="N14" s="4"/>
       <c r="O14" s="4"/>
       <c r="P14" s="4"/>
       <c r="Q14" s="4"/>
       <c r="R14" s="4"/>
     </row>
-    <row r="15" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A15" s="5" t="s">
         <v>7</v>
       </c>
@@ -1156,7 +1160,7 @@
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
     </row>
-    <row r="16" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A16" s="6" t="s">
         <v>7</v>
       </c>
@@ -1180,7 +1184,7 @@
       <c r="Q16" s="4"/>
       <c r="R16" s="4"/>
     </row>
-    <row r="17" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A17" s="5" t="s">
         <v>39</v>
       </c>
@@ -1203,7 +1207,7 @@
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
     </row>
-    <row r="18" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A18" s="6" t="s">
         <v>39</v>
       </c>
@@ -1230,7 +1234,7 @@
       <c r="Q18" s="4"/>
       <c r="R18" s="4"/>
     </row>
-    <row r="19" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A19" s="5" t="s">
         <v>39</v>
       </c>
@@ -1255,7 +1259,7 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
     </row>
-    <row r="20" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A20" s="6" t="s">
         <v>39</v>
       </c>
@@ -1281,7 +1285,7 @@
       <c r="Q20" s="4"/>
       <c r="R20" s="4"/>
     </row>
-    <row r="21" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A21" s="5" t="s">
         <v>39</v>
       </c>
@@ -1308,7 +1312,7 @@
       <c r="Q21" s="3"/>
       <c r="R21" s="3"/>
     </row>
-    <row r="22" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A22" s="6" t="s">
         <v>39</v>
       </c>
@@ -1334,7 +1338,7 @@
       <c r="Q22" s="4"/>
       <c r="R22" s="4"/>
     </row>
-    <row r="23" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A23" s="5" t="s">
         <v>39</v>
       </c>
@@ -1361,7 +1365,7 @@
       <c r="Q23" s="3"/>
       <c r="R23" s="3"/>
     </row>
-    <row r="24" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A24" s="6" t="s">
         <v>39</v>
       </c>
@@ -1387,7 +1391,7 @@
       <c r="Q24" s="4"/>
       <c r="R24" s="4"/>
     </row>
-    <row r="25" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A25" s="5" t="s">
         <v>39</v>
       </c>
@@ -1413,7 +1417,7 @@
       <c r="Q25" s="3"/>
       <c r="R25" s="3"/>
     </row>
-    <row r="26" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A26" s="6" t="s">
         <v>39</v>
       </c>
@@ -1440,7 +1444,7 @@
       <c r="Q26" s="4"/>
       <c r="R26" s="4"/>
     </row>
-    <row r="27" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A27" s="5" t="s">
         <v>39</v>
       </c>
@@ -1467,7 +1471,7 @@
       <c r="Q27" s="3"/>
       <c r="R27" s="3"/>
     </row>
-    <row r="28" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A28" s="6" t="s">
         <v>39</v>
       </c>
@@ -1494,7 +1498,7 @@
       <c r="Q28" s="4"/>
       <c r="R28" s="4"/>
     </row>
-    <row r="29" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A29" s="5" t="s">
         <v>39</v>
       </c>
@@ -1522,7 +1526,7 @@
       <c r="Q29" s="3"/>
       <c r="R29" s="3"/>
     </row>
-    <row r="30" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A30" s="6" t="s">
         <v>39</v>
       </c>
@@ -1550,7 +1554,7 @@
       <c r="Q30" s="4"/>
       <c r="R30" s="4"/>
     </row>
-    <row r="31" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A31" s="5" t="s">
         <v>39</v>
       </c>
@@ -1578,7 +1582,7 @@
       <c r="Q31" s="3"/>
       <c r="R31" s="3"/>
     </row>
-    <row r="32" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A32" s="6" t="s">
         <v>70</v>
       </c>
@@ -1597,15 +1601,15 @@
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
       <c r="K32" s="4"/>
-      <c r="L32" s="18"/>
-      <c r="M32" s="18"/>
+      <c r="L32" s="19"/>
+      <c r="M32" s="19"/>
       <c r="N32" s="4"/>
       <c r="O32" s="4"/>
       <c r="P32" s="4"/>
       <c r="Q32" s="4"/>
       <c r="R32" s="4"/>
     </row>
-    <row r="33" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A33" s="5" t="s">
         <v>70</v>
       </c>
@@ -1633,7 +1637,7 @@
       <c r="Q33" s="3"/>
       <c r="R33" s="3"/>
     </row>
-    <row r="34" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A34" s="6" t="s">
         <v>70</v>
       </c>
@@ -1658,7 +1662,7 @@
       <c r="Q34" s="4"/>
       <c r="R34" s="4"/>
     </row>
-    <row r="35" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A35" s="5" t="s">
         <v>70</v>
       </c>
@@ -1683,7 +1687,7 @@
       <c r="Q35" s="3"/>
       <c r="R35" s="3"/>
     </row>
-    <row r="36" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A36" s="6" t="s">
         <v>70</v>
       </c>
@@ -1710,7 +1714,7 @@
       <c r="Q36" s="4"/>
       <c r="R36" s="4"/>
     </row>
-    <row r="37" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A37" s="5" t="s">
         <v>70</v>
       </c>
@@ -1737,7 +1741,7 @@
       <c r="Q37" s="3"/>
       <c r="R37" s="3"/>
     </row>
-    <row r="38" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A38" s="6" t="s">
         <v>70</v>
       </c>
@@ -1763,7 +1767,7 @@
       <c r="Q38" s="4"/>
       <c r="R38" s="4"/>
     </row>
-    <row r="39" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A39" s="5" t="s">
         <v>70</v>
       </c>
@@ -1790,7 +1794,7 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
     </row>
-    <row r="40" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A40" s="6" t="s">
         <v>70</v>
       </c>
@@ -1816,7 +1820,7 @@
       <c r="Q40" s="4"/>
       <c r="R40" s="4"/>
     </row>
-    <row r="41" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A41" s="5" t="s">
         <v>70</v>
       </c>
@@ -1842,7 +1846,7 @@
       <c r="Q41" s="3"/>
       <c r="R41" s="3"/>
     </row>
-    <row r="42" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A42" s="6" t="s">
         <v>70</v>
       </c>
@@ -1868,7 +1872,7 @@
       <c r="Q42" s="4"/>
       <c r="R42" s="4"/>
     </row>
-    <row r="43" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A43" s="5" t="s">
         <v>70</v>
       </c>
@@ -1894,7 +1898,7 @@
       <c r="Q43" s="3"/>
       <c r="R43" s="3"/>
     </row>
-    <row r="44" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A44" s="6" t="s">
         <v>70</v>
       </c>
@@ -1919,7 +1923,7 @@
       <c r="Q44" s="4"/>
       <c r="R44" s="4"/>
     </row>
-    <row r="45" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A45" s="5" t="s">
         <v>70</v>
       </c>
@@ -1946,7 +1950,7 @@
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
     </row>
-    <row r="46" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A46" s="6" t="s">
         <v>70</v>
       </c>
@@ -1972,7 +1976,7 @@
       <c r="Q46" s="4"/>
       <c r="R46" s="4"/>
     </row>
-    <row r="47" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A47" s="5"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -1990,7 +1994,7 @@
       <c r="Q47" s="3"/>
       <c r="R47" s="3"/>
     </row>
-    <row r="48" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A48" s="6"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -2008,7 +2012,7 @@
       <c r="Q48" s="4"/>
       <c r="R48" s="4"/>
     </row>
-    <row r="49" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A49" s="5"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
@@ -2026,7 +2030,7 @@
       <c r="Q49" s="3"/>
       <c r="R49" s="3"/>
     </row>
-    <row r="50" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A50" s="6"/>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
@@ -2044,7 +2048,7 @@
       <c r="Q50" s="4"/>
       <c r="R50" s="4"/>
     </row>
-    <row r="51" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A51" s="5"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -2062,7 +2066,7 @@
       <c r="Q51" s="3"/>
       <c r="R51" s="3"/>
     </row>
-    <row r="52" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A52" s="6"/>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
@@ -2080,7 +2084,7 @@
       <c r="Q52" s="4"/>
       <c r="R52" s="4"/>
     </row>
-    <row r="53" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A53" s="5"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
@@ -2100,7 +2104,7 @@
       <c r="Q53" s="3"/>
       <c r="R53" s="3"/>
     </row>
-    <row r="54" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A54" s="6"/>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
@@ -2120,7 +2124,7 @@
       <c r="Q54" s="4"/>
       <c r="R54" s="4"/>
     </row>
-    <row r="55" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A55" s="5"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -2140,7 +2144,7 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
     </row>
-    <row r="56" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A56" s="6"/>
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
@@ -2160,7 +2164,7 @@
       <c r="Q56" s="4"/>
       <c r="R56" s="4"/>
     </row>
-    <row r="57" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A57" s="5"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
@@ -2180,7 +2184,7 @@
       <c r="Q57" s="3"/>
       <c r="R57" s="3"/>
     </row>
-    <row r="58" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A58" s="6"/>
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
@@ -2200,7 +2204,7 @@
       <c r="Q58" s="4"/>
       <c r="R58" s="4"/>
     </row>
-    <row r="59" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A59" s="5"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
@@ -2220,7 +2224,7 @@
       <c r="Q59" s="3"/>
       <c r="R59" s="3"/>
     </row>
-    <row r="60" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A60" s="6"/>
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
@@ -2240,7 +2244,7 @@
       <c r="Q60" s="4"/>
       <c r="R60" s="4"/>
     </row>
-    <row r="61" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A61" s="5"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
@@ -2260,987 +2264,987 @@
       <c r="Q61" s="3"/>
       <c r="R61" s="3"/>
     </row>
-    <row r="62" spans="1:18" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="63" spans="1:18" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="64" spans="1:18" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="65" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="66" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="67" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="68" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="69" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="70" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="71" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="72" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="73" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="74" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="75" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="76" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="77" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="78" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="79" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="80" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="81" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="82" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="83" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="84" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="85" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="86" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="87" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="88" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="89" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="90" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="91" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="92" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="93" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="94" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="95" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="96" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="97" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="98" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="99" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="100" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="101" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="102" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="103" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="104" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="105" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="106" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="107" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="108" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="109" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="110" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="111" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="112" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="113" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="114" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="115" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="116" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="117" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="118" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="119" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="120" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="121" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="122" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="123" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="124" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="125" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="126" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="127" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="128" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="129" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="130" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="131" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="132" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="133" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="134" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="135" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="136" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="137" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="138" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="139" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="140" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="141" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="142" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="143" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="144" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="145" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="146" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="147" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="148" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="149" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="150" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="151" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="152" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="153" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="154" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="155" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="156" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="157" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="158" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="159" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="160" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="161" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="162" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="163" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="164" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="165" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="166" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="167" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="168" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="169" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="170" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="171" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="172" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="173" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="174" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="175" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="176" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="177" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="178" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="179" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="180" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="181" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="182" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="183" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="184" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="185" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="186" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="187" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="188" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="189" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="190" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="191" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="192" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="193" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="194" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="195" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="196" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="197" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="198" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="199" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="200" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="201" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="202" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="203" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="204" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="205" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="206" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="207" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="208" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="209" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="210" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="211" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="212" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="213" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="214" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="215" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="216" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="217" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="218" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="219" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="220" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="221" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="222" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="223" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="224" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="225" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="227" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="231" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="232" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="233" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="234" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="235" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="236" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="237" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="238" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="239" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="240" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="257" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="258" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="259" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="260" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="261" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="262" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="263" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="264" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="265" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="266" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="267" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="268" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="269" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="270" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="271" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="272" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="273" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="274" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="275" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="276" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="277" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="278" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="279" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="280" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="281" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="282" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="283" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="284" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="285" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="286" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="287" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="288" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="289" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="290" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="291" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="292" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="293" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="294" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="295" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="296" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="297" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="298" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="299" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="300" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="301" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="302" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="303" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="304" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="305" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="306" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="307" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="308" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="309" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="310" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="311" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="312" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="313" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="314" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="315" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="316" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="317" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="318" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="319" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="320" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="321" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="322" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="323" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="324" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="325" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="326" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="327" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="328" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="329" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="330" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="331" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="332" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="333" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="334" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="335" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="336" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="337" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="338" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="339" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="340" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="341" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="342" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="343" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="344" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="345" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="346" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="347" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="348" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="349" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="350" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="351" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="352" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="353" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="354" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="355" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="356" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="357" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="358" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="359" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="360" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="361" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="362" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="363" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="364" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="365" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="366" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="367" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="368" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="369" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="370" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="371" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="372" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="373" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="374" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="375" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="376" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="377" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="378" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="379" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="380" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="381" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="382" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="383" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="384" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="385" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="386" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="387" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="388" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="389" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="390" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="391" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="392" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="393" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="394" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="395" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="396" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="397" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="398" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="399" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="400" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="401" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="402" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="403" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="404" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="405" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="406" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="407" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="408" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="409" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="410" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="411" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="412" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="413" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="414" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="415" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="416" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="417" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="418" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="419" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="420" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="421" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="422" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="423" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="424" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="425" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="426" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="427" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="428" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="429" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="430" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="431" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="432" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="433" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="434" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="435" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="436" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="437" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="438" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="439" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="440" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="441" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="442" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="443" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="444" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="445" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="446" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="447" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="448" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="449" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="450" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="451" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="452" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="453" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="454" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="455" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="456" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="457" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="458" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="459" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="460" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="461" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="462" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="463" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="464" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="465" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="466" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="467" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="468" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="469" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="470" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="471" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="472" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="473" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="474" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="475" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="476" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="477" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="478" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="479" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="480" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="481" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="482" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="483" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="484" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="485" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="486" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="487" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="488" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="489" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="490" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="491" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="492" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="493" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="494" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="495" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="496" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="497" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="498" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="499" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="500" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="501" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="502" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="503" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="504" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="505" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="506" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="507" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="508" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="509" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="510" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="511" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="512" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="513" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="514" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="515" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="516" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="517" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="518" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="519" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="520" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="521" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="522" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="523" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="524" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="525" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="526" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="527" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="528" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="529" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="530" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="531" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="532" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="533" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="534" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="535" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="536" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="537" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="538" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="539" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="540" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="541" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="542" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="543" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="544" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="545" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="546" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="547" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="548" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="549" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="550" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="551" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="552" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="553" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="554" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="555" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="556" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="557" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="558" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="559" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="560" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="561" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="562" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="563" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="564" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="565" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="566" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="567" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="568" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="569" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="570" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="571" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="572" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="573" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="574" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="575" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="576" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="577" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="578" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="579" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="580" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="581" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="582" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="583" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="584" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="585" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="586" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="587" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="588" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="589" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="590" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="591" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="592" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="593" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="594" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="595" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="596" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="597" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="598" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="599" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="600" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="601" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="602" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="603" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="604" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="605" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="606" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="607" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="608" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="609" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="610" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="611" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="612" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="613" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="614" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="615" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="616" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="617" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="618" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="619" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="620" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="621" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="622" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="623" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="624" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="625" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="626" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="627" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="628" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="629" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="630" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="631" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="632" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="633" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="634" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="635" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="636" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="637" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="638" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="639" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="640" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="641" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="642" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="643" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="644" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="645" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="646" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="647" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="648" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="649" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="650" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="651" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="652" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="653" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="654" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="655" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="656" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="657" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="658" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="659" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="660" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="661" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="662" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="663" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="664" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="665" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="666" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="667" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="668" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="669" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="670" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="671" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="672" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="673" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="674" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="675" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="676" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="677" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="678" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="679" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="680" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="681" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="682" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="683" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="684" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="685" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="686" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="687" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="688" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="689" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="690" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="691" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="692" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="693" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="694" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="695" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="696" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="697" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="698" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="699" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="700" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="701" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="702" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="703" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="704" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="705" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="706" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="707" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="708" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="709" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="710" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="711" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="712" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="713" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="714" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="715" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="716" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="717" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="718" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="719" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="720" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="721" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="722" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="723" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="724" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="725" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="726" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="727" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="728" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="729" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="730" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="731" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="732" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="733" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="734" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="735" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="736" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="737" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="738" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="739" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="740" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="741" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="742" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="743" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="744" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="745" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="746" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="747" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="748" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="749" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="750" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="751" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="752" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="753" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="754" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="755" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="756" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="757" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="758" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="759" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="760" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="761" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="762" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="763" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="764" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="765" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="766" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="767" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="768" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="769" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="770" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="771" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="772" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="773" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="774" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="775" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="776" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="777" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="778" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="779" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="780" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="781" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="782" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="783" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="784" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="785" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="786" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="787" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="788" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="789" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="790" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="791" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="792" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="793" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="794" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="795" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="796" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="797" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="798" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="799" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="800" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="801" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="802" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="803" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="804" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="805" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="806" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="807" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="808" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="809" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="810" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="811" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="812" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="813" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="814" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="815" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="816" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="817" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="818" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="819" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="820" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="821" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="822" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="823" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="824" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="825" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="826" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="827" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="828" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="829" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="830" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="831" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="832" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="833" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="834" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="835" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="836" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="837" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="838" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="839" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="840" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="841" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="842" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="843" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="844" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="845" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="846" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="847" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="848" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="849" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="850" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="851" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="852" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="853" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="854" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="855" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="856" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="857" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="858" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="859" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="860" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="861" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="862" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="863" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="864" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="865" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="866" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="867" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="868" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="869" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="870" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="871" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="872" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="873" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="874" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="875" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="876" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="877" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="878" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="879" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="880" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="881" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="882" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="883" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="884" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="885" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="886" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="887" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="888" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="889" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="890" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="891" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="892" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="893" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="894" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="895" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="896" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="897" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="898" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="899" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="900" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="901" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="902" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="903" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="904" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="905" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="906" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="907" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="908" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="909" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="910" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="911" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="912" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="913" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="914" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="915" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="916" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="917" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="918" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="919" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="920" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="921" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="922" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="923" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="924" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="925" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="926" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="927" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="928" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="929" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="930" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="931" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="932" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="933" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="934" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="935" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="936" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="937" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="938" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="939" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="940" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="941" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="942" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="943" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="944" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="945" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="946" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="947" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="948" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="949" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="950" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="951" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="952" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="953" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="954" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="955" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="956" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="957" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="958" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="959" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="960" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="961" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="962" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="963" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="964" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="965" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="966" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="967" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="968" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="969" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="970" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="971" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="972" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="973" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="974" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="975" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="976" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="977" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="978" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="979" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="980" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="981" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="982" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="983" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="984" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="985" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="986" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="987" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="988" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="989" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="990" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="991" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="992" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="993" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="994" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="995" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="996" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="997" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="998" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="999" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="1000" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="1001" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="1002" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="1003" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="1004" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="1005" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="1006" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="1007" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="1008" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="1009" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="1010" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="1011" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="1012" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="1013" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="1014" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="1015" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="1016" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="1017" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="1018" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="1019" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="1020" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="1021" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="1022" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="1023" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="1024" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="1025" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="1026" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="1027" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="1028" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="1029" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="1030" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="1031" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="1032" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="1033" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="1034" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="1035" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="1036" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="1037" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="1038" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="1039" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="1040" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="1041" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="1042" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="62" spans="1:18" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="63" spans="1:18" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="64" spans="1:18" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="65" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="66" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="67" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="68" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="69" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="70" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="71" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="72" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="73" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="74" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="75" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="76" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="77" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="78" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="79" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="80" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="81" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="82" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="83" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="84" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="85" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="86" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="87" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="88" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="89" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="90" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="91" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="92" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="93" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="94" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="95" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="96" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="97" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="98" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="99" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="100" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="101" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="102" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="103" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="104" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="105" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="106" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="107" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="108" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="109" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="110" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="111" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="112" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="113" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="114" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="115" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="116" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="117" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="118" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="119" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="120" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="121" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="122" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="123" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="124" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="125" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="126" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="127" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="128" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="129" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="130" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="131" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="132" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="133" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="134" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="135" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="136" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="137" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="138" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="139" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="140" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="141" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="142" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="143" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="144" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="145" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="146" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="147" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="148" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="149" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="150" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="151" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="152" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="153" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="154" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="155" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="156" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="157" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="158" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="159" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="160" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="161" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="162" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="163" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="164" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="165" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="166" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="167" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="168" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="169" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="170" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="171" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="172" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="173" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="174" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="175" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="176" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="177" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="178" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="179" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="180" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="181" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="182" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="183" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="184" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="185" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="186" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="187" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="188" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="189" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="190" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="191" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="192" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="193" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="194" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="195" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="196" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="197" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="198" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="199" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="200" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="201" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="202" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="203" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="204" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="205" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="206" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="207" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="208" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="209" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="210" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="211" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="212" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="213" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="214" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="215" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="216" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="217" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="218" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="219" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="220" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="221" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="222" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="223" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="224" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="225" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="226" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="227" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="228" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="229" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="230" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="231" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="232" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="233" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="234" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="235" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="236" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="237" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="238" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="239" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="240" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="241" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="242" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="243" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="244" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="245" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="246" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="247" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="248" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="249" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="250" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="251" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="252" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="253" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="254" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="255" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="256" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="257" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="258" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="259" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="260" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="261" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="262" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="263" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="264" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="265" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="266" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="267" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="268" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="269" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="270" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="271" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="272" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="273" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="274" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="275" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="276" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="277" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="278" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="279" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="280" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="281" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="282" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="283" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="284" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="285" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="286" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="287" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="288" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="289" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="290" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="291" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="292" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="293" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="294" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="295" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="296" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="297" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="298" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="299" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="300" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="301" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="302" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="303" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="304" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="305" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="306" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="307" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="308" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="309" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="310" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="311" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="312" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="313" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="314" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="315" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="316" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="317" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="318" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="319" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="320" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="321" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="322" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="323" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="324" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="325" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="326" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="327" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="328" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="329" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="330" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="331" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="332" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="333" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="334" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="335" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="336" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="337" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="338" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="339" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="340" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="341" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="342" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="343" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="344" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="345" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="346" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="347" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="348" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="349" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="350" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="351" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="352" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="353" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="354" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="355" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="356" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="357" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="358" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="359" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="360" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="361" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="362" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="363" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="364" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="365" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="366" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="367" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="368" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="369" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="370" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="371" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="372" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="373" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="374" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="375" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="376" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="377" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="378" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="379" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="380" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="381" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="382" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="383" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="384" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="385" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="386" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="387" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="388" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="389" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="390" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="391" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="392" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="393" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="394" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="395" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="396" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="397" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="398" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="399" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="400" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="401" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="402" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="403" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="404" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="405" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="406" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="407" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="408" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="409" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="410" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="411" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="412" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="413" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="414" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="415" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="416" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="417" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="418" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="419" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="420" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="421" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="422" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="423" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="424" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="425" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="426" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="427" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="428" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="429" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="430" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="431" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="432" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="433" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="434" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="435" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="436" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="437" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="438" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="439" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="440" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="441" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="442" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="443" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="444" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="445" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="446" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="447" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="448" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="449" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="450" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="451" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="452" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="453" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="454" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="455" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="456" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="457" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="458" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="459" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="460" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="461" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="462" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="463" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="464" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="465" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="466" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="467" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="468" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="469" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="470" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="471" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="472" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="473" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="474" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="475" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="476" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="477" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="478" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="479" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="480" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="481" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="482" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="483" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="484" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="485" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="486" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="487" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="488" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="489" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="490" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="491" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="492" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="493" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="494" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="495" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="496" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="497" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="498" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="499" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="500" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="501" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="502" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="503" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="504" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="505" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="506" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="507" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="508" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="509" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="510" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="511" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="512" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="513" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="514" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="515" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="516" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="517" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="518" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="519" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="520" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="521" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="522" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="523" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="524" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="525" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="526" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="527" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="528" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="529" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="530" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="531" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="532" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="533" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="534" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="535" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="536" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="537" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="538" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="539" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="540" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="541" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="542" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="543" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="544" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="545" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="546" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="547" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="548" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="549" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="550" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="551" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="552" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="553" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="554" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="555" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="556" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="557" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="558" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="559" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="560" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="561" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="562" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="563" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="564" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="565" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="566" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="567" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="568" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="569" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="570" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="571" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="572" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="573" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="574" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="575" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="576" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="577" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="578" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="579" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="580" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="581" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="582" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="583" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="584" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="585" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="586" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="587" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="588" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="589" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="590" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="591" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="592" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="593" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="594" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="595" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="596" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="597" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="598" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="599" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="600" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="601" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="602" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="603" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="604" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="605" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="606" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="607" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="608" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="609" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="610" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="611" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="612" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="613" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="614" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="615" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="616" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="617" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="618" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="619" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="620" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="621" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="622" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="623" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="624" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="625" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="626" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="627" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="628" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="629" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="630" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="631" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="632" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="633" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="634" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="635" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="636" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="637" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="638" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="639" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="640" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="641" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="642" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="643" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="644" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="645" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="646" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="647" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="648" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="649" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="650" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="651" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="652" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="653" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="654" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="655" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="656" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="657" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="658" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="659" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="660" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="661" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="662" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="663" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="664" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="665" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="666" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="667" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="668" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="669" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="670" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="671" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="672" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="673" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="674" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="675" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="676" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="677" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="678" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="679" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="680" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="681" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="682" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="683" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="684" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="685" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="686" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="687" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="688" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="689" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="690" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="691" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="692" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="693" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="694" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="695" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="696" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="697" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="698" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="699" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="700" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="701" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="702" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="703" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="704" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="705" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="706" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="707" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="708" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="709" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="710" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="711" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="712" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="713" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="714" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="715" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="716" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="717" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="718" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="719" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="720" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="721" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="722" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="723" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="724" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="725" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="726" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="727" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="728" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="729" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="730" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="731" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="732" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="733" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="734" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="735" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="736" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="737" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="738" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="739" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="740" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="741" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="742" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="743" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="744" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="745" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="746" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="747" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="748" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="749" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="750" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="751" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="752" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="753" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="754" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="755" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="756" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="757" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="758" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="759" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="760" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="761" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="762" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="763" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="764" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="765" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="766" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="767" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="768" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="769" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="770" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="771" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="772" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="773" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="774" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="775" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="776" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="777" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="778" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="779" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="780" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="781" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="782" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="783" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="784" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="785" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="786" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="787" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="788" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="789" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="790" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="791" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="792" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="793" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="794" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="795" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="796" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="797" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="798" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="799" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="800" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="801" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="802" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="803" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="804" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="805" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="806" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="807" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="808" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="809" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="810" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="811" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="812" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="813" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="814" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="815" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="816" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="817" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="818" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="819" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="820" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="821" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="822" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="823" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="824" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="825" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="826" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="827" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="828" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="829" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="830" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="831" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="832" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="833" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="834" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="835" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="836" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="837" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="838" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="839" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="840" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="841" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="842" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="843" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="844" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="845" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="846" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="847" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="848" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="849" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="850" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="851" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="852" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="853" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="854" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="855" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="856" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="857" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="858" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="859" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="860" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="861" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="862" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="863" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="864" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="865" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="866" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="867" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="868" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="869" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="870" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="871" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="872" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="873" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="874" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="875" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="876" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="877" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="878" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="879" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="880" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="881" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="882" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="883" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="884" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="885" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="886" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="887" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="888" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="889" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="890" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="891" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="892" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="893" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="894" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="895" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="896" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="897" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="898" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="899" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="900" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="901" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="902" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="903" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="904" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="905" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="906" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="907" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="908" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="909" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="910" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="911" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="912" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="913" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="914" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="915" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="916" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="917" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="918" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="919" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="920" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="921" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="922" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="923" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="924" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="925" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="926" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="927" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="928" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="929" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="930" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="931" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="932" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="933" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="934" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="935" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="936" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="937" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="938" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="939" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="940" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="941" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="942" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="943" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="944" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="945" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="946" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="947" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="948" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="949" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="950" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="951" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="952" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="953" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="954" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="955" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="956" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="957" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="958" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="959" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="960" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="961" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="962" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="963" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="964" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="965" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="966" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="967" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="968" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="969" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="970" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="971" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="972" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="973" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="974" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="975" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="976" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="977" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="978" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="979" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="980" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="981" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="982" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="983" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="984" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="985" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="986" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="987" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="988" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="989" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="990" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="991" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="992" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="993" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="994" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="995" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="996" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="997" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="998" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="999" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="1000" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="1001" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="1002" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="1003" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="1004" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="1005" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="1006" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="1007" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="1008" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="1009" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="1010" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="1011" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="1012" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="1013" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="1014" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="1015" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="1016" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="1017" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="1018" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="1019" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="1020" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="1021" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="1022" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="1023" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="1024" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="1025" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="1026" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="1027" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="1028" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="1029" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="1030" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="1031" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="1032" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="1033" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="1034" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="1035" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="1036" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="1037" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="1038" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="1039" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="1040" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="1041" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="1042" ht="13" x14ac:dyDescent="0.15"/>
   </sheetData>
   <autoFilter ref="A1:A1042" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="2">
@@ -3257,14 +3261,14 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:R981"/>
-  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="39.140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="39.1640625" style="17" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="255.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
@@ -3287,11 +3291,11 @@
       <c r="Q1" s="14"/>
       <c r="R1" s="14"/>
     </row>
-    <row r="2" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A2" s="16"/>
       <c r="B2" s="15"/>
     </row>
-    <row r="3" spans="1:18" ht="89.25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" ht="98" x14ac:dyDescent="0.15">
       <c r="A3" s="16" t="s">
         <v>7</v>
       </c>
@@ -3299,7 +3303,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="63.75" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" ht="70" x14ac:dyDescent="0.15">
       <c r="A4" s="16" t="s">
         <v>39</v>
       </c>
@@ -3307,7 +3311,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="89.25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" ht="84" x14ac:dyDescent="0.15">
       <c r="A5" s="16" t="s">
         <v>70</v>
       </c>
@@ -3315,2932 +3319,2932 @@
         <v>103</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="15"/>
     </row>
-    <row r="7" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="15"/>
     </row>
-    <row r="8" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="15"/>
     </row>
-    <row r="9" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="15"/>
     </row>
-    <row r="10" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="15"/>
     </row>
-    <row r="11" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="15"/>
     </row>
-    <row r="12" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="15"/>
     </row>
-    <row r="13" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="15"/>
     </row>
-    <row r="14" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="15"/>
     </row>
-    <row r="15" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="15"/>
     </row>
-    <row r="16" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="15"/>
     </row>
-    <row r="17" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="15"/>
     </row>
-    <row r="18" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="15"/>
     </row>
-    <row r="19" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="15"/>
     </row>
-    <row r="20" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="15"/>
     </row>
-    <row r="21" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="15"/>
     </row>
-    <row r="22" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="15"/>
     </row>
-    <row r="23" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="15"/>
     </row>
-    <row r="24" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="15"/>
     </row>
-    <row r="25" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B25" s="15"/>
     </row>
-    <row r="26" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="15"/>
     </row>
-    <row r="27" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="15"/>
     </row>
-    <row r="28" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="15"/>
     </row>
-    <row r="29" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="15"/>
     </row>
-    <row r="30" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="15"/>
     </row>
-    <row r="31" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="15"/>
     </row>
-    <row r="32" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="15"/>
     </row>
-    <row r="33" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="15"/>
     </row>
-    <row r="34" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="15"/>
     </row>
-    <row r="35" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="15"/>
     </row>
-    <row r="36" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B36" s="15"/>
     </row>
-    <row r="37" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B37" s="15"/>
     </row>
-    <row r="38" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="15"/>
     </row>
-    <row r="39" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="15"/>
     </row>
-    <row r="40" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="15"/>
     </row>
-    <row r="41" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B41" s="15"/>
     </row>
-    <row r="42" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="15"/>
     </row>
-    <row r="43" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B43" s="15"/>
     </row>
-    <row r="44" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="15"/>
     </row>
-    <row r="45" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B45" s="15"/>
     </row>
-    <row r="46" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="15"/>
     </row>
-    <row r="47" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B47" s="15"/>
     </row>
-    <row r="48" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B48" s="15"/>
     </row>
-    <row r="49" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="15"/>
     </row>
-    <row r="50" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B50" s="15"/>
     </row>
-    <row r="51" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B51" s="15"/>
     </row>
-    <row r="52" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B52" s="15"/>
     </row>
-    <row r="53" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B53" s="15"/>
     </row>
-    <row r="54" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B54" s="15"/>
     </row>
-    <row r="55" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B55" s="15"/>
     </row>
-    <row r="56" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B56" s="15"/>
     </row>
-    <row r="57" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B57" s="15"/>
     </row>
-    <row r="58" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B58" s="15"/>
     </row>
-    <row r="59" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B59" s="15"/>
     </row>
-    <row r="60" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B60" s="15"/>
     </row>
-    <row r="61" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B61" s="15"/>
     </row>
-    <row r="62" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B62" s="15"/>
     </row>
-    <row r="63" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B63" s="15"/>
     </row>
-    <row r="64" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B64" s="15"/>
     </row>
-    <row r="65" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B65" s="15"/>
     </row>
-    <row r="66" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B66" s="15"/>
     </row>
-    <row r="67" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B67" s="15"/>
     </row>
-    <row r="68" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B68" s="15"/>
     </row>
-    <row r="69" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B69" s="15"/>
     </row>
-    <row r="70" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B70" s="15"/>
     </row>
-    <row r="71" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B71" s="15"/>
     </row>
-    <row r="72" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B72" s="15"/>
     </row>
-    <row r="73" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B73" s="15"/>
     </row>
-    <row r="74" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B74" s="15"/>
     </row>
-    <row r="75" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B75" s="15"/>
     </row>
-    <row r="76" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B76" s="15"/>
     </row>
-    <row r="77" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B77" s="15"/>
     </row>
-    <row r="78" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B78" s="15"/>
     </row>
-    <row r="79" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B79" s="15"/>
     </row>
-    <row r="80" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B80" s="15"/>
     </row>
-    <row r="81" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="81" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B81" s="15"/>
     </row>
-    <row r="82" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="82" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B82" s="15"/>
     </row>
-    <row r="83" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="83" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B83" s="15"/>
     </row>
-    <row r="84" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="84" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B84" s="15"/>
     </row>
-    <row r="85" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="85" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B85" s="15"/>
     </row>
-    <row r="86" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="86" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B86" s="15"/>
     </row>
-    <row r="87" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="87" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B87" s="15"/>
     </row>
-    <row r="88" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="88" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B88" s="15"/>
     </row>
-    <row r="89" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="89" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B89" s="15"/>
     </row>
-    <row r="90" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="90" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B90" s="15"/>
     </row>
-    <row r="91" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="91" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B91" s="15"/>
     </row>
-    <row r="92" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="92" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B92" s="15"/>
     </row>
-    <row r="93" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="93" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B93" s="15"/>
     </row>
-    <row r="94" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="94" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B94" s="15"/>
     </row>
-    <row r="95" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="95" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B95" s="15"/>
     </row>
-    <row r="96" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="96" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B96" s="15"/>
     </row>
-    <row r="97" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="97" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B97" s="15"/>
     </row>
-    <row r="98" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="98" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B98" s="15"/>
     </row>
-    <row r="99" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="99" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B99" s="15"/>
     </row>
-    <row r="100" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="100" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B100" s="15"/>
     </row>
-    <row r="101" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="101" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B101" s="15"/>
     </row>
-    <row r="102" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="102" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B102" s="15"/>
     </row>
-    <row r="103" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="103" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B103" s="15"/>
     </row>
-    <row r="104" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="104" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B104" s="15"/>
     </row>
-    <row r="105" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="105" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B105" s="15"/>
     </row>
-    <row r="106" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="106" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B106" s="15"/>
     </row>
-    <row r="107" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="107" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B107" s="15"/>
     </row>
-    <row r="108" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="108" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B108" s="15"/>
     </row>
-    <row r="109" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="109" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B109" s="15"/>
     </row>
-    <row r="110" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="110" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B110" s="15"/>
     </row>
-    <row r="111" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="111" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B111" s="15"/>
     </row>
-    <row r="112" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="112" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B112" s="15"/>
     </row>
-    <row r="113" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="113" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B113" s="15"/>
     </row>
-    <row r="114" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="114" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B114" s="15"/>
     </row>
-    <row r="115" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="115" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B115" s="15"/>
     </row>
-    <row r="116" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="116" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B116" s="15"/>
     </row>
-    <row r="117" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="117" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B117" s="15"/>
     </row>
-    <row r="118" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="118" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B118" s="15"/>
     </row>
-    <row r="119" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="119" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B119" s="15"/>
     </row>
-    <row r="120" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="120" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B120" s="15"/>
     </row>
-    <row r="121" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="121" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B121" s="15"/>
     </row>
-    <row r="122" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="122" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B122" s="15"/>
     </row>
-    <row r="123" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="123" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B123" s="15"/>
     </row>
-    <row r="124" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="124" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B124" s="15"/>
     </row>
-    <row r="125" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="125" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B125" s="15"/>
     </row>
-    <row r="126" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="126" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B126" s="15"/>
     </row>
-    <row r="127" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="127" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B127" s="15"/>
     </row>
-    <row r="128" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="128" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B128" s="15"/>
     </row>
-    <row r="129" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="129" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B129" s="15"/>
     </row>
-    <row r="130" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="130" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B130" s="15"/>
     </row>
-    <row r="131" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="131" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B131" s="15"/>
     </row>
-    <row r="132" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="132" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B132" s="15"/>
     </row>
-    <row r="133" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="133" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B133" s="15"/>
     </row>
-    <row r="134" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="134" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B134" s="15"/>
     </row>
-    <row r="135" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="135" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B135" s="15"/>
     </row>
-    <row r="136" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="136" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B136" s="15"/>
     </row>
-    <row r="137" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="137" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B137" s="15"/>
     </row>
-    <row r="138" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="138" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B138" s="15"/>
     </row>
-    <row r="139" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="139" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B139" s="15"/>
     </row>
-    <row r="140" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="140" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B140" s="15"/>
     </row>
-    <row r="141" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="141" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B141" s="15"/>
     </row>
-    <row r="142" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="142" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B142" s="15"/>
     </row>
-    <row r="143" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="143" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B143" s="15"/>
     </row>
-    <row r="144" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="144" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B144" s="15"/>
     </row>
-    <row r="145" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="145" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B145" s="15"/>
     </row>
-    <row r="146" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="146" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B146" s="15"/>
     </row>
-    <row r="147" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="147" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B147" s="15"/>
     </row>
-    <row r="148" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="148" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B148" s="15"/>
     </row>
-    <row r="149" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="149" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B149" s="15"/>
     </row>
-    <row r="150" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="150" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B150" s="15"/>
     </row>
-    <row r="151" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="151" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B151" s="15"/>
     </row>
-    <row r="152" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="152" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B152" s="15"/>
     </row>
-    <row r="153" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="153" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B153" s="15"/>
     </row>
-    <row r="154" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="154" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B154" s="15"/>
     </row>
-    <row r="155" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="155" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B155" s="15"/>
     </row>
-    <row r="156" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="156" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B156" s="15"/>
     </row>
-    <row r="157" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="157" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B157" s="15"/>
     </row>
-    <row r="158" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="158" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B158" s="15"/>
     </row>
-    <row r="159" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="159" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B159" s="15"/>
     </row>
-    <row r="160" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="160" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B160" s="15"/>
     </row>
-    <row r="161" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="161" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B161" s="15"/>
     </row>
-    <row r="162" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="162" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B162" s="15"/>
     </row>
-    <row r="163" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="163" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B163" s="15"/>
     </row>
-    <row r="164" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="164" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B164" s="15"/>
     </row>
-    <row r="165" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="165" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B165" s="15"/>
     </row>
-    <row r="166" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="166" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B166" s="15"/>
     </row>
-    <row r="167" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="167" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B167" s="15"/>
     </row>
-    <row r="168" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="168" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B168" s="15"/>
     </row>
-    <row r="169" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="169" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B169" s="15"/>
     </row>
-    <row r="170" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="170" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B170" s="15"/>
     </row>
-    <row r="171" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="171" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B171" s="15"/>
     </row>
-    <row r="172" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="172" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B172" s="15"/>
     </row>
-    <row r="173" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="173" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B173" s="15"/>
     </row>
-    <row r="174" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="174" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B174" s="15"/>
     </row>
-    <row r="175" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="175" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B175" s="15"/>
     </row>
-    <row r="176" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="176" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B176" s="15"/>
     </row>
-    <row r="177" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="177" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B177" s="15"/>
     </row>
-    <row r="178" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="178" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B178" s="15"/>
     </row>
-    <row r="179" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="179" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B179" s="15"/>
     </row>
-    <row r="180" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="180" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B180" s="15"/>
     </row>
-    <row r="181" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="181" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B181" s="15"/>
     </row>
-    <row r="182" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="182" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B182" s="15"/>
     </row>
-    <row r="183" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="183" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B183" s="15"/>
     </row>
-    <row r="184" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="184" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B184" s="15"/>
     </row>
-    <row r="185" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="185" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B185" s="15"/>
     </row>
-    <row r="186" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="186" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B186" s="15"/>
     </row>
-    <row r="187" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="187" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B187" s="15"/>
     </row>
-    <row r="188" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="188" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B188" s="15"/>
     </row>
-    <row r="189" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="189" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B189" s="15"/>
     </row>
-    <row r="190" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="190" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B190" s="15"/>
     </row>
-    <row r="191" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="191" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B191" s="15"/>
     </row>
-    <row r="192" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="192" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B192" s="15"/>
     </row>
-    <row r="193" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="193" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B193" s="15"/>
     </row>
-    <row r="194" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="194" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B194" s="15"/>
     </row>
-    <row r="195" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="195" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B195" s="15"/>
     </row>
-    <row r="196" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="196" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B196" s="15"/>
     </row>
-    <row r="197" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="197" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B197" s="15"/>
     </row>
-    <row r="198" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="198" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B198" s="15"/>
     </row>
-    <row r="199" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="199" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B199" s="15"/>
     </row>
-    <row r="200" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="200" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B200" s="15"/>
     </row>
-    <row r="201" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="201" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B201" s="15"/>
     </row>
-    <row r="202" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="202" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B202" s="15"/>
     </row>
-    <row r="203" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="203" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B203" s="15"/>
     </row>
-    <row r="204" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="204" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B204" s="15"/>
     </row>
-    <row r="205" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="205" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B205" s="15"/>
     </row>
-    <row r="206" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="206" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B206" s="15"/>
     </row>
-    <row r="207" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="207" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B207" s="15"/>
     </row>
-    <row r="208" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="208" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B208" s="15"/>
     </row>
-    <row r="209" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="209" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B209" s="15"/>
     </row>
-    <row r="210" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="210" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B210" s="15"/>
     </row>
-    <row r="211" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="211" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B211" s="15"/>
     </row>
-    <row r="212" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="212" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B212" s="15"/>
     </row>
-    <row r="213" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="213" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B213" s="15"/>
     </row>
-    <row r="214" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="214" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B214" s="15"/>
     </row>
-    <row r="215" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="215" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B215" s="15"/>
     </row>
-    <row r="216" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="216" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B216" s="15"/>
     </row>
-    <row r="217" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="217" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B217" s="15"/>
     </row>
-    <row r="218" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="218" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B218" s="15"/>
     </row>
-    <row r="219" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="219" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B219" s="15"/>
     </row>
-    <row r="220" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="220" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B220" s="15"/>
     </row>
-    <row r="221" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="221" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B221" s="15"/>
     </row>
-    <row r="222" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="222" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B222" s="15"/>
     </row>
-    <row r="223" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="223" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B223" s="15"/>
     </row>
-    <row r="224" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="224" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B224" s="15"/>
     </row>
-    <row r="225" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="225" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B225" s="15"/>
     </row>
-    <row r="226" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="226" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B226" s="15"/>
     </row>
-    <row r="227" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="227" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B227" s="15"/>
     </row>
-    <row r="228" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="228" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B228" s="15"/>
     </row>
-    <row r="229" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="229" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B229" s="15"/>
     </row>
-    <row r="230" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="230" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B230" s="15"/>
     </row>
-    <row r="231" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="231" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B231" s="15"/>
     </row>
-    <row r="232" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="232" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B232" s="15"/>
     </row>
-    <row r="233" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="233" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B233" s="15"/>
     </row>
-    <row r="234" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="234" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B234" s="15"/>
     </row>
-    <row r="235" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="235" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B235" s="15"/>
     </row>
-    <row r="236" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="236" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B236" s="15"/>
     </row>
-    <row r="237" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="237" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B237" s="15"/>
     </row>
-    <row r="238" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="238" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B238" s="15"/>
     </row>
-    <row r="239" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="239" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B239" s="15"/>
     </row>
-    <row r="240" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="240" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B240" s="15"/>
     </row>
-    <row r="241" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="241" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B241" s="15"/>
     </row>
-    <row r="242" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="242" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B242" s="15"/>
     </row>
-    <row r="243" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="243" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B243" s="15"/>
     </row>
-    <row r="244" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="244" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B244" s="15"/>
     </row>
-    <row r="245" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="245" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B245" s="15"/>
     </row>
-    <row r="246" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="246" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B246" s="15"/>
     </row>
-    <row r="247" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="247" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B247" s="15"/>
     </row>
-    <row r="248" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="248" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B248" s="15"/>
     </row>
-    <row r="249" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="249" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B249" s="15"/>
     </row>
-    <row r="250" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="250" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B250" s="15"/>
     </row>
-    <row r="251" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="251" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B251" s="15"/>
     </row>
-    <row r="252" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="252" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B252" s="15"/>
     </row>
-    <row r="253" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="253" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B253" s="15"/>
     </row>
-    <row r="254" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="254" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B254" s="15"/>
     </row>
-    <row r="255" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="255" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B255" s="15"/>
     </row>
-    <row r="256" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="256" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B256" s="15"/>
     </row>
-    <row r="257" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="257" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B257" s="15"/>
     </row>
-    <row r="258" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="258" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B258" s="15"/>
     </row>
-    <row r="259" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="259" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B259" s="15"/>
     </row>
-    <row r="260" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="260" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B260" s="15"/>
     </row>
-    <row r="261" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="261" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B261" s="15"/>
     </row>
-    <row r="262" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="262" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B262" s="15"/>
     </row>
-    <row r="263" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="263" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B263" s="15"/>
     </row>
-    <row r="264" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="264" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B264" s="15"/>
     </row>
-    <row r="265" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="265" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B265" s="15"/>
     </row>
-    <row r="266" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="266" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B266" s="15"/>
     </row>
-    <row r="267" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="267" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B267" s="15"/>
     </row>
-    <row r="268" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="268" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B268" s="15"/>
     </row>
-    <row r="269" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="269" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B269" s="15"/>
     </row>
-    <row r="270" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="270" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B270" s="15"/>
     </row>
-    <row r="271" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="271" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B271" s="15"/>
     </row>
-    <row r="272" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="272" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B272" s="15"/>
     </row>
-    <row r="273" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="273" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B273" s="15"/>
     </row>
-    <row r="274" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="274" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B274" s="15"/>
     </row>
-    <row r="275" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="275" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B275" s="15"/>
     </row>
-    <row r="276" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="276" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B276" s="15"/>
     </row>
-    <row r="277" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="277" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B277" s="15"/>
     </row>
-    <row r="278" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="278" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B278" s="15"/>
     </row>
-    <row r="279" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="279" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B279" s="15"/>
     </row>
-    <row r="280" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="280" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B280" s="15"/>
     </row>
-    <row r="281" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="281" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B281" s="15"/>
     </row>
-    <row r="282" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="282" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B282" s="15"/>
     </row>
-    <row r="283" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="283" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B283" s="15"/>
     </row>
-    <row r="284" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="284" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B284" s="15"/>
     </row>
-    <row r="285" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="285" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B285" s="15"/>
     </row>
-    <row r="286" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="286" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B286" s="15"/>
     </row>
-    <row r="287" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="287" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B287" s="15"/>
     </row>
-    <row r="288" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="288" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B288" s="15"/>
     </row>
-    <row r="289" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="289" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B289" s="15"/>
     </row>
-    <row r="290" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="290" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B290" s="15"/>
     </row>
-    <row r="291" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="291" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B291" s="15"/>
     </row>
-    <row r="292" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="292" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B292" s="15"/>
     </row>
-    <row r="293" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="293" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B293" s="15"/>
     </row>
-    <row r="294" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="294" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B294" s="15"/>
     </row>
-    <row r="295" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="295" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B295" s="15"/>
     </row>
-    <row r="296" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="296" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B296" s="15"/>
     </row>
-    <row r="297" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="297" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B297" s="15"/>
     </row>
-    <row r="298" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="298" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B298" s="15"/>
     </row>
-    <row r="299" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="299" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B299" s="15"/>
     </row>
-    <row r="300" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="300" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B300" s="15"/>
     </row>
-    <row r="301" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="301" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B301" s="15"/>
     </row>
-    <row r="302" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="302" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B302" s="15"/>
     </row>
-    <row r="303" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="303" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B303" s="15"/>
     </row>
-    <row r="304" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="304" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B304" s="15"/>
     </row>
-    <row r="305" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="305" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B305" s="15"/>
     </row>
-    <row r="306" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="306" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B306" s="15"/>
     </row>
-    <row r="307" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="307" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B307" s="15"/>
     </row>
-    <row r="308" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="308" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B308" s="15"/>
     </row>
-    <row r="309" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="309" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B309" s="15"/>
     </row>
-    <row r="310" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="310" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B310" s="15"/>
     </row>
-    <row r="311" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="311" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B311" s="15"/>
     </row>
-    <row r="312" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="312" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B312" s="15"/>
     </row>
-    <row r="313" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="313" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B313" s="15"/>
     </row>
-    <row r="314" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="314" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B314" s="15"/>
     </row>
-    <row r="315" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="315" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B315" s="15"/>
     </row>
-    <row r="316" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="316" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B316" s="15"/>
     </row>
-    <row r="317" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="317" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B317" s="15"/>
     </row>
-    <row r="318" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="318" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B318" s="15"/>
     </row>
-    <row r="319" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="319" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B319" s="15"/>
     </row>
-    <row r="320" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="320" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B320" s="15"/>
     </row>
-    <row r="321" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="321" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B321" s="15"/>
     </row>
-    <row r="322" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="322" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B322" s="15"/>
     </row>
-    <row r="323" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="323" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B323" s="15"/>
     </row>
-    <row r="324" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="324" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B324" s="15"/>
     </row>
-    <row r="325" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="325" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B325" s="15"/>
     </row>
-    <row r="326" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="326" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B326" s="15"/>
     </row>
-    <row r="327" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="327" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B327" s="15"/>
     </row>
-    <row r="328" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="328" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B328" s="15"/>
     </row>
-    <row r="329" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="329" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B329" s="15"/>
     </row>
-    <row r="330" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="330" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B330" s="15"/>
     </row>
-    <row r="331" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="331" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B331" s="15"/>
     </row>
-    <row r="332" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="332" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B332" s="15"/>
     </row>
-    <row r="333" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="333" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B333" s="15"/>
     </row>
-    <row r="334" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="334" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B334" s="15"/>
     </row>
-    <row r="335" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="335" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B335" s="15"/>
     </row>
-    <row r="336" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="336" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B336" s="15"/>
     </row>
-    <row r="337" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="337" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B337" s="15"/>
     </row>
-    <row r="338" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="338" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B338" s="15"/>
     </row>
-    <row r="339" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="339" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B339" s="15"/>
     </row>
-    <row r="340" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="340" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B340" s="15"/>
     </row>
-    <row r="341" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="341" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B341" s="15"/>
     </row>
-    <row r="342" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="342" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B342" s="15"/>
     </row>
-    <row r="343" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="343" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B343" s="15"/>
     </row>
-    <row r="344" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="344" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B344" s="15"/>
     </row>
-    <row r="345" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="345" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B345" s="15"/>
     </row>
-    <row r="346" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="346" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B346" s="15"/>
     </row>
-    <row r="347" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="347" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B347" s="15"/>
     </row>
-    <row r="348" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="348" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B348" s="15"/>
     </row>
-    <row r="349" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="349" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B349" s="15"/>
     </row>
-    <row r="350" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="350" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B350" s="15"/>
     </row>
-    <row r="351" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="351" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B351" s="15"/>
     </row>
-    <row r="352" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="352" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B352" s="15"/>
     </row>
-    <row r="353" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="353" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B353" s="15"/>
     </row>
-    <row r="354" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="354" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B354" s="15"/>
     </row>
-    <row r="355" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="355" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B355" s="15"/>
     </row>
-    <row r="356" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="356" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B356" s="15"/>
     </row>
-    <row r="357" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="357" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B357" s="15"/>
     </row>
-    <row r="358" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="358" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B358" s="15"/>
     </row>
-    <row r="359" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="359" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B359" s="15"/>
     </row>
-    <row r="360" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="360" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B360" s="15"/>
     </row>
-    <row r="361" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="361" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B361" s="15"/>
     </row>
-    <row r="362" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="362" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B362" s="15"/>
     </row>
-    <row r="363" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="363" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B363" s="15"/>
     </row>
-    <row r="364" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="364" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B364" s="15"/>
     </row>
-    <row r="365" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="365" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B365" s="15"/>
     </row>
-    <row r="366" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="366" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B366" s="15"/>
     </row>
-    <row r="367" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="367" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B367" s="15"/>
     </row>
-    <row r="368" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="368" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B368" s="15"/>
     </row>
-    <row r="369" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="369" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B369" s="15"/>
     </row>
-    <row r="370" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="370" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B370" s="15"/>
     </row>
-    <row r="371" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="371" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B371" s="15"/>
     </row>
-    <row r="372" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="372" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B372" s="15"/>
     </row>
-    <row r="373" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="373" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B373" s="15"/>
     </row>
-    <row r="374" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="374" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B374" s="15"/>
     </row>
-    <row r="375" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="375" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B375" s="15"/>
     </row>
-    <row r="376" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="376" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B376" s="15"/>
     </row>
-    <row r="377" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="377" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B377" s="15"/>
     </row>
-    <row r="378" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="378" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B378" s="15"/>
     </row>
-    <row r="379" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="379" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B379" s="15"/>
     </row>
-    <row r="380" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="380" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B380" s="15"/>
     </row>
-    <row r="381" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="381" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B381" s="15"/>
     </row>
-    <row r="382" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="382" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B382" s="15"/>
     </row>
-    <row r="383" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="383" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B383" s="15"/>
     </row>
-    <row r="384" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="384" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B384" s="15"/>
     </row>
-    <row r="385" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="385" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B385" s="15"/>
     </row>
-    <row r="386" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="386" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B386" s="15"/>
     </row>
-    <row r="387" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="387" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B387" s="15"/>
     </row>
-    <row r="388" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="388" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B388" s="15"/>
     </row>
-    <row r="389" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="389" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B389" s="15"/>
     </row>
-    <row r="390" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="390" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B390" s="15"/>
     </row>
-    <row r="391" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="391" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B391" s="15"/>
     </row>
-    <row r="392" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="392" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B392" s="15"/>
     </row>
-    <row r="393" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="393" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B393" s="15"/>
     </row>
-    <row r="394" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="394" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B394" s="15"/>
     </row>
-    <row r="395" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="395" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B395" s="15"/>
     </row>
-    <row r="396" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="396" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B396" s="15"/>
     </row>
-    <row r="397" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="397" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B397" s="15"/>
     </row>
-    <row r="398" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="398" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B398" s="15"/>
     </row>
-    <row r="399" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="399" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B399" s="15"/>
     </row>
-    <row r="400" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="400" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B400" s="15"/>
     </row>
-    <row r="401" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="401" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B401" s="15"/>
     </row>
-    <row r="402" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="402" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B402" s="15"/>
     </row>
-    <row r="403" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="403" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B403" s="15"/>
     </row>
-    <row r="404" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="404" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B404" s="15"/>
     </row>
-    <row r="405" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="405" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B405" s="15"/>
     </row>
-    <row r="406" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="406" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B406" s="15"/>
     </row>
-    <row r="407" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="407" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B407" s="15"/>
     </row>
-    <row r="408" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="408" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B408" s="15"/>
     </row>
-    <row r="409" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="409" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B409" s="15"/>
     </row>
-    <row r="410" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="410" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B410" s="15"/>
     </row>
-    <row r="411" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="411" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B411" s="15"/>
     </row>
-    <row r="412" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="412" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B412" s="15"/>
     </row>
-    <row r="413" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="413" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B413" s="15"/>
     </row>
-    <row r="414" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="414" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B414" s="15"/>
     </row>
-    <row r="415" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="415" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B415" s="15"/>
     </row>
-    <row r="416" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="416" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B416" s="15"/>
     </row>
-    <row r="417" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="417" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B417" s="15"/>
     </row>
-    <row r="418" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="418" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B418" s="15"/>
     </row>
-    <row r="419" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="419" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B419" s="15"/>
     </row>
-    <row r="420" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="420" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B420" s="15"/>
     </row>
-    <row r="421" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="421" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B421" s="15"/>
     </row>
-    <row r="422" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="422" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B422" s="15"/>
     </row>
-    <row r="423" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="423" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B423" s="15"/>
     </row>
-    <row r="424" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="424" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B424" s="15"/>
     </row>
-    <row r="425" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="425" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B425" s="15"/>
     </row>
-    <row r="426" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="426" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B426" s="15"/>
     </row>
-    <row r="427" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="427" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B427" s="15"/>
     </row>
-    <row r="428" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="428" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B428" s="15"/>
     </row>
-    <row r="429" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="429" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B429" s="15"/>
     </row>
-    <row r="430" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="430" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B430" s="15"/>
     </row>
-    <row r="431" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="431" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B431" s="15"/>
     </row>
-    <row r="432" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="432" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B432" s="15"/>
     </row>
-    <row r="433" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="433" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B433" s="15"/>
     </row>
-    <row r="434" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="434" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B434" s="15"/>
     </row>
-    <row r="435" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="435" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B435" s="15"/>
     </row>
-    <row r="436" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="436" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B436" s="15"/>
     </row>
-    <row r="437" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="437" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B437" s="15"/>
     </row>
-    <row r="438" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="438" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B438" s="15"/>
     </row>
-    <row r="439" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="439" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B439" s="15"/>
     </row>
-    <row r="440" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="440" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B440" s="15"/>
     </row>
-    <row r="441" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="441" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B441" s="15"/>
     </row>
-    <row r="442" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="442" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B442" s="15"/>
     </row>
-    <row r="443" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="443" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B443" s="15"/>
     </row>
-    <row r="444" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="444" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B444" s="15"/>
     </row>
-    <row r="445" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="445" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B445" s="15"/>
     </row>
-    <row r="446" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="446" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B446" s="15"/>
     </row>
-    <row r="447" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="447" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B447" s="15"/>
     </row>
-    <row r="448" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="448" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B448" s="15"/>
     </row>
-    <row r="449" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="449" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B449" s="15"/>
     </row>
-    <row r="450" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="450" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B450" s="15"/>
     </row>
-    <row r="451" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="451" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B451" s="15"/>
     </row>
-    <row r="452" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="452" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B452" s="15"/>
     </row>
-    <row r="453" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="453" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B453" s="15"/>
     </row>
-    <row r="454" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="454" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B454" s="15"/>
     </row>
-    <row r="455" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="455" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B455" s="15"/>
     </row>
-    <row r="456" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="456" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B456" s="15"/>
     </row>
-    <row r="457" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="457" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B457" s="15"/>
     </row>
-    <row r="458" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="458" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B458" s="15"/>
     </row>
-    <row r="459" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="459" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B459" s="15"/>
     </row>
-    <row r="460" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="460" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B460" s="15"/>
     </row>
-    <row r="461" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="461" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B461" s="15"/>
     </row>
-    <row r="462" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="462" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B462" s="15"/>
     </row>
-    <row r="463" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="463" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B463" s="15"/>
     </row>
-    <row r="464" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="464" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B464" s="15"/>
     </row>
-    <row r="465" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="465" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B465" s="15"/>
     </row>
-    <row r="466" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="466" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B466" s="15"/>
     </row>
-    <row r="467" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="467" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B467" s="15"/>
     </row>
-    <row r="468" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="468" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B468" s="15"/>
     </row>
-    <row r="469" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="469" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B469" s="15"/>
     </row>
-    <row r="470" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="470" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B470" s="15"/>
     </row>
-    <row r="471" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="471" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B471" s="15"/>
     </row>
-    <row r="472" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="472" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B472" s="15"/>
     </row>
-    <row r="473" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="473" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B473" s="15"/>
     </row>
-    <row r="474" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="474" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B474" s="15"/>
     </row>
-    <row r="475" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="475" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B475" s="15"/>
     </row>
-    <row r="476" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="476" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B476" s="15"/>
     </row>
-    <row r="477" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="477" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B477" s="15"/>
     </row>
-    <row r="478" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="478" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B478" s="15"/>
     </row>
-    <row r="479" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="479" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B479" s="15"/>
     </row>
-    <row r="480" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="480" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B480" s="15"/>
     </row>
-    <row r="481" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="481" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B481" s="15"/>
     </row>
-    <row r="482" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="482" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B482" s="15"/>
     </row>
-    <row r="483" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="483" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B483" s="15"/>
     </row>
-    <row r="484" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="484" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B484" s="15"/>
     </row>
-    <row r="485" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="485" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B485" s="15"/>
     </row>
-    <row r="486" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="486" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B486" s="15"/>
     </row>
-    <row r="487" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="487" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B487" s="15"/>
     </row>
-    <row r="488" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="488" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B488" s="15"/>
     </row>
-    <row r="489" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="489" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B489" s="15"/>
     </row>
-    <row r="490" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="490" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B490" s="15"/>
     </row>
-    <row r="491" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="491" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B491" s="15"/>
     </row>
-    <row r="492" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="492" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B492" s="15"/>
     </row>
-    <row r="493" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="493" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B493" s="15"/>
     </row>
-    <row r="494" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="494" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B494" s="15"/>
     </row>
-    <row r="495" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="495" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B495" s="15"/>
     </row>
-    <row r="496" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="496" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B496" s="15"/>
     </row>
-    <row r="497" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="497" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B497" s="15"/>
     </row>
-    <row r="498" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="498" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B498" s="15"/>
     </row>
-    <row r="499" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="499" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B499" s="15"/>
     </row>
-    <row r="500" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="500" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B500" s="15"/>
     </row>
-    <row r="501" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="501" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B501" s="15"/>
     </row>
-    <row r="502" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="502" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B502" s="15"/>
     </row>
-    <row r="503" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="503" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B503" s="15"/>
     </row>
-    <row r="504" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="504" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B504" s="15"/>
     </row>
-    <row r="505" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="505" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B505" s="15"/>
     </row>
-    <row r="506" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="506" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B506" s="15"/>
     </row>
-    <row r="507" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="507" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B507" s="15"/>
     </row>
-    <row r="508" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="508" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B508" s="15"/>
     </row>
-    <row r="509" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="509" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B509" s="15"/>
     </row>
-    <row r="510" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="510" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B510" s="15"/>
     </row>
-    <row r="511" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="511" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B511" s="15"/>
     </row>
-    <row r="512" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="512" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B512" s="15"/>
     </row>
-    <row r="513" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="513" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B513" s="15"/>
     </row>
-    <row r="514" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="514" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B514" s="15"/>
     </row>
-    <row r="515" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="515" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B515" s="15"/>
     </row>
-    <row r="516" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="516" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B516" s="15"/>
     </row>
-    <row r="517" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="517" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B517" s="15"/>
     </row>
-    <row r="518" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="518" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B518" s="15"/>
     </row>
-    <row r="519" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="519" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B519" s="15"/>
     </row>
-    <row r="520" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="520" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B520" s="15"/>
     </row>
-    <row r="521" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="521" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B521" s="15"/>
     </row>
-    <row r="522" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="522" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B522" s="15"/>
     </row>
-    <row r="523" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="523" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B523" s="15"/>
     </row>
-    <row r="524" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="524" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B524" s="15"/>
     </row>
-    <row r="525" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="525" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B525" s="15"/>
     </row>
-    <row r="526" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="526" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B526" s="15"/>
     </row>
-    <row r="527" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="527" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B527" s="15"/>
     </row>
-    <row r="528" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="528" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B528" s="15"/>
     </row>
-    <row r="529" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="529" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B529" s="15"/>
     </row>
-    <row r="530" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="530" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B530" s="15"/>
     </row>
-    <row r="531" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="531" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B531" s="15"/>
     </row>
-    <row r="532" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="532" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B532" s="15"/>
     </row>
-    <row r="533" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="533" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B533" s="15"/>
     </row>
-    <row r="534" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="534" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B534" s="15"/>
     </row>
-    <row r="535" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="535" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B535" s="15"/>
     </row>
-    <row r="536" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="536" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B536" s="15"/>
     </row>
-    <row r="537" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="537" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B537" s="15"/>
     </row>
-    <row r="538" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="538" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B538" s="15"/>
     </row>
-    <row r="539" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="539" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B539" s="15"/>
     </row>
-    <row r="540" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="540" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B540" s="15"/>
     </row>
-    <row r="541" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="541" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B541" s="15"/>
     </row>
-    <row r="542" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="542" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B542" s="15"/>
     </row>
-    <row r="543" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="543" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B543" s="15"/>
     </row>
-    <row r="544" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="544" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B544" s="15"/>
     </row>
-    <row r="545" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="545" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B545" s="15"/>
     </row>
-    <row r="546" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="546" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B546" s="15"/>
     </row>
-    <row r="547" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="547" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B547" s="15"/>
     </row>
-    <row r="548" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="548" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B548" s="15"/>
     </row>
-    <row r="549" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="549" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B549" s="15"/>
     </row>
-    <row r="550" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="550" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B550" s="15"/>
     </row>
-    <row r="551" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="551" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B551" s="15"/>
     </row>
-    <row r="552" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="552" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B552" s="15"/>
     </row>
-    <row r="553" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="553" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B553" s="15"/>
     </row>
-    <row r="554" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="554" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B554" s="15"/>
     </row>
-    <row r="555" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="555" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B555" s="15"/>
     </row>
-    <row r="556" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="556" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B556" s="15"/>
     </row>
-    <row r="557" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="557" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B557" s="15"/>
     </row>
-    <row r="558" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="558" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B558" s="15"/>
     </row>
-    <row r="559" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="559" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B559" s="15"/>
     </row>
-    <row r="560" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="560" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B560" s="15"/>
     </row>
-    <row r="561" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="561" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B561" s="15"/>
     </row>
-    <row r="562" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="562" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B562" s="15"/>
     </row>
-    <row r="563" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="563" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B563" s="15"/>
     </row>
-    <row r="564" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="564" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B564" s="15"/>
     </row>
-    <row r="565" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="565" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B565" s="15"/>
     </row>
-    <row r="566" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="566" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B566" s="15"/>
     </row>
-    <row r="567" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="567" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B567" s="15"/>
     </row>
-    <row r="568" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="568" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B568" s="15"/>
     </row>
-    <row r="569" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="569" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B569" s="15"/>
     </row>
-    <row r="570" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="570" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B570" s="15"/>
     </row>
-    <row r="571" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="571" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B571" s="15"/>
     </row>
-    <row r="572" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="572" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B572" s="15"/>
     </row>
-    <row r="573" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="573" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B573" s="15"/>
     </row>
-    <row r="574" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="574" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B574" s="15"/>
     </row>
-    <row r="575" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="575" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B575" s="15"/>
     </row>
-    <row r="576" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="576" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B576" s="15"/>
     </row>
-    <row r="577" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="577" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B577" s="15"/>
     </row>
-    <row r="578" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="578" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B578" s="15"/>
     </row>
-    <row r="579" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="579" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B579" s="15"/>
     </row>
-    <row r="580" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="580" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B580" s="15"/>
     </row>
-    <row r="581" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="581" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B581" s="15"/>
     </row>
-    <row r="582" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="582" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B582" s="15"/>
     </row>
-    <row r="583" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="583" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B583" s="15"/>
     </row>
-    <row r="584" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="584" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B584" s="15"/>
     </row>
-    <row r="585" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="585" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B585" s="15"/>
     </row>
-    <row r="586" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="586" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B586" s="15"/>
     </row>
-    <row r="587" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="587" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B587" s="15"/>
     </row>
-    <row r="588" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="588" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B588" s="15"/>
     </row>
-    <row r="589" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="589" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B589" s="15"/>
     </row>
-    <row r="590" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="590" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B590" s="15"/>
     </row>
-    <row r="591" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="591" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B591" s="15"/>
     </row>
-    <row r="592" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="592" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B592" s="15"/>
     </row>
-    <row r="593" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="593" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B593" s="15"/>
     </row>
-    <row r="594" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="594" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B594" s="15"/>
     </row>
-    <row r="595" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="595" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B595" s="15"/>
     </row>
-    <row r="596" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="596" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B596" s="15"/>
     </row>
-    <row r="597" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="597" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B597" s="15"/>
     </row>
-    <row r="598" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="598" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B598" s="15"/>
     </row>
-    <row r="599" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="599" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B599" s="15"/>
     </row>
-    <row r="600" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="600" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B600" s="15"/>
     </row>
-    <row r="601" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="601" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B601" s="15"/>
     </row>
-    <row r="602" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="602" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B602" s="15"/>
     </row>
-    <row r="603" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="603" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B603" s="15"/>
     </row>
-    <row r="604" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="604" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B604" s="15"/>
     </row>
-    <row r="605" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="605" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B605" s="15"/>
     </row>
-    <row r="606" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="606" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B606" s="15"/>
     </row>
-    <row r="607" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="607" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B607" s="15"/>
     </row>
-    <row r="608" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="608" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B608" s="15"/>
     </row>
-    <row r="609" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="609" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B609" s="15"/>
     </row>
-    <row r="610" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="610" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B610" s="15"/>
     </row>
-    <row r="611" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="611" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B611" s="15"/>
     </row>
-    <row r="612" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="612" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B612" s="15"/>
     </row>
-    <row r="613" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="613" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B613" s="15"/>
     </row>
-    <row r="614" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="614" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B614" s="15"/>
     </row>
-    <row r="615" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="615" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B615" s="15"/>
     </row>
-    <row r="616" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="616" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B616" s="15"/>
     </row>
-    <row r="617" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="617" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B617" s="15"/>
     </row>
-    <row r="618" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="618" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B618" s="15"/>
     </row>
-    <row r="619" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="619" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B619" s="15"/>
     </row>
-    <row r="620" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="620" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B620" s="15"/>
     </row>
-    <row r="621" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="621" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B621" s="15"/>
     </row>
-    <row r="622" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="622" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B622" s="15"/>
     </row>
-    <row r="623" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="623" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B623" s="15"/>
     </row>
-    <row r="624" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="624" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B624" s="15"/>
     </row>
-    <row r="625" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="625" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B625" s="15"/>
     </row>
-    <row r="626" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="626" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B626" s="15"/>
     </row>
-    <row r="627" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="627" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B627" s="15"/>
     </row>
-    <row r="628" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="628" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B628" s="15"/>
     </row>
-    <row r="629" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="629" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B629" s="15"/>
     </row>
-    <row r="630" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="630" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B630" s="15"/>
     </row>
-    <row r="631" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="631" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B631" s="15"/>
     </row>
-    <row r="632" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="632" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B632" s="15"/>
     </row>
-    <row r="633" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="633" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B633" s="15"/>
     </row>
-    <row r="634" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="634" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B634" s="15"/>
     </row>
-    <row r="635" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="635" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B635" s="15"/>
     </row>
-    <row r="636" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="636" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B636" s="15"/>
     </row>
-    <row r="637" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="637" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B637" s="15"/>
     </row>
-    <row r="638" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="638" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B638" s="15"/>
     </row>
-    <row r="639" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="639" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B639" s="15"/>
     </row>
-    <row r="640" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="640" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B640" s="15"/>
     </row>
-    <row r="641" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="641" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B641" s="15"/>
     </row>
-    <row r="642" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="642" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B642" s="15"/>
     </row>
-    <row r="643" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="643" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B643" s="15"/>
     </row>
-    <row r="644" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="644" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B644" s="15"/>
     </row>
-    <row r="645" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="645" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B645" s="15"/>
     </row>
-    <row r="646" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="646" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B646" s="15"/>
     </row>
-    <row r="647" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="647" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B647" s="15"/>
     </row>
-    <row r="648" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="648" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B648" s="15"/>
     </row>
-    <row r="649" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="649" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B649" s="15"/>
     </row>
-    <row r="650" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="650" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B650" s="15"/>
     </row>
-    <row r="651" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="651" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B651" s="15"/>
     </row>
-    <row r="652" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="652" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B652" s="15"/>
     </row>
-    <row r="653" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="653" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B653" s="15"/>
     </row>
-    <row r="654" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="654" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B654" s="15"/>
     </row>
-    <row r="655" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="655" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B655" s="15"/>
     </row>
-    <row r="656" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="656" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B656" s="15"/>
     </row>
-    <row r="657" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="657" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B657" s="15"/>
     </row>
-    <row r="658" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="658" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B658" s="15"/>
     </row>
-    <row r="659" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="659" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B659" s="15"/>
     </row>
-    <row r="660" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="660" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B660" s="15"/>
     </row>
-    <row r="661" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="661" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B661" s="15"/>
     </row>
-    <row r="662" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="662" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B662" s="15"/>
     </row>
-    <row r="663" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="663" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B663" s="15"/>
     </row>
-    <row r="664" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="664" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B664" s="15"/>
     </row>
-    <row r="665" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="665" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B665" s="15"/>
     </row>
-    <row r="666" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="666" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B666" s="15"/>
     </row>
-    <row r="667" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="667" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B667" s="15"/>
     </row>
-    <row r="668" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="668" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B668" s="15"/>
     </row>
-    <row r="669" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="669" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B669" s="15"/>
     </row>
-    <row r="670" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="670" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B670" s="15"/>
     </row>
-    <row r="671" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="671" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B671" s="15"/>
     </row>
-    <row r="672" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="672" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B672" s="15"/>
     </row>
-    <row r="673" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="673" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B673" s="15"/>
     </row>
-    <row r="674" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="674" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B674" s="15"/>
     </row>
-    <row r="675" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="675" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B675" s="15"/>
     </row>
-    <row r="676" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="676" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B676" s="15"/>
     </row>
-    <row r="677" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="677" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B677" s="15"/>
     </row>
-    <row r="678" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="678" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B678" s="15"/>
     </row>
-    <row r="679" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="679" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B679" s="15"/>
     </row>
-    <row r="680" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="680" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B680" s="15"/>
     </row>
-    <row r="681" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="681" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B681" s="15"/>
     </row>
-    <row r="682" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="682" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B682" s="15"/>
     </row>
-    <row r="683" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="683" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B683" s="15"/>
     </row>
-    <row r="684" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="684" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B684" s="15"/>
     </row>
-    <row r="685" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="685" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B685" s="15"/>
     </row>
-    <row r="686" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="686" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B686" s="15"/>
     </row>
-    <row r="687" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="687" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B687" s="15"/>
     </row>
-    <row r="688" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="688" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B688" s="15"/>
     </row>
-    <row r="689" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="689" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B689" s="15"/>
     </row>
-    <row r="690" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="690" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B690" s="15"/>
     </row>
-    <row r="691" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="691" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B691" s="15"/>
     </row>
-    <row r="692" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="692" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B692" s="15"/>
     </row>
-    <row r="693" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="693" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B693" s="15"/>
     </row>
-    <row r="694" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="694" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B694" s="15"/>
     </row>
-    <row r="695" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="695" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B695" s="15"/>
     </row>
-    <row r="696" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="696" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B696" s="15"/>
     </row>
-    <row r="697" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="697" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B697" s="15"/>
     </row>
-    <row r="698" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="698" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B698" s="15"/>
     </row>
-    <row r="699" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="699" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B699" s="15"/>
     </row>
-    <row r="700" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="700" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B700" s="15"/>
     </row>
-    <row r="701" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="701" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B701" s="15"/>
     </row>
-    <row r="702" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="702" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B702" s="15"/>
     </row>
-    <row r="703" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="703" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B703" s="15"/>
     </row>
-    <row r="704" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="704" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B704" s="15"/>
     </row>
-    <row r="705" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="705" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B705" s="15"/>
     </row>
-    <row r="706" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="706" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B706" s="15"/>
     </row>
-    <row r="707" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="707" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B707" s="15"/>
     </row>
-    <row r="708" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="708" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B708" s="15"/>
     </row>
-    <row r="709" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="709" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B709" s="15"/>
     </row>
-    <row r="710" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="710" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B710" s="15"/>
     </row>
-    <row r="711" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="711" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B711" s="15"/>
     </row>
-    <row r="712" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="712" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B712" s="15"/>
     </row>
-    <row r="713" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="713" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B713" s="15"/>
     </row>
-    <row r="714" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="714" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B714" s="15"/>
     </row>
-    <row r="715" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="715" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B715" s="15"/>
     </row>
-    <row r="716" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="716" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B716" s="15"/>
     </row>
-    <row r="717" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="717" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B717" s="15"/>
     </row>
-    <row r="718" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="718" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B718" s="15"/>
     </row>
-    <row r="719" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="719" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B719" s="15"/>
     </row>
-    <row r="720" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="720" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B720" s="15"/>
     </row>
-    <row r="721" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="721" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B721" s="15"/>
     </row>
-    <row r="722" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="722" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B722" s="15"/>
     </row>
-    <row r="723" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="723" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B723" s="15"/>
     </row>
-    <row r="724" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="724" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B724" s="15"/>
     </row>
-    <row r="725" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="725" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B725" s="15"/>
     </row>
-    <row r="726" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="726" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B726" s="15"/>
     </row>
-    <row r="727" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="727" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B727" s="15"/>
     </row>
-    <row r="728" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="728" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B728" s="15"/>
     </row>
-    <row r="729" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="729" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B729" s="15"/>
     </row>
-    <row r="730" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="730" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B730" s="15"/>
     </row>
-    <row r="731" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="731" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B731" s="15"/>
     </row>
-    <row r="732" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="732" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B732" s="15"/>
     </row>
-    <row r="733" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="733" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B733" s="15"/>
     </row>
-    <row r="734" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="734" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B734" s="15"/>
     </row>
-    <row r="735" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="735" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B735" s="15"/>
     </row>
-    <row r="736" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="736" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B736" s="15"/>
     </row>
-    <row r="737" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="737" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B737" s="15"/>
     </row>
-    <row r="738" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="738" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B738" s="15"/>
     </row>
-    <row r="739" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="739" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B739" s="15"/>
     </row>
-    <row r="740" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="740" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B740" s="15"/>
     </row>
-    <row r="741" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="741" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B741" s="15"/>
     </row>
-    <row r="742" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="742" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B742" s="15"/>
     </row>
-    <row r="743" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="743" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B743" s="15"/>
     </row>
-    <row r="744" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="744" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B744" s="15"/>
     </row>
-    <row r="745" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="745" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B745" s="15"/>
     </row>
-    <row r="746" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="746" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B746" s="15"/>
     </row>
-    <row r="747" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="747" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B747" s="15"/>
     </row>
-    <row r="748" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="748" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B748" s="15"/>
     </row>
-    <row r="749" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="749" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B749" s="15"/>
     </row>
-    <row r="750" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="750" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B750" s="15"/>
     </row>
-    <row r="751" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="751" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B751" s="15"/>
     </row>
-    <row r="752" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="752" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B752" s="15"/>
     </row>
-    <row r="753" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="753" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B753" s="15"/>
     </row>
-    <row r="754" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="754" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B754" s="15"/>
     </row>
-    <row r="755" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="755" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B755" s="15"/>
     </row>
-    <row r="756" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="756" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B756" s="15"/>
     </row>
-    <row r="757" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="757" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B757" s="15"/>
     </row>
-    <row r="758" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="758" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B758" s="15"/>
     </row>
-    <row r="759" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="759" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B759" s="15"/>
     </row>
-    <row r="760" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="760" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B760" s="15"/>
     </row>
-    <row r="761" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="761" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B761" s="15"/>
     </row>
-    <row r="762" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="762" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B762" s="15"/>
     </row>
-    <row r="763" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="763" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B763" s="15"/>
     </row>
-    <row r="764" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="764" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B764" s="15"/>
     </row>
-    <row r="765" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="765" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B765" s="15"/>
     </row>
-    <row r="766" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="766" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B766" s="15"/>
     </row>
-    <row r="767" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="767" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B767" s="15"/>
     </row>
-    <row r="768" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="768" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B768" s="15"/>
     </row>
-    <row r="769" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="769" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B769" s="15"/>
     </row>
-    <row r="770" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="770" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B770" s="15"/>
     </row>
-    <row r="771" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="771" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B771" s="15"/>
     </row>
-    <row r="772" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="772" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B772" s="15"/>
     </row>
-    <row r="773" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="773" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B773" s="15"/>
     </row>
-    <row r="774" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="774" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B774" s="15"/>
     </row>
-    <row r="775" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="775" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B775" s="15"/>
     </row>
-    <row r="776" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="776" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B776" s="15"/>
     </row>
-    <row r="777" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="777" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B777" s="15"/>
     </row>
-    <row r="778" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="778" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B778" s="15"/>
     </row>
-    <row r="779" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="779" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B779" s="15"/>
     </row>
-    <row r="780" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="780" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B780" s="15"/>
     </row>
-    <row r="781" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="781" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B781" s="15"/>
     </row>
-    <row r="782" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="782" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B782" s="15"/>
     </row>
-    <row r="783" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="783" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B783" s="15"/>
     </row>
-    <row r="784" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="784" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B784" s="15"/>
     </row>
-    <row r="785" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="785" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B785" s="15"/>
     </row>
-    <row r="786" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="786" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B786" s="15"/>
     </row>
-    <row r="787" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="787" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B787" s="15"/>
     </row>
-    <row r="788" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="788" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B788" s="15"/>
     </row>
-    <row r="789" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="789" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B789" s="15"/>
     </row>
-    <row r="790" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="790" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B790" s="15"/>
     </row>
-    <row r="791" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="791" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B791" s="15"/>
     </row>
-    <row r="792" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="792" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B792" s="15"/>
     </row>
-    <row r="793" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="793" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B793" s="15"/>
     </row>
-    <row r="794" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="794" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B794" s="15"/>
     </row>
-    <row r="795" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="795" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B795" s="15"/>
     </row>
-    <row r="796" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="796" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B796" s="15"/>
     </row>
-    <row r="797" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="797" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B797" s="15"/>
     </row>
-    <row r="798" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="798" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B798" s="15"/>
     </row>
-    <row r="799" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="799" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B799" s="15"/>
     </row>
-    <row r="800" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="800" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B800" s="15"/>
     </row>
-    <row r="801" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="801" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B801" s="15"/>
     </row>
-    <row r="802" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="802" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B802" s="15"/>
     </row>
-    <row r="803" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="803" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B803" s="15"/>
     </row>
-    <row r="804" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="804" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B804" s="15"/>
     </row>
-    <row r="805" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="805" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B805" s="15"/>
     </row>
-    <row r="806" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="806" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B806" s="15"/>
     </row>
-    <row r="807" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="807" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B807" s="15"/>
     </row>
-    <row r="808" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="808" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B808" s="15"/>
     </row>
-    <row r="809" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="809" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B809" s="15"/>
     </row>
-    <row r="810" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="810" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B810" s="15"/>
     </row>
-    <row r="811" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="811" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B811" s="15"/>
     </row>
-    <row r="812" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="812" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B812" s="15"/>
     </row>
-    <row r="813" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="813" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B813" s="15"/>
     </row>
-    <row r="814" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="814" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B814" s="15"/>
     </row>
-    <row r="815" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="815" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B815" s="15"/>
     </row>
-    <row r="816" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="816" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B816" s="15"/>
     </row>
-    <row r="817" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="817" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B817" s="15"/>
     </row>
-    <row r="818" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="818" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B818" s="15"/>
     </row>
-    <row r="819" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="819" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B819" s="15"/>
     </row>
-    <row r="820" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="820" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B820" s="15"/>
     </row>
-    <row r="821" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="821" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B821" s="15"/>
     </row>
-    <row r="822" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="822" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B822" s="15"/>
     </row>
-    <row r="823" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="823" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B823" s="15"/>
     </row>
-    <row r="824" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="824" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B824" s="15"/>
     </row>
-    <row r="825" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="825" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B825" s="15"/>
     </row>
-    <row r="826" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="826" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B826" s="15"/>
     </row>
-    <row r="827" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="827" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B827" s="15"/>
     </row>
-    <row r="828" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="828" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B828" s="15"/>
     </row>
-    <row r="829" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="829" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B829" s="15"/>
     </row>
-    <row r="830" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="830" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B830" s="15"/>
     </row>
-    <row r="831" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="831" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B831" s="15"/>
     </row>
-    <row r="832" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="832" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B832" s="15"/>
     </row>
-    <row r="833" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="833" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B833" s="15"/>
     </row>
-    <row r="834" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="834" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B834" s="15"/>
     </row>
-    <row r="835" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="835" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B835" s="15"/>
     </row>
-    <row r="836" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="836" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B836" s="15"/>
     </row>
-    <row r="837" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="837" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B837" s="15"/>
     </row>
-    <row r="838" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="838" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B838" s="15"/>
     </row>
-    <row r="839" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="839" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B839" s="15"/>
     </row>
-    <row r="840" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="840" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B840" s="15"/>
     </row>
-    <row r="841" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="841" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B841" s="15"/>
     </row>
-    <row r="842" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="842" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B842" s="15"/>
     </row>
-    <row r="843" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="843" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B843" s="15"/>
     </row>
-    <row r="844" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="844" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B844" s="15"/>
     </row>
-    <row r="845" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="845" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B845" s="15"/>
     </row>
-    <row r="846" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="846" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B846" s="15"/>
     </row>
-    <row r="847" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="847" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B847" s="15"/>
     </row>
-    <row r="848" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="848" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B848" s="15"/>
     </row>
-    <row r="849" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="849" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B849" s="15"/>
     </row>
-    <row r="850" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="850" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B850" s="15"/>
     </row>
-    <row r="851" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="851" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B851" s="15"/>
     </row>
-    <row r="852" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="852" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B852" s="15"/>
     </row>
-    <row r="853" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="853" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B853" s="15"/>
     </row>
-    <row r="854" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="854" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B854" s="15"/>
     </row>
-    <row r="855" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="855" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B855" s="15"/>
     </row>
-    <row r="856" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="856" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B856" s="15"/>
     </row>
-    <row r="857" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="857" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B857" s="15"/>
     </row>
-    <row r="858" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="858" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B858" s="15"/>
     </row>
-    <row r="859" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="859" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B859" s="15"/>
     </row>
-    <row r="860" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="860" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B860" s="15"/>
     </row>
-    <row r="861" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="861" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B861" s="15"/>
     </row>
-    <row r="862" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="862" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B862" s="15"/>
     </row>
-    <row r="863" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="863" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B863" s="15"/>
     </row>
-    <row r="864" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="864" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B864" s="15"/>
     </row>
-    <row r="865" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="865" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B865" s="15"/>
     </row>
-    <row r="866" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="866" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B866" s="15"/>
     </row>
-    <row r="867" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="867" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B867" s="15"/>
     </row>
-    <row r="868" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="868" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B868" s="15"/>
     </row>
-    <row r="869" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="869" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B869" s="15"/>
     </row>
-    <row r="870" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="870" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B870" s="15"/>
     </row>
-    <row r="871" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="871" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B871" s="15"/>
     </row>
-    <row r="872" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="872" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B872" s="15"/>
     </row>
-    <row r="873" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="873" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B873" s="15"/>
     </row>
-    <row r="874" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="874" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B874" s="15"/>
     </row>
-    <row r="875" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="875" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B875" s="15"/>
     </row>
-    <row r="876" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="876" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B876" s="15"/>
     </row>
-    <row r="877" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="877" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B877" s="15"/>
     </row>
-    <row r="878" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="878" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B878" s="15"/>
     </row>
-    <row r="879" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="879" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B879" s="15"/>
     </row>
-    <row r="880" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="880" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B880" s="15"/>
     </row>
-    <row r="881" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="881" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B881" s="15"/>
     </row>
-    <row r="882" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="882" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B882" s="15"/>
     </row>
-    <row r="883" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="883" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B883" s="15"/>
     </row>
-    <row r="884" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="884" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B884" s="15"/>
     </row>
-    <row r="885" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="885" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B885" s="15"/>
     </row>
-    <row r="886" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="886" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B886" s="15"/>
     </row>
-    <row r="887" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="887" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B887" s="15"/>
     </row>
-    <row r="888" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="888" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B888" s="15"/>
     </row>
-    <row r="889" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="889" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B889" s="15"/>
     </row>
-    <row r="890" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="890" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B890" s="15"/>
     </row>
-    <row r="891" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="891" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B891" s="15"/>
     </row>
-    <row r="892" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="892" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B892" s="15"/>
     </row>
-    <row r="893" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="893" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B893" s="15"/>
     </row>
-    <row r="894" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="894" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B894" s="15"/>
     </row>
-    <row r="895" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="895" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B895" s="15"/>
     </row>
-    <row r="896" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="896" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B896" s="15"/>
     </row>
-    <row r="897" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="897" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B897" s="15"/>
     </row>
-    <row r="898" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="898" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B898" s="15"/>
     </row>
-    <row r="899" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="899" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B899" s="15"/>
     </row>
-    <row r="900" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="900" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B900" s="15"/>
     </row>
-    <row r="901" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="901" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B901" s="15"/>
     </row>
-    <row r="902" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="902" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B902" s="15"/>
     </row>
-    <row r="903" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="903" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B903" s="15"/>
     </row>
-    <row r="904" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="904" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B904" s="15"/>
     </row>
-    <row r="905" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="905" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B905" s="15"/>
     </row>
-    <row r="906" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="906" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B906" s="15"/>
     </row>
-    <row r="907" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="907" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B907" s="15"/>
     </row>
-    <row r="908" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="908" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B908" s="15"/>
     </row>
-    <row r="909" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="909" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B909" s="15"/>
     </row>
-    <row r="910" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="910" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B910" s="15"/>
     </row>
-    <row r="911" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="911" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B911" s="15"/>
     </row>
-    <row r="912" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="912" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B912" s="15"/>
     </row>
-    <row r="913" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="913" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B913" s="15"/>
     </row>
-    <row r="914" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="914" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B914" s="15"/>
     </row>
-    <row r="915" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="915" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B915" s="15"/>
     </row>
-    <row r="916" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="916" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B916" s="15"/>
     </row>
-    <row r="917" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="917" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B917" s="15"/>
     </row>
-    <row r="918" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="918" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B918" s="15"/>
     </row>
-    <row r="919" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="919" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B919" s="15"/>
     </row>
-    <row r="920" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="920" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B920" s="15"/>
     </row>
-    <row r="921" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="921" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B921" s="15"/>
     </row>
-    <row r="922" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="922" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B922" s="15"/>
     </row>
-    <row r="923" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="923" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B923" s="15"/>
     </row>
-    <row r="924" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="924" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B924" s="15"/>
     </row>
-    <row r="925" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="925" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B925" s="15"/>
     </row>
-    <row r="926" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="926" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B926" s="15"/>
     </row>
-    <row r="927" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="927" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B927" s="15"/>
     </row>
-    <row r="928" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="928" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B928" s="15"/>
     </row>
-    <row r="929" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="929" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B929" s="15"/>
     </row>
-    <row r="930" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="930" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B930" s="15"/>
     </row>
-    <row r="931" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="931" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B931" s="15"/>
     </row>
-    <row r="932" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="932" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B932" s="15"/>
     </row>
-    <row r="933" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="933" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B933" s="15"/>
     </row>
-    <row r="934" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="934" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B934" s="15"/>
     </row>
-    <row r="935" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="935" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B935" s="15"/>
     </row>
-    <row r="936" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="936" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B936" s="15"/>
     </row>
-    <row r="937" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="937" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B937" s="15"/>
     </row>
-    <row r="938" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="938" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B938" s="15"/>
     </row>
-    <row r="939" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="939" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B939" s="15"/>
     </row>
-    <row r="940" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="940" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B940" s="15"/>
     </row>
-    <row r="941" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="941" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B941" s="15"/>
     </row>
-    <row r="942" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="942" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B942" s="15"/>
     </row>
-    <row r="943" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="943" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B943" s="15"/>
     </row>
-    <row r="944" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="944" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B944" s="15"/>
     </row>
-    <row r="945" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="945" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B945" s="15"/>
     </row>
-    <row r="946" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="946" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B946" s="15"/>
     </row>
-    <row r="947" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="947" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B947" s="15"/>
     </row>
-    <row r="948" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="948" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B948" s="15"/>
     </row>
-    <row r="949" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="949" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B949" s="15"/>
     </row>
-    <row r="950" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="950" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B950" s="15"/>
     </row>
-    <row r="951" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="951" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B951" s="15"/>
     </row>
-    <row r="952" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="952" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B952" s="15"/>
     </row>
-    <row r="953" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="953" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B953" s="15"/>
     </row>
-    <row r="954" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="954" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B954" s="15"/>
     </row>
-    <row r="955" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="955" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B955" s="15"/>
     </row>
-    <row r="956" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="956" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B956" s="15"/>
     </row>
-    <row r="957" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="957" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B957" s="15"/>
     </row>
-    <row r="958" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="958" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B958" s="15"/>
     </row>
-    <row r="959" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="959" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B959" s="15"/>
     </row>
-    <row r="960" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="960" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B960" s="15"/>
     </row>
-    <row r="961" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="961" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B961" s="15"/>
     </row>
-    <row r="962" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="962" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B962" s="15"/>
     </row>
-    <row r="963" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="963" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B963" s="15"/>
     </row>
-    <row r="964" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="964" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B964" s="15"/>
     </row>
-    <row r="965" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="965" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B965" s="15"/>
     </row>
-    <row r="966" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="966" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B966" s="15"/>
     </row>
-    <row r="967" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="967" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B967" s="15"/>
     </row>
-    <row r="968" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="968" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B968" s="15"/>
     </row>
-    <row r="969" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="969" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B969" s="15"/>
     </row>
-    <row r="970" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="970" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B970" s="15"/>
     </row>
-    <row r="971" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="971" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B971" s="15"/>
     </row>
-    <row r="972" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="972" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B972" s="15"/>
     </row>
-    <row r="973" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="973" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B973" s="15"/>
     </row>
-    <row r="974" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="974" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B974" s="15"/>
     </row>
-    <row r="975" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="975" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B975" s="15"/>
     </row>
-    <row r="976" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="976" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B976" s="15"/>
     </row>
-    <row r="977" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="977" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B977" s="15"/>
     </row>
-    <row r="978" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="978" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B978" s="15"/>
     </row>
-    <row r="979" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="979" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B979" s="15"/>
     </row>
-    <row r="980" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="980" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B980" s="15"/>
     </row>
-    <row r="981" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="981" spans="2:2" ht="13" x14ac:dyDescent="0.15">
       <c r="B981" s="15"/>
     </row>
   </sheetData>

--- a/data/input/OthoDataset.xlsx
+++ b/data/input/OthoDataset.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/i833032/DevResearch/Otho/data/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADFBA894-E6C9-594E-B62D-3194C12A29F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1307E0D9-1618-4542-8963-ACA0BCE4A0EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CQs" sheetId="1" r:id="rId1"/>
     <sheet name="Story" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CQs!$A$1:$A$1042</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CQs!$A$1:$D$60</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="187">
   <si>
     <t>StoryID</t>
   </si>
@@ -357,6 +357,256 @@
     <t>Hospital setting
 Pasquale Di Gennaro first studied to become a nursing assistant, but after working some years he decided to continue studying to become a certified nurse. He took his degree in May 2001. On September 21 (2001) he was employed at Ospedale Riunito delle Tre Valli in the city of Nocera Inferiore (IT). In the hospital there are different unions organising the staff. Pasquale Di Gennaro has been the union representative for male nurses at Ospedale Riunito delle Tre Valli from 2002. Senior doctors regularly evaluate all employees working with patient care, and these written statements are stored for future reference.
 To constantly update their knowledge both nurses and doctors read research articles that can be found in article collections at the hospital library. Article collections are usually available both as books and electronically on CDs. In 2008 an article collection entitled “Nurse practices in cancer patient care – longitudinal studies at Italian hospitals” was published as a book. The book contains an article by Pasquale Di Gennaro, entitled “A 5 year-program for improving cancer care – experiences and future directions”. In total the book version of this collection has 346 pages. For discussing new articles Italian hospitals regularly hold seminars where a number of articles are presented. In December 2008 such a seminar was held in Nocera Inferiore at Ospedale Riunito delle Tre Valli.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What invoices are all listed in an EDIFACT message? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Which organizations are involved in the invoice? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">What role does organization S play in the invoice? </t>
+  </si>
+  <si>
+    <t>Which organization is the buyer in the invoice?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What information is displayed about the involved organizations? </t>
+  </si>
+  <si>
+    <t>What is the address of the buyer?</t>
+  </si>
+  <si>
+    <t>What items are sold in the invoice?</t>
+  </si>
+  <si>
+    <t>What information is displayed about the items sold?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What is the net price of the items sold in the invoice? </t>
+  </si>
+  <si>
+    <t>What are the invoice details of the invoice?</t>
+  </si>
+  <si>
+    <t>What is the invoice amount of the invoice?</t>
+  </si>
+  <si>
+    <t>What is the invoice number?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What information must be provided so that the file format is valid? </t>
+  </si>
+  <si>
+    <t>To which business process can the invoice be assigned?</t>
+  </si>
+  <si>
+    <t>EDIFACT</t>
+  </si>
+  <si>
+    <t>EdifactCQ1</t>
+  </si>
+  <si>
+    <t>EdifactCQ2</t>
+  </si>
+  <si>
+    <t>EdifactCQ3</t>
+  </si>
+  <si>
+    <t>EdifactCQ4</t>
+  </si>
+  <si>
+    <t>EdifactCQ5</t>
+  </si>
+  <si>
+    <t>EdifactCQ6</t>
+  </si>
+  <si>
+    <t>EdifactCQ7</t>
+  </si>
+  <si>
+    <t>EdifactCQ8</t>
+  </si>
+  <si>
+    <t>EdifactCQ9</t>
+  </si>
+  <si>
+    <t>EdifactCQ10</t>
+  </si>
+  <si>
+    <t>EdifactCQ11</t>
+  </si>
+  <si>
+    <t>EdifactCQ12</t>
+  </si>
+  <si>
+    <t>EdifactCQ13</t>
+  </si>
+  <si>
+    <t>EdifactCQ14</t>
+  </si>
+  <si>
+    <t>The UN/EDIFACT standard defines a rigid hierarchy for digital business documents, beginning with an Interchange envelope that contains specific Messages like the INVOIC for global trade transactions. Each message is composed of Segments, such as the Beginning of Message (BGM) for document identification and the Name and Address (NAD) for participant details. These segments are further broken down into Composite and Simple Data Elements, separated by specific delimiters like plus signs and colons. Within a single invoice message, data is organized into three distinct sections: a header containing document dates and reference numbers, a detail section listing individual line items with their net prices and quantities, and a summary section providing the total tax and invoice amounts.
+In industrial procurement scenarios, such as those at the Einkaufsbüro Deutscher Eisenhändler (E/D/E), an organization often performs multiple roles within a single transaction, acting as the Buyer in one context and the Delivery Party in another. Each role may involve different attributes, such as separate headquarters and warehouse addresses, which are linked to the organization through specific Agent Role patterns and identifiers like Global Location Numbers. To ensure semantic interoperability, these documents are aligned with the European Standard EN 16931-1 and the Purchase-to-Pay Ontology (P2P-O), which defines core classes for items, prices, and organizations. The resulting knowledge graphs allow for automated validation using SHACL constraints, verifying that itemized prices sum correctly to the reported totals and that all mandatory identifiers required by the D96A directory are present and logically consistent.</t>
+  </si>
+  <si>
+    <t>ERA</t>
+  </si>
+  <si>
+    <t>Which are the distinct values for a particular parameter P (e.g., minimum radius of horizontal curve) of a track in member state C?</t>
+  </si>
+  <si>
+    <t>How many tunnels are there per member state?</t>
+  </si>
+  <si>
+    <t>What is the tunnel length per member state?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What is the railway length per member state? </t>
+  </si>
+  <si>
+    <t>What are the platform lengths in ascending order? (What is the variety of platform lengths in Eurrope?</t>
+  </si>
+  <si>
+    <t>What are the parameters of a certain entity E in the vocabulary (e.g., operational point, siding?</t>
+  </si>
+  <si>
+    <t>Which are non TSI compliant legacy signalling systems existent in the different countries?</t>
+  </si>
+  <si>
+    <t>What are the number of tons per track?</t>
+  </si>
+  <si>
+    <t>Which are the energy supply system values (voltage frequency) per SOL per member state?</t>
+  </si>
+  <si>
+    <t>What is the network of an infrastructure manager IM?</t>
+  </si>
+  <si>
+    <t>Which are the electrified lines of NN  kV and with a nominal track gauge of NNNN mm</t>
+  </si>
+  <si>
+    <t>Which are the diesel vehicle types?</t>
+  </si>
+  <si>
+    <t>Which are the tracks with a contact line system type that is not electrified</t>
+  </si>
+  <si>
+    <t>What is the track length of  Trans-European Transport Network (TEN-T) lines per member state?</t>
+  </si>
+  <si>
+    <t>What is the primary location code per member state and in a map,  and its distance to a station</t>
+  </si>
+  <si>
+    <t>How many tracks are equipped with GSM-r per member state (rate of deployment?</t>
+  </si>
+  <si>
+    <t>Which tracks are equipped with GSM-r per member state and do they belong to corridor lines?</t>
+  </si>
+  <si>
+    <t>which are the tunnels in Belgium that are not category (rolling stock fire category)  A nor B?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How many countries are using local and non-international Gauges (gauging profile)? </t>
+  </si>
+  <si>
+    <t>What are the available values for the GSM-R version per member state?</t>
+  </si>
+  <si>
+    <t>What are the available ETCS levels and ETCS baselines per member state?</t>
+  </si>
+  <si>
+    <t>What are the number of operational points per member state?</t>
+  </si>
+  <si>
+    <t>What are number of sections of line per member state</t>
+  </si>
+  <si>
+    <t>What is the total length of lines (grouped by member state and type of line - currently section of line or tunnel)?</t>
+  </si>
+  <si>
+    <t>summary of the presence of the core parameter load capability  across all tracks per member state</t>
+  </si>
+  <si>
+    <t>summary of the sections of lines and tracks where the core parameter load capability does not appear (example with Spain)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EraCQ1 </t>
+  </si>
+  <si>
+    <t>EraCQ2</t>
+  </si>
+  <si>
+    <t>EraCQ3</t>
+  </si>
+  <si>
+    <t>EraCQ4</t>
+  </si>
+  <si>
+    <t>EraCQ5</t>
+  </si>
+  <si>
+    <t>EraCQ6</t>
+  </si>
+  <si>
+    <t>EraCQ7</t>
+  </si>
+  <si>
+    <t>EraCQ8</t>
+  </si>
+  <si>
+    <t>EraCQ9</t>
+  </si>
+  <si>
+    <t>EraCQ10</t>
+  </si>
+  <si>
+    <t>EraCQ11</t>
+  </si>
+  <si>
+    <t>EraCQ12</t>
+  </si>
+  <si>
+    <t>EraCQ13</t>
+  </si>
+  <si>
+    <t>EraCQ14</t>
+  </si>
+  <si>
+    <t>EraCQ15</t>
+  </si>
+  <si>
+    <t>EraCQ16</t>
+  </si>
+  <si>
+    <t>EraCQ17</t>
+  </si>
+  <si>
+    <t>EraCQ18</t>
+  </si>
+  <si>
+    <t>EraCQ19</t>
+  </si>
+  <si>
+    <t>EraCQ20</t>
+  </si>
+  <si>
+    <t>EraCQ21</t>
+  </si>
+  <si>
+    <t>EraCQ22</t>
+  </si>
+  <si>
+    <t>EraCQ23</t>
+  </si>
+  <si>
+    <t>EraCQ24</t>
+  </si>
+  <si>
+    <t>EraCQ25</t>
+  </si>
+  <si>
+    <t>EraCQ26</t>
   </si>
 </sst>
 </file>
@@ -386,25 +636,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -445,7 +694,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -459,16 +708,6 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -482,10 +721,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -755,22 +996,16 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:R1042"/>
+  <dimension ref="A1:D1041"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="50.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="94.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.1640625" customWidth="1"/>
-    <col min="5" max="5" width="6.6640625" customWidth="1"/>
-    <col min="7" max="7" width="17.6640625" customWidth="1"/>
-    <col min="8" max="8" width="11.33203125" customWidth="1"/>
-    <col min="10" max="10" width="17.33203125" customWidth="1"/>
-    <col min="11" max="11" width="16.83203125" customWidth="1"/>
-    <col min="13" max="13" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:4" ht="13" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -783,22 +1018,8 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-    </row>
-    <row r="2" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="2" spans="1:4" ht="13" x14ac:dyDescent="0.15">
       <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
@@ -811,16 +1032,8 @@
       <c r="D2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-    </row>
-    <row r="3" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="3" spans="1:4" ht="13" x14ac:dyDescent="0.15">
       <c r="A3" s="5" t="s">
         <v>7</v>
       </c>
@@ -833,19 +1046,8 @@
       <c r="D3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="3"/>
-    </row>
-    <row r="4" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="4" spans="1:4" ht="13" x14ac:dyDescent="0.15">
       <c r="A4" s="6" t="s">
         <v>7</v>
       </c>
@@ -858,19 +1060,8 @@
       <c r="D4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="N4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
-    </row>
-    <row r="5" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="5" spans="1:4" ht="13" x14ac:dyDescent="0.15">
       <c r="A5" s="5" t="s">
         <v>7</v>
       </c>
@@ -883,22 +1074,8 @@
       <c r="D5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3"/>
-    </row>
-    <row r="6" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="6" spans="1:4" ht="13" x14ac:dyDescent="0.15">
       <c r="A6" s="6" t="s">
         <v>7</v>
       </c>
@@ -911,21 +1088,8 @@
       <c r="D6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="8"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="4"/>
-      <c r="Q6" s="4"/>
-      <c r="R6" s="4"/>
-    </row>
-    <row r="7" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="7" spans="1:4" ht="13" x14ac:dyDescent="0.15">
       <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
@@ -938,22 +1102,8 @@
       <c r="D7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
-      <c r="P7" s="3"/>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3"/>
-    </row>
-    <row r="8" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="8" spans="1:4" ht="13" x14ac:dyDescent="0.15">
       <c r="A8" s="6" t="s">
         <v>7</v>
       </c>
@@ -966,22 +1116,8 @@
       <c r="D8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
-      <c r="N8" s="4"/>
-      <c r="O8" s="4"/>
-      <c r="P8" s="4"/>
-      <c r="Q8" s="4"/>
-      <c r="R8" s="4"/>
-    </row>
-    <row r="9" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="9" spans="1:4" ht="13" x14ac:dyDescent="0.15">
       <c r="A9" s="5" t="s">
         <v>7</v>
       </c>
@@ -994,21 +1130,8 @@
       <c r="D9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="10" spans="1:4" ht="13" x14ac:dyDescent="0.15">
       <c r="A10" s="6" t="s">
         <v>7</v>
       </c>
@@ -1021,18 +1144,8 @@
       <c r="D10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="M10" s="4"/>
-      <c r="N10" s="4"/>
-      <c r="P10" s="4"/>
-      <c r="Q10" s="4"/>
-      <c r="R10" s="4"/>
-    </row>
-    <row r="11" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="11" spans="1:4" ht="13" x14ac:dyDescent="0.15">
       <c r="A11" s="5" t="s">
         <v>7</v>
       </c>
@@ -1045,18 +1158,8 @@
       <c r="D11" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
-      <c r="Q11" s="3"/>
-      <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="12" spans="1:4" ht="13" x14ac:dyDescent="0.15">
       <c r="A12" s="6" t="s">
         <v>7</v>
       </c>
@@ -1069,17 +1172,8 @@
       <c r="D12" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="O12" s="4"/>
-      <c r="P12" s="4"/>
-      <c r="Q12" s="4"/>
-      <c r="R12" s="4"/>
-    </row>
-    <row r="13" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="13" spans="1:4" ht="13" x14ac:dyDescent="0.15">
       <c r="A13" s="5" t="s">
         <v>7</v>
       </c>
@@ -1092,20 +1186,8 @@
       <c r="D13" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="N13" s="7"/>
-      <c r="O13" s="3"/>
-      <c r="P13" s="3"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="14" spans="1:4" ht="13" x14ac:dyDescent="0.15">
       <c r="A14" s="6" t="s">
         <v>7</v>
       </c>
@@ -1118,22 +1200,8 @@
       <c r="D14" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="19"/>
-      <c r="M14" s="19"/>
-      <c r="N14" s="4"/>
-      <c r="O14" s="4"/>
-      <c r="P14" s="4"/>
-      <c r="Q14" s="4"/>
-      <c r="R14" s="4"/>
-    </row>
-    <row r="15" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="15" spans="1:4" ht="13" x14ac:dyDescent="0.15">
       <c r="A15" s="5" t="s">
         <v>7</v>
       </c>
@@ -1146,21 +1214,8 @@
       <c r="D15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="7"/>
-      <c r="O15" s="7"/>
-      <c r="Q15" s="3"/>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="16" spans="1:4" ht="13" x14ac:dyDescent="0.15">
       <c r="A16" s="6" t="s">
         <v>7</v>
       </c>
@@ -1173,18 +1228,8 @@
       <c r="D16" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="L16" s="4"/>
-      <c r="N16" s="4"/>
-      <c r="Q16" s="4"/>
-      <c r="R16" s="4"/>
-    </row>
-    <row r="17" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="17" spans="1:4" ht="13" x14ac:dyDescent="0.15">
       <c r="A17" s="5" t="s">
         <v>39</v>
       </c>
@@ -1197,17 +1242,8 @@
       <c r="D17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="N17" s="3"/>
-      <c r="Q17" s="3"/>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="18" spans="1:4" ht="13" x14ac:dyDescent="0.15">
       <c r="A18" s="6" t="s">
         <v>39</v>
       </c>
@@ -1220,21 +1256,8 @@
       <c r="D18" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
-      <c r="K18" s="4"/>
-      <c r="L18" s="4"/>
-      <c r="M18" s="4"/>
-      <c r="N18" s="4"/>
-      <c r="O18" s="4"/>
-      <c r="Q18" s="4"/>
-      <c r="R18" s="4"/>
-    </row>
-    <row r="19" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="19" spans="1:4" ht="13" x14ac:dyDescent="0.15">
       <c r="A19" s="5" t="s">
         <v>39</v>
       </c>
@@ -1247,19 +1270,8 @@
       <c r="D19" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="N19" s="3"/>
-      <c r="Q19" s="3"/>
-      <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="20" spans="1:4" ht="13" x14ac:dyDescent="0.15">
       <c r="A20" s="6" t="s">
         <v>39</v>
       </c>
@@ -1272,20 +1284,8 @@
       <c r="D20" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
-      <c r="K20" s="4"/>
-      <c r="L20" s="4"/>
-      <c r="M20" s="4"/>
-      <c r="N20" s="4"/>
-      <c r="Q20" s="4"/>
-      <c r="R20" s="4"/>
-    </row>
-    <row r="21" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="21" spans="1:4" ht="13" x14ac:dyDescent="0.15">
       <c r="A21" s="5" t="s">
         <v>39</v>
       </c>
@@ -1298,21 +1298,8 @@
       <c r="D21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="3"/>
-      <c r="Q21" s="3"/>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="22" spans="1:4" ht="13" x14ac:dyDescent="0.15">
       <c r="A22" s="6" t="s">
         <v>39</v>
       </c>
@@ -1325,20 +1312,8 @@
       <c r="D22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
-      <c r="K22" s="4"/>
-      <c r="M22" s="4"/>
-      <c r="N22" s="4"/>
-      <c r="O22" s="4"/>
-      <c r="Q22" s="4"/>
-      <c r="R22" s="4"/>
-    </row>
-    <row r="23" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="23" spans="1:4" ht="13" x14ac:dyDescent="0.15">
       <c r="A23" s="5" t="s">
         <v>39</v>
       </c>
@@ -1351,21 +1326,8 @@
       <c r="D23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
-      <c r="M23" s="9"/>
-      <c r="N23" s="3"/>
-      <c r="O23" s="3"/>
-      <c r="Q23" s="3"/>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="24" spans="1:4" ht="13" x14ac:dyDescent="0.15">
       <c r="A24" s="6" t="s">
         <v>39</v>
       </c>
@@ -1378,20 +1340,8 @@
       <c r="D24" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
-      <c r="K24" s="4"/>
-      <c r="L24" s="8"/>
-      <c r="N24" s="4"/>
-      <c r="O24" s="4"/>
-      <c r="Q24" s="4"/>
-      <c r="R24" s="4"/>
-    </row>
-    <row r="25" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="25" spans="1:4" ht="13" x14ac:dyDescent="0.15">
       <c r="A25" s="5" t="s">
         <v>39</v>
       </c>
@@ -1404,20 +1354,8 @@
       <c r="D25" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="N25" s="3"/>
-      <c r="O25" s="3"/>
-      <c r="Q25" s="3"/>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="26" spans="1:4" ht="13" x14ac:dyDescent="0.15">
       <c r="A26" s="6" t="s">
         <v>39</v>
       </c>
@@ -1430,21 +1368,8 @@
       <c r="D26" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="10"/>
-      <c r="K26" s="4"/>
-      <c r="L26" s="4"/>
-      <c r="M26" s="4"/>
-      <c r="N26" s="4"/>
-      <c r="O26" s="4"/>
-      <c r="Q26" s="4"/>
-      <c r="R26" s="4"/>
-    </row>
-    <row r="27" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="27" spans="1:4" ht="13" x14ac:dyDescent="0.15">
       <c r="A27" s="5" t="s">
         <v>39</v>
       </c>
@@ -1457,21 +1382,8 @@
       <c r="D27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-      <c r="M27" s="3"/>
-      <c r="N27" s="3"/>
-      <c r="O27" s="3"/>
-      <c r="Q27" s="3"/>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="28" spans="1:4" ht="13" x14ac:dyDescent="0.15">
       <c r="A28" s="6" t="s">
         <v>39</v>
       </c>
@@ -1484,21 +1396,8 @@
       <c r="D28" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
-      <c r="K28" s="4"/>
-      <c r="L28" s="4"/>
-      <c r="M28" s="4"/>
-      <c r="N28" s="4"/>
-      <c r="O28" s="4"/>
-      <c r="Q28" s="4"/>
-      <c r="R28" s="4"/>
-    </row>
-    <row r="29" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="29" spans="1:4" ht="13" x14ac:dyDescent="0.15">
       <c r="A29" s="5" t="s">
         <v>39</v>
       </c>
@@ -1511,22 +1410,8 @@
       <c r="D29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
-      <c r="J29" s="3"/>
-      <c r="K29" s="3"/>
-      <c r="L29" s="3"/>
-      <c r="M29" s="3"/>
-      <c r="N29" s="3"/>
-      <c r="O29" s="3"/>
-      <c r="P29" s="3"/>
-      <c r="Q29" s="3"/>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="30" spans="1:4" ht="13" x14ac:dyDescent="0.15">
       <c r="A30" s="6" t="s">
         <v>39</v>
       </c>
@@ -1539,22 +1424,8 @@
       <c r="D30" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
-      <c r="I30" s="4"/>
-      <c r="J30" s="4"/>
-      <c r="K30" s="4"/>
-      <c r="L30" s="4"/>
-      <c r="M30" s="4"/>
-      <c r="N30" s="4"/>
-      <c r="O30" s="4"/>
-      <c r="P30" s="4"/>
-      <c r="Q30" s="4"/>
-      <c r="R30" s="4"/>
-    </row>
-    <row r="31" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="31" spans="1:4" ht="13" x14ac:dyDescent="0.15">
       <c r="A31" s="5" t="s">
         <v>39</v>
       </c>
@@ -1567,22 +1438,8 @@
       <c r="D31" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
-      <c r="J31" s="7"/>
-      <c r="K31" s="3"/>
-      <c r="L31" s="7"/>
-      <c r="M31" s="3"/>
-      <c r="N31" s="7"/>
-      <c r="O31" s="3"/>
-      <c r="P31" s="3"/>
-      <c r="Q31" s="3"/>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="32" spans="1:4" ht="13" x14ac:dyDescent="0.15">
       <c r="A32" s="6" t="s">
         <v>70</v>
       </c>
@@ -1595,21 +1452,8 @@
       <c r="D32" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4"/>
-      <c r="J32" s="4"/>
-      <c r="K32" s="4"/>
-      <c r="L32" s="19"/>
-      <c r="M32" s="19"/>
-      <c r="N32" s="4"/>
-      <c r="O32" s="4"/>
-      <c r="P32" s="4"/>
-      <c r="Q32" s="4"/>
-      <c r="R32" s="4"/>
-    </row>
-    <row r="33" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="33" spans="1:4" ht="13" x14ac:dyDescent="0.15">
       <c r="A33" s="5" t="s">
         <v>70</v>
       </c>
@@ -1622,22 +1466,8 @@
       <c r="D33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
-      <c r="J33" s="7"/>
-      <c r="K33" s="7"/>
-      <c r="L33" s="7"/>
-      <c r="M33" s="7"/>
-      <c r="N33" s="7"/>
-      <c r="O33" s="7"/>
-      <c r="P33" s="3"/>
-      <c r="Q33" s="3"/>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="34" spans="1:4" ht="13" x14ac:dyDescent="0.15">
       <c r="A34" s="6" t="s">
         <v>70</v>
       </c>
@@ -1650,19 +1480,8 @@
       <c r="D34" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
-      <c r="L34" s="4"/>
-      <c r="N34" s="4"/>
-      <c r="P34" s="4"/>
-      <c r="Q34" s="4"/>
-      <c r="R34" s="4"/>
-    </row>
-    <row r="35" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="35" spans="1:4" ht="13" x14ac:dyDescent="0.15">
       <c r="A35" s="5" t="s">
         <v>70</v>
       </c>
@@ -1675,19 +1494,8 @@
       <c r="D35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
-      <c r="J35" s="3"/>
-      <c r="L35" s="3"/>
-      <c r="N35" s="3"/>
-      <c r="O35" s="3"/>
-      <c r="Q35" s="3"/>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="36" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="36" spans="1:4" ht="13" x14ac:dyDescent="0.15">
       <c r="A36" s="6" t="s">
         <v>70</v>
       </c>
@@ -1700,21 +1508,8 @@
       <c r="D36" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
-      <c r="K36" s="11"/>
-      <c r="L36" s="4"/>
-      <c r="M36" s="4"/>
-      <c r="N36" s="4"/>
-      <c r="O36" s="4"/>
-      <c r="Q36" s="4"/>
-      <c r="R36" s="4"/>
-    </row>
-    <row r="37" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="37" spans="1:4" ht="13" x14ac:dyDescent="0.15">
       <c r="A37" s="5" t="s">
         <v>70</v>
       </c>
@@ -1727,21 +1522,8 @@
       <c r="D37" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
-      <c r="H37" s="3"/>
-      <c r="I37" s="3"/>
-      <c r="J37" s="3"/>
-      <c r="K37" s="12"/>
-      <c r="L37" s="3"/>
-      <c r="M37" s="3"/>
-      <c r="N37" s="3"/>
-      <c r="O37" s="3"/>
-      <c r="Q37" s="3"/>
-      <c r="R37" s="3"/>
-    </row>
-    <row r="38" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="38" spans="1:4" ht="13" x14ac:dyDescent="0.15">
       <c r="A38" s="6" t="s">
         <v>70</v>
       </c>
@@ -1754,20 +1536,8 @@
       <c r="D38" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-      <c r="J38" s="4"/>
-      <c r="L38" s="4"/>
-      <c r="M38" s="4"/>
-      <c r="N38" s="4"/>
-      <c r="O38" s="4"/>
-      <c r="Q38" s="4"/>
-      <c r="R38" s="4"/>
-    </row>
-    <row r="39" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="39" spans="1:4" ht="13" x14ac:dyDescent="0.15">
       <c r="A39" s="5" t="s">
         <v>70</v>
       </c>
@@ -1780,21 +1550,8 @@
       <c r="D39" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
-      <c r="H39" s="3"/>
-      <c r="I39" s="3"/>
-      <c r="J39" s="3"/>
-      <c r="K39" s="3"/>
-      <c r="L39" s="3"/>
-      <c r="M39" s="3"/>
-      <c r="N39" s="3"/>
-      <c r="O39" s="3"/>
-      <c r="Q39" s="3"/>
-      <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="40" spans="1:4" ht="13" x14ac:dyDescent="0.15">
       <c r="A40" s="6" t="s">
         <v>70</v>
       </c>
@@ -1807,20 +1564,8 @@
       <c r="D40" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="4"/>
-      <c r="J40" s="4"/>
-      <c r="K40" s="4"/>
-      <c r="L40" s="4"/>
-      <c r="N40" s="4"/>
-      <c r="O40" s="4"/>
-      <c r="Q40" s="4"/>
-      <c r="R40" s="4"/>
-    </row>
-    <row r="41" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="41" spans="1:4" ht="13" x14ac:dyDescent="0.15">
       <c r="A41" s="5" t="s">
         <v>70</v>
       </c>
@@ -1833,20 +1578,8 @@
       <c r="D41" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3"/>
-      <c r="H41" s="3"/>
-      <c r="I41" s="3"/>
-      <c r="J41" s="3"/>
-      <c r="K41" s="3"/>
-      <c r="L41" s="3"/>
-      <c r="N41" s="3"/>
-      <c r="O41" s="3"/>
-      <c r="Q41" s="3"/>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="42" spans="1:4" ht="13" x14ac:dyDescent="0.15">
       <c r="A42" s="6" t="s">
         <v>70</v>
       </c>
@@ -1859,20 +1592,8 @@
       <c r="D42" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E42" s="4"/>
-      <c r="F42" s="4"/>
-      <c r="G42" s="4"/>
-      <c r="H42" s="4"/>
-      <c r="I42" s="4"/>
-      <c r="J42" s="4"/>
-      <c r="K42" s="4"/>
-      <c r="L42" s="4"/>
-      <c r="N42" s="4"/>
-      <c r="O42" s="4"/>
-      <c r="Q42" s="4"/>
-      <c r="R42" s="4"/>
-    </row>
-    <row r="43" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="43" spans="1:4" ht="13" x14ac:dyDescent="0.15">
       <c r="A43" s="5" t="s">
         <v>70</v>
       </c>
@@ -1885,20 +1606,8 @@
       <c r="D43" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
-      <c r="G43" s="3"/>
-      <c r="H43" s="3"/>
-      <c r="I43" s="3"/>
-      <c r="J43" s="3"/>
-      <c r="K43" s="3"/>
-      <c r="L43" s="3"/>
-      <c r="N43" s="3"/>
-      <c r="O43" s="3"/>
-      <c r="Q43" s="3"/>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="44" spans="1:4" ht="13" x14ac:dyDescent="0.15">
       <c r="A44" s="6" t="s">
         <v>70</v>
       </c>
@@ -1911,394 +1620,525 @@
       <c r="D44" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E44" s="4"/>
-      <c r="F44" s="4"/>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4"/>
-      <c r="I44" s="4"/>
-      <c r="J44" s="4"/>
-      <c r="K44" s="4"/>
-      <c r="L44" s="4"/>
-      <c r="N44" s="4"/>
-      <c r="Q44" s="4"/>
-      <c r="R44" s="4"/>
-    </row>
-    <row r="45" spans="1:18" ht="13" x14ac:dyDescent="0.15">
-      <c r="A45" s="5" t="s">
+    </row>
+    <row r="45" spans="1:4" ht="13" x14ac:dyDescent="0.15">
+      <c r="A45" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B45" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="C45" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="D45" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E45" s="3"/>
-      <c r="F45" s="3"/>
-      <c r="G45" s="3"/>
-      <c r="H45" s="3"/>
-      <c r="I45" s="3"/>
-      <c r="J45" s="3"/>
-      <c r="K45" s="3"/>
-      <c r="L45" s="3"/>
-      <c r="M45" s="3"/>
-      <c r="N45" s="3"/>
-      <c r="O45" s="3"/>
-      <c r="Q45" s="3"/>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="1:18" ht="13" x14ac:dyDescent="0.15">
-      <c r="A46" s="6" t="s">
+    </row>
+    <row r="46" spans="1:4" ht="13" x14ac:dyDescent="0.15">
+      <c r="A46" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C46" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D46" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E46" s="4"/>
-      <c r="F46" s="4"/>
-      <c r="H46" s="4"/>
-      <c r="I46" s="4"/>
-      <c r="J46" s="4"/>
-      <c r="K46" s="4"/>
-      <c r="L46" s="4"/>
-      <c r="M46" s="4"/>
-      <c r="N46" s="4"/>
-      <c r="O46" s="4"/>
-      <c r="Q46" s="4"/>
-      <c r="R46" s="4"/>
-    </row>
-    <row r="47" spans="1:18" ht="13" x14ac:dyDescent="0.15">
-      <c r="A47" s="5"/>
-      <c r="B47" s="3"/>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3"/>
-      <c r="E47" s="3"/>
-      <c r="F47" s="3"/>
-      <c r="G47" s="3"/>
-      <c r="H47" s="3"/>
-      <c r="I47" s="3"/>
-      <c r="J47" s="3"/>
-      <c r="K47" s="3"/>
-      <c r="L47" s="3"/>
-      <c r="M47" s="3"/>
-      <c r="N47" s="3"/>
-      <c r="Q47" s="3"/>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="1:18" ht="13" x14ac:dyDescent="0.15">
-      <c r="A48" s="6"/>
-      <c r="B48" s="4"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
-      <c r="E48" s="4"/>
-      <c r="F48" s="4"/>
-      <c r="G48" s="4"/>
-      <c r="H48" s="4"/>
-      <c r="I48" s="4"/>
-      <c r="J48" s="4"/>
-      <c r="K48" s="4"/>
-      <c r="L48" s="4"/>
-      <c r="M48" s="4"/>
-      <c r="N48" s="4"/>
-      <c r="Q48" s="4"/>
-      <c r="R48" s="4"/>
-    </row>
-    <row r="49" spans="1:18" ht="13" x14ac:dyDescent="0.15">
-      <c r="A49" s="5"/>
-      <c r="B49" s="3"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
-      <c r="E49" s="3"/>
-      <c r="F49" s="3"/>
-      <c r="G49" s="3"/>
-      <c r="H49" s="3"/>
-      <c r="I49" s="3"/>
-      <c r="J49" s="3"/>
-      <c r="K49" s="3"/>
-      <c r="L49" s="3"/>
-      <c r="M49" s="3"/>
-      <c r="N49" s="3"/>
-      <c r="Q49" s="3"/>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="1:18" ht="13" x14ac:dyDescent="0.15">
-      <c r="A50" s="6"/>
-      <c r="B50" s="4"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4"/>
-      <c r="E50" s="4"/>
-      <c r="F50" s="4"/>
-      <c r="G50" s="4"/>
-      <c r="H50" s="4"/>
-      <c r="I50" s="4"/>
-      <c r="J50" s="10"/>
-      <c r="K50" s="4"/>
-      <c r="L50" s="10"/>
-      <c r="M50" s="4"/>
-      <c r="N50" s="10"/>
-      <c r="Q50" s="4"/>
-      <c r="R50" s="4"/>
-    </row>
-    <row r="51" spans="1:18" ht="13" x14ac:dyDescent="0.15">
-      <c r="A51" s="5"/>
-      <c r="B51" s="3"/>
-      <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
-      <c r="E51" s="3"/>
-      <c r="F51" s="3"/>
-      <c r="G51" s="3"/>
-      <c r="H51" s="3"/>
-      <c r="I51" s="3"/>
-      <c r="J51" s="3"/>
-      <c r="K51" s="3"/>
-      <c r="L51" s="3"/>
-      <c r="M51" s="3"/>
-      <c r="N51" s="3"/>
-      <c r="Q51" s="3"/>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="1:18" ht="13" x14ac:dyDescent="0.15">
-      <c r="A52" s="6"/>
-      <c r="B52" s="4"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="4"/>
-      <c r="E52" s="4"/>
-      <c r="F52" s="4"/>
-      <c r="G52" s="4"/>
-      <c r="H52" s="4"/>
-      <c r="I52" s="4"/>
-      <c r="J52" s="4"/>
-      <c r="K52" s="4"/>
-      <c r="L52" s="4"/>
-      <c r="M52" s="4"/>
-      <c r="N52" s="4"/>
-      <c r="Q52" s="4"/>
-      <c r="R52" s="4"/>
-    </row>
-    <row r="53" spans="1:18" ht="13" x14ac:dyDescent="0.15">
-      <c r="A53" s="5"/>
-      <c r="B53" s="3"/>
-      <c r="C53" s="3"/>
-      <c r="D53" s="3"/>
-      <c r="E53" s="3"/>
-      <c r="F53" s="3"/>
-      <c r="G53" s="3"/>
-      <c r="H53" s="3"/>
-      <c r="I53" s="3"/>
-      <c r="J53" s="3"/>
-      <c r="K53" s="3"/>
-      <c r="L53" s="3"/>
-      <c r="M53" s="3"/>
-      <c r="N53" s="3"/>
-      <c r="O53" s="3"/>
-      <c r="P53" s="3"/>
-      <c r="Q53" s="3"/>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="1:18" ht="13" x14ac:dyDescent="0.15">
-      <c r="A54" s="6"/>
-      <c r="B54" s="4"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="4"/>
-      <c r="E54" s="4"/>
-      <c r="F54" s="4"/>
-      <c r="G54" s="4"/>
-      <c r="H54" s="4"/>
-      <c r="I54" s="4"/>
-      <c r="J54" s="4"/>
-      <c r="K54" s="4"/>
-      <c r="L54" s="4"/>
-      <c r="M54" s="4"/>
-      <c r="N54" s="4"/>
-      <c r="O54" s="4"/>
-      <c r="P54" s="4"/>
-      <c r="Q54" s="4"/>
-      <c r="R54" s="4"/>
-    </row>
-    <row r="55" spans="1:18" ht="13" x14ac:dyDescent="0.15">
-      <c r="A55" s="5"/>
-      <c r="B55" s="3"/>
-      <c r="C55" s="3"/>
-      <c r="D55" s="3"/>
-      <c r="E55" s="3"/>
-      <c r="F55" s="3"/>
-      <c r="G55" s="3"/>
-      <c r="H55" s="3"/>
-      <c r="I55" s="3"/>
-      <c r="J55" s="3"/>
-      <c r="K55" s="3"/>
-      <c r="L55" s="3"/>
-      <c r="M55" s="3"/>
-      <c r="N55" s="3"/>
-      <c r="O55" s="3"/>
-      <c r="P55" s="3"/>
-      <c r="Q55" s="3"/>
-      <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="1:18" ht="13" x14ac:dyDescent="0.15">
-      <c r="A56" s="6"/>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
-      <c r="E56" s="4"/>
-      <c r="F56" s="4"/>
-      <c r="G56" s="4"/>
-      <c r="H56" s="4"/>
-      <c r="I56" s="4"/>
-      <c r="J56" s="4"/>
-      <c r="K56" s="4"/>
-      <c r="L56" s="4"/>
-      <c r="M56" s="4"/>
-      <c r="N56" s="4"/>
-      <c r="O56" s="4"/>
-      <c r="P56" s="4"/>
-      <c r="Q56" s="4"/>
-      <c r="R56" s="4"/>
-    </row>
-    <row r="57" spans="1:18" ht="13" x14ac:dyDescent="0.15">
-      <c r="A57" s="5"/>
-      <c r="B57" s="3"/>
-      <c r="C57" s="3"/>
-      <c r="D57" s="3"/>
-      <c r="E57" s="3"/>
-      <c r="F57" s="3"/>
-      <c r="G57" s="3"/>
-      <c r="H57" s="3"/>
-      <c r="I57" s="3"/>
-      <c r="J57" s="3"/>
-      <c r="K57" s="3"/>
-      <c r="L57" s="3"/>
-      <c r="M57" s="3"/>
-      <c r="N57" s="3"/>
-      <c r="O57" s="3"/>
-      <c r="P57" s="3"/>
-      <c r="Q57" s="3"/>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="1:18" ht="13" x14ac:dyDescent="0.15">
-      <c r="A58" s="6"/>
-      <c r="B58" s="4"/>
-      <c r="C58" s="4"/>
-      <c r="D58" s="4"/>
-      <c r="E58" s="4"/>
-      <c r="F58" s="4"/>
-      <c r="G58" s="4"/>
-      <c r="H58" s="4"/>
-      <c r="I58" s="4"/>
-      <c r="J58" s="4"/>
-      <c r="K58" s="4"/>
-      <c r="L58" s="4"/>
-      <c r="M58" s="4"/>
-      <c r="N58" s="4"/>
-      <c r="O58" s="4"/>
-      <c r="P58" s="4"/>
-      <c r="Q58" s="4"/>
-      <c r="R58" s="4"/>
-    </row>
-    <row r="59" spans="1:18" ht="13" x14ac:dyDescent="0.15">
-      <c r="A59" s="5"/>
-      <c r="B59" s="3"/>
-      <c r="C59" s="3"/>
-      <c r="D59" s="3"/>
-      <c r="E59" s="3"/>
-      <c r="F59" s="3"/>
-      <c r="G59" s="3"/>
-      <c r="H59" s="3"/>
-      <c r="I59" s="3"/>
-      <c r="J59" s="3"/>
-      <c r="K59" s="3"/>
-      <c r="L59" s="3"/>
-      <c r="M59" s="3"/>
-      <c r="N59" s="3"/>
-      <c r="O59" s="3"/>
-      <c r="P59" s="3"/>
-      <c r="Q59" s="3"/>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="1:18" ht="13" x14ac:dyDescent="0.15">
-      <c r="A60" s="6"/>
-      <c r="B60" s="4"/>
-      <c r="C60" s="4"/>
-      <c r="D60" s="4"/>
-      <c r="E60" s="4"/>
-      <c r="F60" s="4"/>
-      <c r="G60" s="4"/>
-      <c r="H60" s="4"/>
-      <c r="I60" s="4"/>
-      <c r="J60" s="4"/>
-      <c r="K60" s="4"/>
-      <c r="L60" s="4"/>
-      <c r="M60" s="4"/>
-      <c r="N60" s="4"/>
-      <c r="O60" s="4"/>
-      <c r="P60" s="4"/>
-      <c r="Q60" s="4"/>
-      <c r="R60" s="4"/>
-    </row>
-    <row r="61" spans="1:18" ht="13" x14ac:dyDescent="0.15">
-      <c r="A61" s="5"/>
-      <c r="B61" s="3"/>
-      <c r="C61" s="3"/>
-      <c r="D61" s="3"/>
-      <c r="E61" s="3"/>
-      <c r="F61" s="3"/>
-      <c r="G61" s="3"/>
-      <c r="H61" s="3"/>
-      <c r="I61" s="3"/>
-      <c r="J61" s="3"/>
-      <c r="K61" s="3"/>
-      <c r="L61" s="3"/>
-      <c r="M61" s="3"/>
-      <c r="N61" s="3"/>
-      <c r="O61" s="3"/>
-      <c r="P61" s="3"/>
-      <c r="Q61" s="3"/>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="1:18" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="63" spans="1:18" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="64" spans="1:18" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="65" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="66" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="67" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="68" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="69" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="70" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="71" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="72" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="73" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="74" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="75" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="76" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="77" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="78" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="79" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="80" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="81" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="82" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="83" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="84" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="85" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="86" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="87" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="88" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="89" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="90" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="91" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="92" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="93" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="94" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="95" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="96" ht="13" x14ac:dyDescent="0.15"/>
+    </row>
+    <row r="47" spans="1:4" ht="13" x14ac:dyDescent="0.15">
+      <c r="A47" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D47" s="4"/>
+    </row>
+    <row r="48" spans="1:4" ht="13" x14ac:dyDescent="0.15">
+      <c r="A48" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D48" s="3"/>
+    </row>
+    <row r="49" spans="1:4" ht="13" x14ac:dyDescent="0.15">
+      <c r="A49" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D49" s="4"/>
+    </row>
+    <row r="50" spans="1:4" ht="13" x14ac:dyDescent="0.15">
+      <c r="A50" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D50" s="3"/>
+    </row>
+    <row r="51" spans="1:4" ht="13" x14ac:dyDescent="0.15">
+      <c r="A51" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D51" s="4"/>
+    </row>
+    <row r="52" spans="1:4" ht="13" x14ac:dyDescent="0.15">
+      <c r="A52" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D52" s="3"/>
+    </row>
+    <row r="53" spans="1:4" ht="13" x14ac:dyDescent="0.15">
+      <c r="A53" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D53" s="4"/>
+    </row>
+    <row r="54" spans="1:4" ht="13" x14ac:dyDescent="0.15">
+      <c r="A54" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D54" s="3"/>
+    </row>
+    <row r="55" spans="1:4" ht="13" x14ac:dyDescent="0.15">
+      <c r="A55" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D55" s="4"/>
+    </row>
+    <row r="56" spans="1:4" ht="13" x14ac:dyDescent="0.15">
+      <c r="A56" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D56" s="3"/>
+    </row>
+    <row r="57" spans="1:4" ht="13" x14ac:dyDescent="0.15">
+      <c r="A57" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D57" s="4"/>
+    </row>
+    <row r="58" spans="1:4" ht="13" x14ac:dyDescent="0.15">
+      <c r="A58" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D58" s="3"/>
+    </row>
+    <row r="59" spans="1:4" ht="13" x14ac:dyDescent="0.15">
+      <c r="A59" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D59" s="4"/>
+    </row>
+    <row r="60" spans="1:4" ht="13" x14ac:dyDescent="0.15">
+      <c r="A60" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D60" s="3"/>
+    </row>
+    <row r="61" spans="1:4" ht="13" x14ac:dyDescent="0.15">
+      <c r="A61" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="D61" s="4"/>
+    </row>
+    <row r="62" spans="1:4" ht="13" x14ac:dyDescent="0.15">
+      <c r="A62" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D62" s="3"/>
+    </row>
+    <row r="63" spans="1:4" ht="13" x14ac:dyDescent="0.15">
+      <c r="A63" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D63" s="4"/>
+    </row>
+    <row r="64" spans="1:4" ht="13" x14ac:dyDescent="0.15">
+      <c r="A64" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D64" s="3"/>
+    </row>
+    <row r="65" spans="1:4" ht="13" x14ac:dyDescent="0.15">
+      <c r="A65" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="D65" s="4"/>
+    </row>
+    <row r="66" spans="1:4" ht="13" x14ac:dyDescent="0.15">
+      <c r="A66" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="D66" s="4"/>
+    </row>
+    <row r="67" spans="1:4" ht="13" x14ac:dyDescent="0.15">
+      <c r="A67" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D67" s="3"/>
+    </row>
+    <row r="68" spans="1:4" ht="13" x14ac:dyDescent="0.15">
+      <c r="A68" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="D68" s="4"/>
+    </row>
+    <row r="69" spans="1:4" ht="13" x14ac:dyDescent="0.15">
+      <c r="A69" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D69" s="3"/>
+    </row>
+    <row r="70" spans="1:4" ht="13" x14ac:dyDescent="0.15">
+      <c r="A70" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="D70" s="4"/>
+    </row>
+    <row r="71" spans="1:4" ht="13" x14ac:dyDescent="0.15">
+      <c r="A71" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D71" s="4"/>
+    </row>
+    <row r="72" spans="1:4" ht="13" x14ac:dyDescent="0.15">
+      <c r="A72" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D72" s="3"/>
+    </row>
+    <row r="73" spans="1:4" ht="13" x14ac:dyDescent="0.15">
+      <c r="A73" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="D73" s="4"/>
+    </row>
+    <row r="74" spans="1:4" ht="13" x14ac:dyDescent="0.15">
+      <c r="A74" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D74" s="3"/>
+    </row>
+    <row r="75" spans="1:4" ht="13" x14ac:dyDescent="0.15">
+      <c r="A75" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="D75" s="4"/>
+    </row>
+    <row r="76" spans="1:4" ht="13" x14ac:dyDescent="0.15">
+      <c r="A76" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="D76" s="4"/>
+    </row>
+    <row r="77" spans="1:4" ht="13" x14ac:dyDescent="0.15">
+      <c r="A77" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D77" s="3"/>
+    </row>
+    <row r="78" spans="1:4" ht="13" x14ac:dyDescent="0.15">
+      <c r="A78" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="D78" s="4"/>
+    </row>
+    <row r="79" spans="1:4" ht="13" x14ac:dyDescent="0.15">
+      <c r="A79" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D79" s="3"/>
+    </row>
+    <row r="80" spans="1:4" ht="13" x14ac:dyDescent="0.15">
+      <c r="A80" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="D80" s="4"/>
+    </row>
+    <row r="81" spans="1:4" ht="13" x14ac:dyDescent="0.15">
+      <c r="A81" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="D81" s="4"/>
+    </row>
+    <row r="82" spans="1:4" ht="13" x14ac:dyDescent="0.15">
+      <c r="A82" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D82" s="3"/>
+    </row>
+    <row r="83" spans="1:4" ht="13" x14ac:dyDescent="0.15">
+      <c r="A83" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D83" s="4"/>
+    </row>
+    <row r="84" spans="1:4" ht="13" x14ac:dyDescent="0.15">
+      <c r="A84" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D84" s="3"/>
+    </row>
+    <row r="85" spans="1:4" ht="13" x14ac:dyDescent="0.15">
+      <c r="A85" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="D85" s="4"/>
+    </row>
+    <row r="86" spans="1:4" ht="13" x14ac:dyDescent="0.15">
+      <c r="A86" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="D86" s="4"/>
+    </row>
+    <row r="87" spans="1:4" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="88" spans="1:4" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="89" spans="1:4" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="90" spans="1:4" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="91" spans="1:4" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="92" spans="1:4" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="93" spans="1:4" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="94" spans="1:4" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="95" spans="1:4" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="96" spans="1:4" ht="13" x14ac:dyDescent="0.15"/>
     <row r="97" ht="13" x14ac:dyDescent="0.15"/>
     <row r="98" ht="13" x14ac:dyDescent="0.15"/>
     <row r="99" ht="13" x14ac:dyDescent="0.15"/>
@@ -3244,14 +3084,11 @@
     <row r="1039" ht="13" x14ac:dyDescent="0.15"/>
     <row r="1040" ht="13" x14ac:dyDescent="0.15"/>
     <row r="1041" ht="13" x14ac:dyDescent="0.15"/>
-    <row r="1042" ht="13" x14ac:dyDescent="0.15"/>
   </sheetData>
-  <autoFilter ref="A1:A1042" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <mergeCells count="2">
-    <mergeCell ref="L14:M14"/>
-    <mergeCell ref="L32:M32"/>
-  </mergeCells>
+  <autoFilter ref="A1:D60" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -3263,2994 +3100,3009 @@
   <dimension ref="A1:R981"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="39.1640625" style="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="255.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="39.1640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="191.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="14"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="8"/>
+      <c r="R1" s="8"/>
     </row>
     <row r="2" spans="1:18" ht="13" x14ac:dyDescent="0.15">
-      <c r="A2" s="16"/>
-      <c r="B2" s="15"/>
+      <c r="A2" s="10"/>
+      <c r="B2" s="9"/>
     </row>
     <row r="3" spans="1:18" ht="98" x14ac:dyDescent="0.15">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="9" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="70" x14ac:dyDescent="0.15">
-      <c r="A4" s="16" t="s">
+    <row r="4" spans="1:18" ht="98" x14ac:dyDescent="0.15">
+      <c r="A4" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="9" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="84" x14ac:dyDescent="0.15">
-      <c r="A5" s="16" t="s">
+    <row r="5" spans="1:18" ht="112" x14ac:dyDescent="0.15">
+      <c r="A5" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="9" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B6" s="15"/>
+    <row r="6" spans="1:18" ht="126" x14ac:dyDescent="0.15">
+      <c r="A6" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="7" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B7" s="15"/>
+      <c r="A7" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="B7" s="9"/>
     </row>
     <row r="8" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B8" s="15"/>
+      <c r="B8" s="9"/>
     </row>
     <row r="9" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="15"/>
+      <c r="B9" s="9"/>
     </row>
     <row r="10" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B10" s="15"/>
+      <c r="B10" s="9"/>
     </row>
     <row r="11" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B11" s="15"/>
+      <c r="B11" s="9"/>
     </row>
     <row r="12" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B12" s="15"/>
+      <c r="B12" s="9"/>
     </row>
     <row r="13" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B13" s="15"/>
+      <c r="B13" s="9"/>
     </row>
     <row r="14" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B14" s="15"/>
+      <c r="B14" s="9"/>
     </row>
     <row r="15" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B15" s="15"/>
+      <c r="B15" s="9"/>
     </row>
     <row r="16" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="15"/>
+      <c r="B16" s="9"/>
     </row>
     <row r="17" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B17" s="15"/>
+      <c r="B17" s="9"/>
     </row>
     <row r="18" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="15"/>
+      <c r="B18" s="9"/>
     </row>
     <row r="19" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B19" s="15"/>
+      <c r="B19" s="9"/>
     </row>
     <row r="20" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B20" s="15"/>
+      <c r="B20" s="9"/>
     </row>
     <row r="21" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B21" s="15"/>
+      <c r="B21" s="9"/>
     </row>
     <row r="22" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B22" s="15"/>
+      <c r="B22" s="9"/>
     </row>
     <row r="23" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B23" s="15"/>
+      <c r="B23" s="9"/>
     </row>
     <row r="24" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B24" s="15"/>
+      <c r="B24" s="9"/>
     </row>
     <row r="25" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B25" s="15"/>
+      <c r="B25" s="9"/>
     </row>
     <row r="26" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B26" s="15"/>
+      <c r="B26" s="9"/>
     </row>
     <row r="27" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B27" s="15"/>
+      <c r="B27" s="9"/>
     </row>
     <row r="28" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B28" s="15"/>
+      <c r="B28" s="9"/>
     </row>
     <row r="29" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B29" s="15"/>
+      <c r="B29" s="9"/>
     </row>
     <row r="30" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B30" s="15"/>
+      <c r="B30" s="9"/>
     </row>
     <row r="31" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B31" s="15"/>
+      <c r="B31" s="9"/>
     </row>
     <row r="32" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B32" s="15"/>
+      <c r="B32" s="9"/>
     </row>
     <row r="33" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B33" s="15"/>
+      <c r="B33" s="9"/>
     </row>
     <row r="34" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B34" s="15"/>
+      <c r="B34" s="9"/>
     </row>
     <row r="35" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B35" s="15"/>
+      <c r="B35" s="9"/>
     </row>
     <row r="36" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="15"/>
+      <c r="B36" s="9"/>
     </row>
     <row r="37" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B37" s="15"/>
+      <c r="B37" s="9"/>
     </row>
     <row r="38" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B38" s="15"/>
+      <c r="B38" s="9"/>
     </row>
     <row r="39" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B39" s="15"/>
+      <c r="B39" s="9"/>
     </row>
     <row r="40" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B40" s="15"/>
+      <c r="B40" s="9"/>
     </row>
     <row r="41" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B41" s="15"/>
+      <c r="B41" s="9"/>
     </row>
     <row r="42" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B42" s="15"/>
+      <c r="B42" s="9"/>
     </row>
     <row r="43" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B43" s="15"/>
+      <c r="B43" s="9"/>
     </row>
     <row r="44" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B44" s="15"/>
+      <c r="B44" s="9"/>
     </row>
     <row r="45" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B45" s="15"/>
+      <c r="B45" s="9"/>
     </row>
     <row r="46" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B46" s="15"/>
+      <c r="B46" s="9"/>
     </row>
     <row r="47" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B47" s="15"/>
+      <c r="B47" s="9"/>
     </row>
     <row r="48" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B48" s="15"/>
+      <c r="B48" s="9"/>
     </row>
     <row r="49" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B49" s="15"/>
+      <c r="B49" s="9"/>
     </row>
     <row r="50" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B50" s="15"/>
+      <c r="B50" s="9"/>
     </row>
     <row r="51" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B51" s="15"/>
+      <c r="B51" s="9"/>
     </row>
     <row r="52" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B52" s="15"/>
+      <c r="B52" s="9"/>
     </row>
     <row r="53" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B53" s="15"/>
+      <c r="B53" s="9"/>
     </row>
     <row r="54" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B54" s="15"/>
+      <c r="B54" s="9"/>
     </row>
     <row r="55" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B55" s="15"/>
+      <c r="B55" s="9"/>
     </row>
     <row r="56" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B56" s="15"/>
+      <c r="B56" s="9"/>
     </row>
     <row r="57" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B57" s="15"/>
+      <c r="B57" s="9"/>
     </row>
     <row r="58" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B58" s="15"/>
+      <c r="B58" s="9"/>
     </row>
     <row r="59" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B59" s="15"/>
+      <c r="B59" s="9"/>
     </row>
     <row r="60" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B60" s="15"/>
+      <c r="B60" s="9"/>
     </row>
     <row r="61" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B61" s="15"/>
+      <c r="B61" s="9"/>
     </row>
     <row r="62" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B62" s="15"/>
+      <c r="B62" s="9"/>
     </row>
     <row r="63" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B63" s="15"/>
+      <c r="B63" s="9"/>
     </row>
     <row r="64" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B64" s="15"/>
+      <c r="B64" s="9"/>
     </row>
     <row r="65" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B65" s="15"/>
+      <c r="B65" s="9"/>
     </row>
     <row r="66" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B66" s="15"/>
+      <c r="B66" s="9"/>
     </row>
     <row r="67" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B67" s="15"/>
+      <c r="B67" s="9"/>
     </row>
     <row r="68" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B68" s="15"/>
+      <c r="B68" s="9"/>
     </row>
     <row r="69" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B69" s="15"/>
+      <c r="B69" s="9"/>
     </row>
     <row r="70" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B70" s="15"/>
+      <c r="B70" s="9"/>
     </row>
     <row r="71" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B71" s="15"/>
+      <c r="B71" s="9"/>
     </row>
     <row r="72" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B72" s="15"/>
+      <c r="B72" s="9"/>
     </row>
     <row r="73" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B73" s="15"/>
+      <c r="B73" s="9"/>
     </row>
     <row r="74" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B74" s="15"/>
+      <c r="B74" s="9"/>
     </row>
     <row r="75" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B75" s="15"/>
+      <c r="B75" s="9"/>
     </row>
     <row r="76" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B76" s="15"/>
+      <c r="B76" s="9"/>
     </row>
     <row r="77" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B77" s="15"/>
+      <c r="B77" s="9"/>
     </row>
     <row r="78" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B78" s="15"/>
+      <c r="B78" s="9"/>
     </row>
     <row r="79" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B79" s="15"/>
+      <c r="B79" s="9"/>
     </row>
     <row r="80" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B80" s="15"/>
+      <c r="B80" s="9"/>
     </row>
     <row r="81" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B81" s="15"/>
+      <c r="B81" s="9"/>
     </row>
     <row r="82" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B82" s="15"/>
+      <c r="B82" s="9"/>
     </row>
     <row r="83" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B83" s="15"/>
+      <c r="B83" s="9"/>
     </row>
     <row r="84" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B84" s="15"/>
+      <c r="B84" s="9"/>
     </row>
     <row r="85" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B85" s="15"/>
+      <c r="B85" s="9"/>
     </row>
     <row r="86" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B86" s="15"/>
+      <c r="B86" s="9"/>
     </row>
     <row r="87" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B87" s="15"/>
+      <c r="B87" s="9"/>
     </row>
     <row r="88" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B88" s="15"/>
+      <c r="B88" s="9"/>
     </row>
     <row r="89" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B89" s="15"/>
+      <c r="B89" s="9"/>
     </row>
     <row r="90" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B90" s="15"/>
+      <c r="B90" s="9"/>
     </row>
     <row r="91" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B91" s="15"/>
+      <c r="B91" s="9"/>
     </row>
     <row r="92" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B92" s="15"/>
+      <c r="B92" s="9"/>
     </row>
     <row r="93" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B93" s="15"/>
+      <c r="B93" s="9"/>
     </row>
     <row r="94" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B94" s="15"/>
+      <c r="B94" s="9"/>
     </row>
     <row r="95" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B95" s="15"/>
+      <c r="B95" s="9"/>
     </row>
     <row r="96" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B96" s="15"/>
+      <c r="B96" s="9"/>
     </row>
     <row r="97" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B97" s="15"/>
+      <c r="B97" s="9"/>
     </row>
     <row r="98" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B98" s="15"/>
+      <c r="B98" s="9"/>
     </row>
     <row r="99" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B99" s="15"/>
+      <c r="B99" s="9"/>
     </row>
     <row r="100" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B100" s="15"/>
+      <c r="B100" s="9"/>
     </row>
     <row r="101" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B101" s="15"/>
+      <c r="B101" s="9"/>
     </row>
     <row r="102" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B102" s="15"/>
+      <c r="B102" s="9"/>
     </row>
     <row r="103" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B103" s="15"/>
+      <c r="B103" s="9"/>
     </row>
     <row r="104" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B104" s="15"/>
+      <c r="B104" s="9"/>
     </row>
     <row r="105" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B105" s="15"/>
+      <c r="B105" s="9"/>
     </row>
     <row r="106" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B106" s="15"/>
+      <c r="B106" s="9"/>
     </row>
     <row r="107" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B107" s="15"/>
+      <c r="B107" s="9"/>
     </row>
     <row r="108" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B108" s="15"/>
+      <c r="B108" s="9"/>
     </row>
     <row r="109" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B109" s="15"/>
+      <c r="B109" s="9"/>
     </row>
     <row r="110" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B110" s="15"/>
+      <c r="B110" s="9"/>
     </row>
     <row r="111" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B111" s="15"/>
+      <c r="B111" s="9"/>
     </row>
     <row r="112" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B112" s="15"/>
+      <c r="B112" s="9"/>
     </row>
     <row r="113" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B113" s="15"/>
+      <c r="B113" s="9"/>
     </row>
     <row r="114" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B114" s="15"/>
+      <c r="B114" s="9"/>
     </row>
     <row r="115" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B115" s="15"/>
+      <c r="B115" s="9"/>
     </row>
     <row r="116" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B116" s="15"/>
+      <c r="B116" s="9"/>
     </row>
     <row r="117" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B117" s="15"/>
+      <c r="B117" s="9"/>
     </row>
     <row r="118" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B118" s="15"/>
+      <c r="B118" s="9"/>
     </row>
     <row r="119" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B119" s="15"/>
+      <c r="B119" s="9"/>
     </row>
     <row r="120" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B120" s="15"/>
+      <c r="B120" s="9"/>
     </row>
     <row r="121" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B121" s="15"/>
+      <c r="B121" s="9"/>
     </row>
     <row r="122" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B122" s="15"/>
+      <c r="B122" s="9"/>
     </row>
     <row r="123" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B123" s="15"/>
+      <c r="B123" s="9"/>
     </row>
     <row r="124" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B124" s="15"/>
+      <c r="B124" s="9"/>
     </row>
     <row r="125" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B125" s="15"/>
+      <c r="B125" s="9"/>
     </row>
     <row r="126" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B126" s="15"/>
+      <c r="B126" s="9"/>
     </row>
     <row r="127" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B127" s="15"/>
+      <c r="B127" s="9"/>
     </row>
     <row r="128" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B128" s="15"/>
+      <c r="B128" s="9"/>
     </row>
     <row r="129" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B129" s="15"/>
+      <c r="B129" s="9"/>
     </row>
     <row r="130" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B130" s="15"/>
+      <c r="B130" s="9"/>
     </row>
     <row r="131" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B131" s="15"/>
+      <c r="B131" s="9"/>
     </row>
     <row r="132" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B132" s="15"/>
+      <c r="B132" s="9"/>
     </row>
     <row r="133" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B133" s="15"/>
+      <c r="B133" s="9"/>
     </row>
     <row r="134" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B134" s="15"/>
+      <c r="B134" s="9"/>
     </row>
     <row r="135" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B135" s="15"/>
+      <c r="B135" s="9"/>
     </row>
     <row r="136" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B136" s="15"/>
+      <c r="B136" s="9"/>
     </row>
     <row r="137" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B137" s="15"/>
+      <c r="B137" s="9"/>
     </row>
     <row r="138" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B138" s="15"/>
+      <c r="B138" s="9"/>
     </row>
     <row r="139" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B139" s="15"/>
+      <c r="B139" s="9"/>
     </row>
     <row r="140" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B140" s="15"/>
+      <c r="B140" s="9"/>
     </row>
     <row r="141" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B141" s="15"/>
+      <c r="B141" s="9"/>
     </row>
     <row r="142" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B142" s="15"/>
+      <c r="B142" s="9"/>
     </row>
     <row r="143" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B143" s="15"/>
+      <c r="B143" s="9"/>
     </row>
     <row r="144" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B144" s="15"/>
+      <c r="B144" s="9"/>
     </row>
     <row r="145" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B145" s="15"/>
+      <c r="B145" s="9"/>
     </row>
     <row r="146" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B146" s="15"/>
+      <c r="B146" s="9"/>
     </row>
     <row r="147" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B147" s="15"/>
+      <c r="B147" s="9"/>
     </row>
     <row r="148" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B148" s="15"/>
+      <c r="B148" s="9"/>
     </row>
     <row r="149" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B149" s="15"/>
+      <c r="B149" s="9"/>
     </row>
     <row r="150" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B150" s="15"/>
+      <c r="B150" s="9"/>
     </row>
     <row r="151" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B151" s="15"/>
+      <c r="B151" s="9"/>
     </row>
     <row r="152" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B152" s="15"/>
+      <c r="B152" s="9"/>
     </row>
     <row r="153" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B153" s="15"/>
+      <c r="B153" s="9"/>
     </row>
     <row r="154" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B154" s="15"/>
+      <c r="B154" s="9"/>
     </row>
     <row r="155" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B155" s="15"/>
+      <c r="B155" s="9"/>
     </row>
     <row r="156" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B156" s="15"/>
+      <c r="B156" s="9"/>
     </row>
     <row r="157" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B157" s="15"/>
+      <c r="B157" s="9"/>
     </row>
     <row r="158" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B158" s="15"/>
+      <c r="B158" s="9"/>
     </row>
     <row r="159" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B159" s="15"/>
+      <c r="B159" s="9"/>
     </row>
     <row r="160" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B160" s="15"/>
+      <c r="B160" s="9"/>
     </row>
     <row r="161" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B161" s="15"/>
+      <c r="B161" s="9"/>
     </row>
     <row r="162" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B162" s="15"/>
+      <c r="B162" s="9"/>
     </row>
     <row r="163" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B163" s="15"/>
+      <c r="B163" s="9"/>
     </row>
     <row r="164" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B164" s="15"/>
+      <c r="B164" s="9"/>
     </row>
     <row r="165" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B165" s="15"/>
+      <c r="B165" s="9"/>
     </row>
     <row r="166" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B166" s="15"/>
+      <c r="B166" s="9"/>
     </row>
     <row r="167" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B167" s="15"/>
+      <c r="B167" s="9"/>
     </row>
     <row r="168" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B168" s="15"/>
+      <c r="B168" s="9"/>
     </row>
     <row r="169" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B169" s="15"/>
+      <c r="B169" s="9"/>
     </row>
     <row r="170" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B170" s="15"/>
+      <c r="B170" s="9"/>
     </row>
     <row r="171" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B171" s="15"/>
+      <c r="B171" s="9"/>
     </row>
     <row r="172" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B172" s="15"/>
+      <c r="B172" s="9"/>
     </row>
     <row r="173" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B173" s="15"/>
+      <c r="B173" s="9"/>
     </row>
     <row r="174" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B174" s="15"/>
+      <c r="B174" s="9"/>
     </row>
     <row r="175" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B175" s="15"/>
+      <c r="B175" s="9"/>
     </row>
     <row r="176" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B176" s="15"/>
+      <c r="B176" s="9"/>
     </row>
     <row r="177" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B177" s="15"/>
+      <c r="B177" s="9"/>
     </row>
     <row r="178" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B178" s="15"/>
+      <c r="B178" s="9"/>
     </row>
     <row r="179" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B179" s="15"/>
+      <c r="B179" s="9"/>
     </row>
     <row r="180" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B180" s="15"/>
+      <c r="B180" s="9"/>
     </row>
     <row r="181" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B181" s="15"/>
+      <c r="B181" s="9"/>
     </row>
     <row r="182" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B182" s="15"/>
+      <c r="B182" s="9"/>
     </row>
     <row r="183" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B183" s="15"/>
+      <c r="B183" s="9"/>
     </row>
     <row r="184" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B184" s="15"/>
+      <c r="B184" s="9"/>
     </row>
     <row r="185" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B185" s="15"/>
+      <c r="B185" s="9"/>
     </row>
     <row r="186" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B186" s="15"/>
+      <c r="B186" s="9"/>
     </row>
     <row r="187" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B187" s="15"/>
+      <c r="B187" s="9"/>
     </row>
     <row r="188" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B188" s="15"/>
+      <c r="B188" s="9"/>
     </row>
     <row r="189" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B189" s="15"/>
+      <c r="B189" s="9"/>
     </row>
     <row r="190" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B190" s="15"/>
+      <c r="B190" s="9"/>
     </row>
     <row r="191" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B191" s="15"/>
+      <c r="B191" s="9"/>
     </row>
     <row r="192" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B192" s="15"/>
+      <c r="B192" s="9"/>
     </row>
     <row r="193" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B193" s="15"/>
+      <c r="B193" s="9"/>
     </row>
     <row r="194" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B194" s="15"/>
+      <c r="B194" s="9"/>
     </row>
     <row r="195" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B195" s="15"/>
+      <c r="B195" s="9"/>
     </row>
     <row r="196" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B196" s="15"/>
+      <c r="B196" s="9"/>
     </row>
     <row r="197" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B197" s="15"/>
+      <c r="B197" s="9"/>
     </row>
     <row r="198" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B198" s="15"/>
+      <c r="B198" s="9"/>
     </row>
     <row r="199" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B199" s="15"/>
+      <c r="B199" s="9"/>
     </row>
     <row r="200" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B200" s="15"/>
+      <c r="B200" s="9"/>
     </row>
     <row r="201" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B201" s="15"/>
+      <c r="B201" s="9"/>
     </row>
     <row r="202" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B202" s="15"/>
+      <c r="B202" s="9"/>
     </row>
     <row r="203" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B203" s="15"/>
+      <c r="B203" s="9"/>
     </row>
     <row r="204" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B204" s="15"/>
+      <c r="B204" s="9"/>
     </row>
     <row r="205" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B205" s="15"/>
+      <c r="B205" s="9"/>
     </row>
     <row r="206" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B206" s="15"/>
+      <c r="B206" s="9"/>
     </row>
     <row r="207" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B207" s="15"/>
+      <c r="B207" s="9"/>
     </row>
     <row r="208" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B208" s="15"/>
+      <c r="B208" s="9"/>
     </row>
     <row r="209" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B209" s="15"/>
+      <c r="B209" s="9"/>
     </row>
     <row r="210" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B210" s="15"/>
+      <c r="B210" s="9"/>
     </row>
     <row r="211" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B211" s="15"/>
+      <c r="B211" s="9"/>
     </row>
     <row r="212" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B212" s="15"/>
+      <c r="B212" s="9"/>
     </row>
     <row r="213" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B213" s="15"/>
+      <c r="B213" s="9"/>
     </row>
     <row r="214" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B214" s="15"/>
+      <c r="B214" s="9"/>
     </row>
     <row r="215" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B215" s="15"/>
+      <c r="B215" s="9"/>
     </row>
     <row r="216" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B216" s="15"/>
+      <c r="B216" s="9"/>
     </row>
     <row r="217" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B217" s="15"/>
+      <c r="B217" s="9"/>
     </row>
     <row r="218" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B218" s="15"/>
+      <c r="B218" s="9"/>
     </row>
     <row r="219" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B219" s="15"/>
+      <c r="B219" s="9"/>
     </row>
     <row r="220" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B220" s="15"/>
+      <c r="B220" s="9"/>
     </row>
     <row r="221" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B221" s="15"/>
+      <c r="B221" s="9"/>
     </row>
     <row r="222" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B222" s="15"/>
+      <c r="B222" s="9"/>
     </row>
     <row r="223" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B223" s="15"/>
+      <c r="B223" s="9"/>
     </row>
     <row r="224" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B224" s="15"/>
+      <c r="B224" s="9"/>
     </row>
     <row r="225" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B225" s="15"/>
+      <c r="B225" s="9"/>
     </row>
     <row r="226" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B226" s="15"/>
+      <c r="B226" s="9"/>
     </row>
     <row r="227" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B227" s="15"/>
+      <c r="B227" s="9"/>
     </row>
     <row r="228" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B228" s="15"/>
+      <c r="B228" s="9"/>
     </row>
     <row r="229" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B229" s="15"/>
+      <c r="B229" s="9"/>
     </row>
     <row r="230" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B230" s="15"/>
+      <c r="B230" s="9"/>
     </row>
     <row r="231" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B231" s="15"/>
+      <c r="B231" s="9"/>
     </row>
     <row r="232" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B232" s="15"/>
+      <c r="B232" s="9"/>
     </row>
     <row r="233" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B233" s="15"/>
+      <c r="B233" s="9"/>
     </row>
     <row r="234" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B234" s="15"/>
+      <c r="B234" s="9"/>
     </row>
     <row r="235" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B235" s="15"/>
+      <c r="B235" s="9"/>
     </row>
     <row r="236" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B236" s="15"/>
+      <c r="B236" s="9"/>
     </row>
     <row r="237" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B237" s="15"/>
+      <c r="B237" s="9"/>
     </row>
     <row r="238" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B238" s="15"/>
+      <c r="B238" s="9"/>
     </row>
     <row r="239" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B239" s="15"/>
+      <c r="B239" s="9"/>
     </row>
     <row r="240" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B240" s="15"/>
+      <c r="B240" s="9"/>
     </row>
     <row r="241" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B241" s="15"/>
+      <c r="B241" s="9"/>
     </row>
     <row r="242" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B242" s="15"/>
+      <c r="B242" s="9"/>
     </row>
     <row r="243" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B243" s="15"/>
+      <c r="B243" s="9"/>
     </row>
     <row r="244" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B244" s="15"/>
+      <c r="B244" s="9"/>
     </row>
     <row r="245" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B245" s="15"/>
+      <c r="B245" s="9"/>
     </row>
     <row r="246" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B246" s="15"/>
+      <c r="B246" s="9"/>
     </row>
     <row r="247" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B247" s="15"/>
+      <c r="B247" s="9"/>
     </row>
     <row r="248" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B248" s="15"/>
+      <c r="B248" s="9"/>
     </row>
     <row r="249" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B249" s="15"/>
+      <c r="B249" s="9"/>
     </row>
     <row r="250" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B250" s="15"/>
+      <c r="B250" s="9"/>
     </row>
     <row r="251" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B251" s="15"/>
+      <c r="B251" s="9"/>
     </row>
     <row r="252" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B252" s="15"/>
+      <c r="B252" s="9"/>
     </row>
     <row r="253" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B253" s="15"/>
+      <c r="B253" s="9"/>
     </row>
     <row r="254" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B254" s="15"/>
+      <c r="B254" s="9"/>
     </row>
     <row r="255" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B255" s="15"/>
+      <c r="B255" s="9"/>
     </row>
     <row r="256" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B256" s="15"/>
+      <c r="B256" s="9"/>
     </row>
     <row r="257" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B257" s="15"/>
+      <c r="B257" s="9"/>
     </row>
     <row r="258" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B258" s="15"/>
+      <c r="B258" s="9"/>
     </row>
     <row r="259" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B259" s="15"/>
+      <c r="B259" s="9"/>
     </row>
     <row r="260" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B260" s="15"/>
+      <c r="B260" s="9"/>
     </row>
     <row r="261" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B261" s="15"/>
+      <c r="B261" s="9"/>
     </row>
     <row r="262" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B262" s="15"/>
+      <c r="B262" s="9"/>
     </row>
     <row r="263" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B263" s="15"/>
+      <c r="B263" s="9"/>
     </row>
     <row r="264" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B264" s="15"/>
+      <c r="B264" s="9"/>
     </row>
     <row r="265" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B265" s="15"/>
+      <c r="B265" s="9"/>
     </row>
     <row r="266" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B266" s="15"/>
+      <c r="B266" s="9"/>
     </row>
     <row r="267" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B267" s="15"/>
+      <c r="B267" s="9"/>
     </row>
     <row r="268" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B268" s="15"/>
+      <c r="B268" s="9"/>
     </row>
     <row r="269" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B269" s="15"/>
+      <c r="B269" s="9"/>
     </row>
     <row r="270" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B270" s="15"/>
+      <c r="B270" s="9"/>
     </row>
     <row r="271" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B271" s="15"/>
+      <c r="B271" s="9"/>
     </row>
     <row r="272" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B272" s="15"/>
+      <c r="B272" s="9"/>
     </row>
     <row r="273" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B273" s="15"/>
+      <c r="B273" s="9"/>
     </row>
     <row r="274" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B274" s="15"/>
+      <c r="B274" s="9"/>
     </row>
     <row r="275" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B275" s="15"/>
+      <c r="B275" s="9"/>
     </row>
     <row r="276" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B276" s="15"/>
+      <c r="B276" s="9"/>
     </row>
     <row r="277" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B277" s="15"/>
+      <c r="B277" s="9"/>
     </row>
     <row r="278" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B278" s="15"/>
+      <c r="B278" s="9"/>
     </row>
     <row r="279" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B279" s="15"/>
+      <c r="B279" s="9"/>
     </row>
     <row r="280" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B280" s="15"/>
+      <c r="B280" s="9"/>
     </row>
     <row r="281" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B281" s="15"/>
+      <c r="B281" s="9"/>
     </row>
     <row r="282" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B282" s="15"/>
+      <c r="B282" s="9"/>
     </row>
     <row r="283" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B283" s="15"/>
+      <c r="B283" s="9"/>
     </row>
     <row r="284" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B284" s="15"/>
+      <c r="B284" s="9"/>
     </row>
     <row r="285" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B285" s="15"/>
+      <c r="B285" s="9"/>
     </row>
     <row r="286" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B286" s="15"/>
+      <c r="B286" s="9"/>
     </row>
     <row r="287" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B287" s="15"/>
+      <c r="B287" s="9"/>
     </row>
     <row r="288" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B288" s="15"/>
+      <c r="B288" s="9"/>
     </row>
     <row r="289" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B289" s="15"/>
+      <c r="B289" s="9"/>
     </row>
     <row r="290" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B290" s="15"/>
+      <c r="B290" s="9"/>
     </row>
     <row r="291" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B291" s="15"/>
+      <c r="B291" s="9"/>
     </row>
     <row r="292" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B292" s="15"/>
+      <c r="B292" s="9"/>
     </row>
     <row r="293" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B293" s="15"/>
+      <c r="B293" s="9"/>
     </row>
     <row r="294" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B294" s="15"/>
+      <c r="B294" s="9"/>
     </row>
     <row r="295" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B295" s="15"/>
+      <c r="B295" s="9"/>
     </row>
     <row r="296" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B296" s="15"/>
+      <c r="B296" s="9"/>
     </row>
     <row r="297" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B297" s="15"/>
+      <c r="B297" s="9"/>
     </row>
     <row r="298" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B298" s="15"/>
+      <c r="B298" s="9"/>
     </row>
     <row r="299" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B299" s="15"/>
+      <c r="B299" s="9"/>
     </row>
     <row r="300" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B300" s="15"/>
+      <c r="B300" s="9"/>
     </row>
     <row r="301" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B301" s="15"/>
+      <c r="B301" s="9"/>
     </row>
     <row r="302" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B302" s="15"/>
+      <c r="B302" s="9"/>
     </row>
     <row r="303" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B303" s="15"/>
+      <c r="B303" s="9"/>
     </row>
     <row r="304" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B304" s="15"/>
+      <c r="B304" s="9"/>
     </row>
     <row r="305" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B305" s="15"/>
+      <c r="B305" s="9"/>
     </row>
     <row r="306" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B306" s="15"/>
+      <c r="B306" s="9"/>
     </row>
     <row r="307" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B307" s="15"/>
+      <c r="B307" s="9"/>
     </row>
     <row r="308" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B308" s="15"/>
+      <c r="B308" s="9"/>
     </row>
     <row r="309" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B309" s="15"/>
+      <c r="B309" s="9"/>
     </row>
     <row r="310" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B310" s="15"/>
+      <c r="B310" s="9"/>
     </row>
     <row r="311" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B311" s="15"/>
+      <c r="B311" s="9"/>
     </row>
     <row r="312" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B312" s="15"/>
+      <c r="B312" s="9"/>
     </row>
     <row r="313" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B313" s="15"/>
+      <c r="B313" s="9"/>
     </row>
     <row r="314" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B314" s="15"/>
+      <c r="B314" s="9"/>
     </row>
     <row r="315" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B315" s="15"/>
+      <c r="B315" s="9"/>
     </row>
     <row r="316" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B316" s="15"/>
+      <c r="B316" s="9"/>
     </row>
     <row r="317" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B317" s="15"/>
+      <c r="B317" s="9"/>
     </row>
     <row r="318" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B318" s="15"/>
+      <c r="B318" s="9"/>
     </row>
     <row r="319" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B319" s="15"/>
+      <c r="B319" s="9"/>
     </row>
     <row r="320" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B320" s="15"/>
+      <c r="B320" s="9"/>
     </row>
     <row r="321" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B321" s="15"/>
+      <c r="B321" s="9"/>
     </row>
     <row r="322" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B322" s="15"/>
+      <c r="B322" s="9"/>
     </row>
     <row r="323" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B323" s="15"/>
+      <c r="B323" s="9"/>
     </row>
     <row r="324" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B324" s="15"/>
+      <c r="B324" s="9"/>
     </row>
     <row r="325" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B325" s="15"/>
+      <c r="B325" s="9"/>
     </row>
     <row r="326" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B326" s="15"/>
+      <c r="B326" s="9"/>
     </row>
     <row r="327" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B327" s="15"/>
+      <c r="B327" s="9"/>
     </row>
     <row r="328" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B328" s="15"/>
+      <c r="B328" s="9"/>
     </row>
     <row r="329" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B329" s="15"/>
+      <c r="B329" s="9"/>
     </row>
     <row r="330" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B330" s="15"/>
+      <c r="B330" s="9"/>
     </row>
     <row r="331" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B331" s="15"/>
+      <c r="B331" s="9"/>
     </row>
     <row r="332" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B332" s="15"/>
+      <c r="B332" s="9"/>
     </row>
     <row r="333" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B333" s="15"/>
+      <c r="B333" s="9"/>
     </row>
     <row r="334" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B334" s="15"/>
+      <c r="B334" s="9"/>
     </row>
     <row r="335" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B335" s="15"/>
+      <c r="B335" s="9"/>
     </row>
     <row r="336" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B336" s="15"/>
+      <c r="B336" s="9"/>
     </row>
     <row r="337" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B337" s="15"/>
+      <c r="B337" s="9"/>
     </row>
     <row r="338" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B338" s="15"/>
+      <c r="B338" s="9"/>
     </row>
     <row r="339" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B339" s="15"/>
+      <c r="B339" s="9"/>
     </row>
     <row r="340" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B340" s="15"/>
+      <c r="B340" s="9"/>
     </row>
     <row r="341" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B341" s="15"/>
+      <c r="B341" s="9"/>
     </row>
     <row r="342" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B342" s="15"/>
+      <c r="B342" s="9"/>
     </row>
     <row r="343" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B343" s="15"/>
+      <c r="B343" s="9"/>
     </row>
     <row r="344" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B344" s="15"/>
+      <c r="B344" s="9"/>
     </row>
     <row r="345" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B345" s="15"/>
+      <c r="B345" s="9"/>
     </row>
     <row r="346" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B346" s="15"/>
+      <c r="B346" s="9"/>
     </row>
     <row r="347" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B347" s="15"/>
+      <c r="B347" s="9"/>
     </row>
     <row r="348" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B348" s="15"/>
+      <c r="B348" s="9"/>
     </row>
     <row r="349" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B349" s="15"/>
+      <c r="B349" s="9"/>
     </row>
     <row r="350" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B350" s="15"/>
+      <c r="B350" s="9"/>
     </row>
     <row r="351" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B351" s="15"/>
+      <c r="B351" s="9"/>
     </row>
     <row r="352" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B352" s="15"/>
+      <c r="B352" s="9"/>
     </row>
     <row r="353" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B353" s="15"/>
+      <c r="B353" s="9"/>
     </row>
     <row r="354" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B354" s="15"/>
+      <c r="B354" s="9"/>
     </row>
     <row r="355" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B355" s="15"/>
+      <c r="B355" s="9"/>
     </row>
     <row r="356" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B356" s="15"/>
+      <c r="B356" s="9"/>
     </row>
     <row r="357" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B357" s="15"/>
+      <c r="B357" s="9"/>
     </row>
     <row r="358" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B358" s="15"/>
+      <c r="B358" s="9"/>
     </row>
     <row r="359" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B359" s="15"/>
+      <c r="B359" s="9"/>
     </row>
     <row r="360" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B360" s="15"/>
+      <c r="B360" s="9"/>
     </row>
     <row r="361" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B361" s="15"/>
+      <c r="B361" s="9"/>
     </row>
     <row r="362" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B362" s="15"/>
+      <c r="B362" s="9"/>
     </row>
     <row r="363" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B363" s="15"/>
+      <c r="B363" s="9"/>
     </row>
     <row r="364" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B364" s="15"/>
+      <c r="B364" s="9"/>
     </row>
     <row r="365" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B365" s="15"/>
+      <c r="B365" s="9"/>
     </row>
     <row r="366" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B366" s="15"/>
+      <c r="B366" s="9"/>
     </row>
     <row r="367" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B367" s="15"/>
+      <c r="B367" s="9"/>
     </row>
     <row r="368" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B368" s="15"/>
+      <c r="B368" s="9"/>
     </row>
     <row r="369" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B369" s="15"/>
+      <c r="B369" s="9"/>
     </row>
     <row r="370" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B370" s="15"/>
+      <c r="B370" s="9"/>
     </row>
     <row r="371" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B371" s="15"/>
+      <c r="B371" s="9"/>
     </row>
     <row r="372" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B372" s="15"/>
+      <c r="B372" s="9"/>
     </row>
     <row r="373" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B373" s="15"/>
+      <c r="B373" s="9"/>
     </row>
     <row r="374" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B374" s="15"/>
+      <c r="B374" s="9"/>
     </row>
     <row r="375" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B375" s="15"/>
+      <c r="B375" s="9"/>
     </row>
     <row r="376" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B376" s="15"/>
+      <c r="B376" s="9"/>
     </row>
     <row r="377" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B377" s="15"/>
+      <c r="B377" s="9"/>
     </row>
     <row r="378" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B378" s="15"/>
+      <c r="B378" s="9"/>
     </row>
     <row r="379" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B379" s="15"/>
+      <c r="B379" s="9"/>
     </row>
     <row r="380" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B380" s="15"/>
+      <c r="B380" s="9"/>
     </row>
     <row r="381" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B381" s="15"/>
+      <c r="B381" s="9"/>
     </row>
     <row r="382" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B382" s="15"/>
+      <c r="B382" s="9"/>
     </row>
     <row r="383" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B383" s="15"/>
+      <c r="B383" s="9"/>
     </row>
     <row r="384" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B384" s="15"/>
+      <c r="B384" s="9"/>
     </row>
     <row r="385" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B385" s="15"/>
+      <c r="B385" s="9"/>
     </row>
     <row r="386" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B386" s="15"/>
+      <c r="B386" s="9"/>
     </row>
     <row r="387" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B387" s="15"/>
+      <c r="B387" s="9"/>
     </row>
     <row r="388" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B388" s="15"/>
+      <c r="B388" s="9"/>
     </row>
     <row r="389" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B389" s="15"/>
+      <c r="B389" s="9"/>
     </row>
     <row r="390" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B390" s="15"/>
+      <c r="B390" s="9"/>
     </row>
     <row r="391" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B391" s="15"/>
+      <c r="B391" s="9"/>
     </row>
     <row r="392" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B392" s="15"/>
+      <c r="B392" s="9"/>
     </row>
     <row r="393" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B393" s="15"/>
+      <c r="B393" s="9"/>
     </row>
     <row r="394" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B394" s="15"/>
+      <c r="B394" s="9"/>
     </row>
     <row r="395" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B395" s="15"/>
+      <c r="B395" s="9"/>
     </row>
     <row r="396" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B396" s="15"/>
+      <c r="B396" s="9"/>
     </row>
     <row r="397" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B397" s="15"/>
+      <c r="B397" s="9"/>
     </row>
     <row r="398" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B398" s="15"/>
+      <c r="B398" s="9"/>
     </row>
     <row r="399" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B399" s="15"/>
+      <c r="B399" s="9"/>
     </row>
     <row r="400" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B400" s="15"/>
+      <c r="B400" s="9"/>
     </row>
     <row r="401" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B401" s="15"/>
+      <c r="B401" s="9"/>
     </row>
     <row r="402" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B402" s="15"/>
+      <c r="B402" s="9"/>
     </row>
     <row r="403" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B403" s="15"/>
+      <c r="B403" s="9"/>
     </row>
     <row r="404" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B404" s="15"/>
+      <c r="B404" s="9"/>
     </row>
     <row r="405" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B405" s="15"/>
+      <c r="B405" s="9"/>
     </row>
     <row r="406" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B406" s="15"/>
+      <c r="B406" s="9"/>
     </row>
     <row r="407" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B407" s="15"/>
+      <c r="B407" s="9"/>
     </row>
     <row r="408" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B408" s="15"/>
+      <c r="B408" s="9"/>
     </row>
     <row r="409" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B409" s="15"/>
+      <c r="B409" s="9"/>
     </row>
     <row r="410" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B410" s="15"/>
+      <c r="B410" s="9"/>
     </row>
     <row r="411" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B411" s="15"/>
+      <c r="B411" s="9"/>
     </row>
     <row r="412" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B412" s="15"/>
+      <c r="B412" s="9"/>
     </row>
     <row r="413" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B413" s="15"/>
+      <c r="B413" s="9"/>
     </row>
     <row r="414" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B414" s="15"/>
+      <c r="B414" s="9"/>
     </row>
     <row r="415" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B415" s="15"/>
+      <c r="B415" s="9"/>
     </row>
     <row r="416" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B416" s="15"/>
+      <c r="B416" s="9"/>
     </row>
     <row r="417" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B417" s="15"/>
+      <c r="B417" s="9"/>
     </row>
     <row r="418" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B418" s="15"/>
+      <c r="B418" s="9"/>
     </row>
     <row r="419" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B419" s="15"/>
+      <c r="B419" s="9"/>
     </row>
     <row r="420" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B420" s="15"/>
+      <c r="B420" s="9"/>
     </row>
     <row r="421" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B421" s="15"/>
+      <c r="B421" s="9"/>
     </row>
     <row r="422" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B422" s="15"/>
+      <c r="B422" s="9"/>
     </row>
     <row r="423" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B423" s="15"/>
+      <c r="B423" s="9"/>
     </row>
     <row r="424" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B424" s="15"/>
+      <c r="B424" s="9"/>
     </row>
     <row r="425" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B425" s="15"/>
+      <c r="B425" s="9"/>
     </row>
     <row r="426" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B426" s="15"/>
+      <c r="B426" s="9"/>
     </row>
     <row r="427" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B427" s="15"/>
+      <c r="B427" s="9"/>
     </row>
     <row r="428" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B428" s="15"/>
+      <c r="B428" s="9"/>
     </row>
     <row r="429" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B429" s="15"/>
+      <c r="B429" s="9"/>
     </row>
     <row r="430" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B430" s="15"/>
+      <c r="B430" s="9"/>
     </row>
     <row r="431" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B431" s="15"/>
+      <c r="B431" s="9"/>
     </row>
     <row r="432" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B432" s="15"/>
+      <c r="B432" s="9"/>
     </row>
     <row r="433" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B433" s="15"/>
+      <c r="B433" s="9"/>
     </row>
     <row r="434" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B434" s="15"/>
+      <c r="B434" s="9"/>
     </row>
     <row r="435" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B435" s="15"/>
+      <c r="B435" s="9"/>
     </row>
     <row r="436" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B436" s="15"/>
+      <c r="B436" s="9"/>
     </row>
     <row r="437" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B437" s="15"/>
+      <c r="B437" s="9"/>
     </row>
     <row r="438" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B438" s="15"/>
+      <c r="B438" s="9"/>
     </row>
     <row r="439" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B439" s="15"/>
+      <c r="B439" s="9"/>
     </row>
     <row r="440" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B440" s="15"/>
+      <c r="B440" s="9"/>
     </row>
     <row r="441" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B441" s="15"/>
+      <c r="B441" s="9"/>
     </row>
     <row r="442" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B442" s="15"/>
+      <c r="B442" s="9"/>
     </row>
     <row r="443" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B443" s="15"/>
+      <c r="B443" s="9"/>
     </row>
     <row r="444" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B444" s="15"/>
+      <c r="B444" s="9"/>
     </row>
     <row r="445" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B445" s="15"/>
+      <c r="B445" s="9"/>
     </row>
     <row r="446" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B446" s="15"/>
+      <c r="B446" s="9"/>
     </row>
     <row r="447" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B447" s="15"/>
+      <c r="B447" s="9"/>
     </row>
     <row r="448" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B448" s="15"/>
+      <c r="B448" s="9"/>
     </row>
     <row r="449" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B449" s="15"/>
+      <c r="B449" s="9"/>
     </row>
     <row r="450" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B450" s="15"/>
+      <c r="B450" s="9"/>
     </row>
     <row r="451" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B451" s="15"/>
+      <c r="B451" s="9"/>
     </row>
     <row r="452" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B452" s="15"/>
+      <c r="B452" s="9"/>
     </row>
     <row r="453" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B453" s="15"/>
+      <c r="B453" s="9"/>
     </row>
     <row r="454" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B454" s="15"/>
+      <c r="B454" s="9"/>
     </row>
     <row r="455" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B455" s="15"/>
+      <c r="B455" s="9"/>
     </row>
     <row r="456" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B456" s="15"/>
+      <c r="B456" s="9"/>
     </row>
     <row r="457" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B457" s="15"/>
+      <c r="B457" s="9"/>
     </row>
     <row r="458" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B458" s="15"/>
+      <c r="B458" s="9"/>
     </row>
     <row r="459" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B459" s="15"/>
+      <c r="B459" s="9"/>
     </row>
     <row r="460" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B460" s="15"/>
+      <c r="B460" s="9"/>
     </row>
     <row r="461" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B461" s="15"/>
+      <c r="B461" s="9"/>
     </row>
     <row r="462" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B462" s="15"/>
+      <c r="B462" s="9"/>
     </row>
     <row r="463" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B463" s="15"/>
+      <c r="B463" s="9"/>
     </row>
     <row r="464" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B464" s="15"/>
+      <c r="B464" s="9"/>
     </row>
     <row r="465" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B465" s="15"/>
+      <c r="B465" s="9"/>
     </row>
     <row r="466" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B466" s="15"/>
+      <c r="B466" s="9"/>
     </row>
     <row r="467" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B467" s="15"/>
+      <c r="B467" s="9"/>
     </row>
     <row r="468" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B468" s="15"/>
+      <c r="B468" s="9"/>
     </row>
     <row r="469" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B469" s="15"/>
+      <c r="B469" s="9"/>
     </row>
     <row r="470" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B470" s="15"/>
+      <c r="B470" s="9"/>
     </row>
     <row r="471" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B471" s="15"/>
+      <c r="B471" s="9"/>
     </row>
     <row r="472" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B472" s="15"/>
+      <c r="B472" s="9"/>
     </row>
     <row r="473" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B473" s="15"/>
+      <c r="B473" s="9"/>
     </row>
     <row r="474" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B474" s="15"/>
+      <c r="B474" s="9"/>
     </row>
     <row r="475" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B475" s="15"/>
+      <c r="B475" s="9"/>
     </row>
     <row r="476" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B476" s="15"/>
+      <c r="B476" s="9"/>
     </row>
     <row r="477" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B477" s="15"/>
+      <c r="B477" s="9"/>
     </row>
     <row r="478" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B478" s="15"/>
+      <c r="B478" s="9"/>
     </row>
     <row r="479" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B479" s="15"/>
+      <c r="B479" s="9"/>
     </row>
     <row r="480" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B480" s="15"/>
+      <c r="B480" s="9"/>
     </row>
     <row r="481" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B481" s="15"/>
+      <c r="B481" s="9"/>
     </row>
     <row r="482" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B482" s="15"/>
+      <c r="B482" s="9"/>
     </row>
     <row r="483" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B483" s="15"/>
+      <c r="B483" s="9"/>
     </row>
     <row r="484" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B484" s="15"/>
+      <c r="B484" s="9"/>
     </row>
     <row r="485" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B485" s="15"/>
+      <c r="B485" s="9"/>
     </row>
     <row r="486" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B486" s="15"/>
+      <c r="B486" s="9"/>
     </row>
     <row r="487" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B487" s="15"/>
+      <c r="B487" s="9"/>
     </row>
     <row r="488" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B488" s="15"/>
+      <c r="B488" s="9"/>
     </row>
     <row r="489" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B489" s="15"/>
+      <c r="B489" s="9"/>
     </row>
     <row r="490" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B490" s="15"/>
+      <c r="B490" s="9"/>
     </row>
     <row r="491" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B491" s="15"/>
+      <c r="B491" s="9"/>
     </row>
     <row r="492" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B492" s="15"/>
+      <c r="B492" s="9"/>
     </row>
     <row r="493" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B493" s="15"/>
+      <c r="B493" s="9"/>
     </row>
     <row r="494" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B494" s="15"/>
+      <c r="B494" s="9"/>
     </row>
     <row r="495" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B495" s="15"/>
+      <c r="B495" s="9"/>
     </row>
     <row r="496" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B496" s="15"/>
+      <c r="B496" s="9"/>
     </row>
     <row r="497" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B497" s="15"/>
+      <c r="B497" s="9"/>
     </row>
     <row r="498" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B498" s="15"/>
+      <c r="B498" s="9"/>
     </row>
     <row r="499" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B499" s="15"/>
+      <c r="B499" s="9"/>
     </row>
     <row r="500" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B500" s="15"/>
+      <c r="B500" s="9"/>
     </row>
     <row r="501" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B501" s="15"/>
+      <c r="B501" s="9"/>
     </row>
     <row r="502" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B502" s="15"/>
+      <c r="B502" s="9"/>
     </row>
     <row r="503" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B503" s="15"/>
+      <c r="B503" s="9"/>
     </row>
     <row r="504" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B504" s="15"/>
+      <c r="B504" s="9"/>
     </row>
     <row r="505" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B505" s="15"/>
+      <c r="B505" s="9"/>
     </row>
     <row r="506" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B506" s="15"/>
+      <c r="B506" s="9"/>
     </row>
     <row r="507" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B507" s="15"/>
+      <c r="B507" s="9"/>
     </row>
     <row r="508" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B508" s="15"/>
+      <c r="B508" s="9"/>
     </row>
     <row r="509" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B509" s="15"/>
+      <c r="B509" s="9"/>
     </row>
     <row r="510" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B510" s="15"/>
+      <c r="B510" s="9"/>
     </row>
     <row r="511" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B511" s="15"/>
+      <c r="B511" s="9"/>
     </row>
     <row r="512" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B512" s="15"/>
+      <c r="B512" s="9"/>
     </row>
     <row r="513" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B513" s="15"/>
+      <c r="B513" s="9"/>
     </row>
     <row r="514" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B514" s="15"/>
+      <c r="B514" s="9"/>
     </row>
     <row r="515" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B515" s="15"/>
+      <c r="B515" s="9"/>
     </row>
     <row r="516" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B516" s="15"/>
+      <c r="B516" s="9"/>
     </row>
     <row r="517" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B517" s="15"/>
+      <c r="B517" s="9"/>
     </row>
     <row r="518" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B518" s="15"/>
+      <c r="B518" s="9"/>
     </row>
     <row r="519" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B519" s="15"/>
+      <c r="B519" s="9"/>
     </row>
     <row r="520" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B520" s="15"/>
+      <c r="B520" s="9"/>
     </row>
     <row r="521" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B521" s="15"/>
+      <c r="B521" s="9"/>
     </row>
     <row r="522" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B522" s="15"/>
+      <c r="B522" s="9"/>
     </row>
     <row r="523" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B523" s="15"/>
+      <c r="B523" s="9"/>
     </row>
     <row r="524" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B524" s="15"/>
+      <c r="B524" s="9"/>
     </row>
     <row r="525" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B525" s="15"/>
+      <c r="B525" s="9"/>
     </row>
     <row r="526" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B526" s="15"/>
+      <c r="B526" s="9"/>
     </row>
     <row r="527" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B527" s="15"/>
+      <c r="B527" s="9"/>
     </row>
     <row r="528" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B528" s="15"/>
+      <c r="B528" s="9"/>
     </row>
     <row r="529" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B529" s="15"/>
+      <c r="B529" s="9"/>
     </row>
     <row r="530" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B530" s="15"/>
+      <c r="B530" s="9"/>
     </row>
     <row r="531" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B531" s="15"/>
+      <c r="B531" s="9"/>
     </row>
     <row r="532" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B532" s="15"/>
+      <c r="B532" s="9"/>
     </row>
     <row r="533" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B533" s="15"/>
+      <c r="B533" s="9"/>
     </row>
     <row r="534" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B534" s="15"/>
+      <c r="B534" s="9"/>
     </row>
     <row r="535" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B535" s="15"/>
+      <c r="B535" s="9"/>
     </row>
     <row r="536" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B536" s="15"/>
+      <c r="B536" s="9"/>
     </row>
     <row r="537" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B537" s="15"/>
+      <c r="B537" s="9"/>
     </row>
     <row r="538" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B538" s="15"/>
+      <c r="B538" s="9"/>
     </row>
     <row r="539" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B539" s="15"/>
+      <c r="B539" s="9"/>
     </row>
     <row r="540" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B540" s="15"/>
+      <c r="B540" s="9"/>
     </row>
     <row r="541" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B541" s="15"/>
+      <c r="B541" s="9"/>
     </row>
     <row r="542" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B542" s="15"/>
+      <c r="B542" s="9"/>
     </row>
     <row r="543" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B543" s="15"/>
+      <c r="B543" s="9"/>
     </row>
     <row r="544" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B544" s="15"/>
+      <c r="B544" s="9"/>
     </row>
     <row r="545" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B545" s="15"/>
+      <c r="B545" s="9"/>
     </row>
     <row r="546" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B546" s="15"/>
+      <c r="B546" s="9"/>
     </row>
     <row r="547" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B547" s="15"/>
+      <c r="B547" s="9"/>
     </row>
     <row r="548" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B548" s="15"/>
+      <c r="B548" s="9"/>
     </row>
     <row r="549" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B549" s="15"/>
+      <c r="B549" s="9"/>
     </row>
     <row r="550" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B550" s="15"/>
+      <c r="B550" s="9"/>
     </row>
     <row r="551" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B551" s="15"/>
+      <c r="B551" s="9"/>
     </row>
     <row r="552" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B552" s="15"/>
+      <c r="B552" s="9"/>
     </row>
     <row r="553" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B553" s="15"/>
+      <c r="B553" s="9"/>
     </row>
     <row r="554" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B554" s="15"/>
+      <c r="B554" s="9"/>
     </row>
     <row r="555" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B555" s="15"/>
+      <c r="B555" s="9"/>
     </row>
     <row r="556" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B556" s="15"/>
+      <c r="B556" s="9"/>
     </row>
     <row r="557" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B557" s="15"/>
+      <c r="B557" s="9"/>
     </row>
     <row r="558" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B558" s="15"/>
+      <c r="B558" s="9"/>
     </row>
     <row r="559" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B559" s="15"/>
+      <c r="B559" s="9"/>
     </row>
     <row r="560" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B560" s="15"/>
+      <c r="B560" s="9"/>
     </row>
     <row r="561" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B561" s="15"/>
+      <c r="B561" s="9"/>
     </row>
     <row r="562" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B562" s="15"/>
+      <c r="B562" s="9"/>
     </row>
     <row r="563" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B563" s="15"/>
+      <c r="B563" s="9"/>
     </row>
     <row r="564" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B564" s="15"/>
+      <c r="B564" s="9"/>
     </row>
     <row r="565" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B565" s="15"/>
+      <c r="B565" s="9"/>
     </row>
     <row r="566" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B566" s="15"/>
+      <c r="B566" s="9"/>
     </row>
     <row r="567" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B567" s="15"/>
+      <c r="B567" s="9"/>
     </row>
     <row r="568" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B568" s="15"/>
+      <c r="B568" s="9"/>
     </row>
     <row r="569" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B569" s="15"/>
+      <c r="B569" s="9"/>
     </row>
     <row r="570" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B570" s="15"/>
+      <c r="B570" s="9"/>
     </row>
     <row r="571" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B571" s="15"/>
+      <c r="B571" s="9"/>
     </row>
     <row r="572" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B572" s="15"/>
+      <c r="B572" s="9"/>
     </row>
     <row r="573" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B573" s="15"/>
+      <c r="B573" s="9"/>
     </row>
     <row r="574" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B574" s="15"/>
+      <c r="B574" s="9"/>
     </row>
     <row r="575" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B575" s="15"/>
+      <c r="B575" s="9"/>
     </row>
     <row r="576" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B576" s="15"/>
+      <c r="B576" s="9"/>
     </row>
     <row r="577" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B577" s="15"/>
+      <c r="B577" s="9"/>
     </row>
     <row r="578" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B578" s="15"/>
+      <c r="B578" s="9"/>
     </row>
     <row r="579" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B579" s="15"/>
+      <c r="B579" s="9"/>
     </row>
     <row r="580" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B580" s="15"/>
+      <c r="B580" s="9"/>
     </row>
     <row r="581" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B581" s="15"/>
+      <c r="B581" s="9"/>
     </row>
     <row r="582" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B582" s="15"/>
+      <c r="B582" s="9"/>
     </row>
     <row r="583" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B583" s="15"/>
+      <c r="B583" s="9"/>
     </row>
     <row r="584" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B584" s="15"/>
+      <c r="B584" s="9"/>
     </row>
     <row r="585" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B585" s="15"/>
+      <c r="B585" s="9"/>
     </row>
     <row r="586" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B586" s="15"/>
+      <c r="B586" s="9"/>
     </row>
     <row r="587" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B587" s="15"/>
+      <c r="B587" s="9"/>
     </row>
     <row r="588" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B588" s="15"/>
+      <c r="B588" s="9"/>
     </row>
     <row r="589" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B589" s="15"/>
+      <c r="B589" s="9"/>
     </row>
     <row r="590" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B590" s="15"/>
+      <c r="B590" s="9"/>
     </row>
     <row r="591" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B591" s="15"/>
+      <c r="B591" s="9"/>
     </row>
     <row r="592" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B592" s="15"/>
+      <c r="B592" s="9"/>
     </row>
     <row r="593" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B593" s="15"/>
+      <c r="B593" s="9"/>
     </row>
     <row r="594" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B594" s="15"/>
+      <c r="B594" s="9"/>
     </row>
     <row r="595" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B595" s="15"/>
+      <c r="B595" s="9"/>
     </row>
     <row r="596" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B596" s="15"/>
+      <c r="B596" s="9"/>
     </row>
     <row r="597" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B597" s="15"/>
+      <c r="B597" s="9"/>
     </row>
     <row r="598" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B598" s="15"/>
+      <c r="B598" s="9"/>
     </row>
     <row r="599" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B599" s="15"/>
+      <c r="B599" s="9"/>
     </row>
     <row r="600" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B600" s="15"/>
+      <c r="B600" s="9"/>
     </row>
     <row r="601" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B601" s="15"/>
+      <c r="B601" s="9"/>
     </row>
     <row r="602" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B602" s="15"/>
+      <c r="B602" s="9"/>
     </row>
     <row r="603" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B603" s="15"/>
+      <c r="B603" s="9"/>
     </row>
     <row r="604" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B604" s="15"/>
+      <c r="B604" s="9"/>
     </row>
     <row r="605" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B605" s="15"/>
+      <c r="B605" s="9"/>
     </row>
     <row r="606" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B606" s="15"/>
+      <c r="B606" s="9"/>
     </row>
     <row r="607" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B607" s="15"/>
+      <c r="B607" s="9"/>
     </row>
     <row r="608" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B608" s="15"/>
+      <c r="B608" s="9"/>
     </row>
     <row r="609" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B609" s="15"/>
+      <c r="B609" s="9"/>
     </row>
     <row r="610" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B610" s="15"/>
+      <c r="B610" s="9"/>
     </row>
     <row r="611" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B611" s="15"/>
+      <c r="B611" s="9"/>
     </row>
     <row r="612" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B612" s="15"/>
+      <c r="B612" s="9"/>
     </row>
     <row r="613" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B613" s="15"/>
+      <c r="B613" s="9"/>
     </row>
     <row r="614" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B614" s="15"/>
+      <c r="B614" s="9"/>
     </row>
     <row r="615" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B615" s="15"/>
+      <c r="B615" s="9"/>
     </row>
     <row r="616" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B616" s="15"/>
+      <c r="B616" s="9"/>
     </row>
     <row r="617" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B617" s="15"/>
+      <c r="B617" s="9"/>
     </row>
     <row r="618" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B618" s="15"/>
+      <c r="B618" s="9"/>
     </row>
     <row r="619" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B619" s="15"/>
+      <c r="B619" s="9"/>
     </row>
     <row r="620" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B620" s="15"/>
+      <c r="B620" s="9"/>
     </row>
     <row r="621" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B621" s="15"/>
+      <c r="B621" s="9"/>
     </row>
     <row r="622" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B622" s="15"/>
+      <c r="B622" s="9"/>
     </row>
     <row r="623" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B623" s="15"/>
+      <c r="B623" s="9"/>
     </row>
     <row r="624" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B624" s="15"/>
+      <c r="B624" s="9"/>
     </row>
     <row r="625" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B625" s="15"/>
+      <c r="B625" s="9"/>
     </row>
     <row r="626" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B626" s="15"/>
+      <c r="B626" s="9"/>
     </row>
     <row r="627" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B627" s="15"/>
+      <c r="B627" s="9"/>
     </row>
     <row r="628" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B628" s="15"/>
+      <c r="B628" s="9"/>
     </row>
     <row r="629" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B629" s="15"/>
+      <c r="B629" s="9"/>
     </row>
     <row r="630" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B630" s="15"/>
+      <c r="B630" s="9"/>
     </row>
     <row r="631" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B631" s="15"/>
+      <c r="B631" s="9"/>
     </row>
     <row r="632" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B632" s="15"/>
+      <c r="B632" s="9"/>
     </row>
     <row r="633" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B633" s="15"/>
+      <c r="B633" s="9"/>
     </row>
     <row r="634" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B634" s="15"/>
+      <c r="B634" s="9"/>
     </row>
     <row r="635" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B635" s="15"/>
+      <c r="B635" s="9"/>
     </row>
     <row r="636" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B636" s="15"/>
+      <c r="B636" s="9"/>
     </row>
     <row r="637" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B637" s="15"/>
+      <c r="B637" s="9"/>
     </row>
     <row r="638" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B638" s="15"/>
+      <c r="B638" s="9"/>
     </row>
     <row r="639" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B639" s="15"/>
+      <c r="B639" s="9"/>
     </row>
     <row r="640" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B640" s="15"/>
+      <c r="B640" s="9"/>
     </row>
     <row r="641" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B641" s="15"/>
+      <c r="B641" s="9"/>
     </row>
     <row r="642" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B642" s="15"/>
+      <c r="B642" s="9"/>
     </row>
     <row r="643" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B643" s="15"/>
+      <c r="B643" s="9"/>
     </row>
     <row r="644" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B644" s="15"/>
+      <c r="B644" s="9"/>
     </row>
     <row r="645" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B645" s="15"/>
+      <c r="B645" s="9"/>
     </row>
     <row r="646" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B646" s="15"/>
+      <c r="B646" s="9"/>
     </row>
     <row r="647" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B647" s="15"/>
+      <c r="B647" s="9"/>
     </row>
     <row r="648" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B648" s="15"/>
+      <c r="B648" s="9"/>
     </row>
     <row r="649" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B649" s="15"/>
+      <c r="B649" s="9"/>
     </row>
     <row r="650" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B650" s="15"/>
+      <c r="B650" s="9"/>
     </row>
     <row r="651" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B651" s="15"/>
+      <c r="B651" s="9"/>
     </row>
     <row r="652" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B652" s="15"/>
+      <c r="B652" s="9"/>
     </row>
     <row r="653" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B653" s="15"/>
+      <c r="B653" s="9"/>
     </row>
     <row r="654" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B654" s="15"/>
+      <c r="B654" s="9"/>
     </row>
     <row r="655" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B655" s="15"/>
+      <c r="B655" s="9"/>
     </row>
     <row r="656" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B656" s="15"/>
+      <c r="B656" s="9"/>
     </row>
     <row r="657" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B657" s="15"/>
+      <c r="B657" s="9"/>
     </row>
     <row r="658" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B658" s="15"/>
+      <c r="B658" s="9"/>
     </row>
     <row r="659" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B659" s="15"/>
+      <c r="B659" s="9"/>
     </row>
     <row r="660" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B660" s="15"/>
+      <c r="B660" s="9"/>
     </row>
     <row r="661" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B661" s="15"/>
+      <c r="B661" s="9"/>
     </row>
     <row r="662" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B662" s="15"/>
+      <c r="B662" s="9"/>
     </row>
     <row r="663" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B663" s="15"/>
+      <c r="B663" s="9"/>
     </row>
     <row r="664" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B664" s="15"/>
+      <c r="B664" s="9"/>
     </row>
     <row r="665" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B665" s="15"/>
+      <c r="B665" s="9"/>
     </row>
     <row r="666" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B666" s="15"/>
+      <c r="B666" s="9"/>
     </row>
     <row r="667" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B667" s="15"/>
+      <c r="B667" s="9"/>
     </row>
     <row r="668" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B668" s="15"/>
+      <c r="B668" s="9"/>
     </row>
     <row r="669" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B669" s="15"/>
+      <c r="B669" s="9"/>
     </row>
     <row r="670" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B670" s="15"/>
+      <c r="B670" s="9"/>
     </row>
     <row r="671" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B671" s="15"/>
+      <c r="B671" s="9"/>
     </row>
     <row r="672" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B672" s="15"/>
+      <c r="B672" s="9"/>
     </row>
     <row r="673" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B673" s="15"/>
+      <c r="B673" s="9"/>
     </row>
     <row r="674" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B674" s="15"/>
+      <c r="B674" s="9"/>
     </row>
     <row r="675" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B675" s="15"/>
+      <c r="B675" s="9"/>
     </row>
     <row r="676" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B676" s="15"/>
+      <c r="B676" s="9"/>
     </row>
     <row r="677" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B677" s="15"/>
+      <c r="B677" s="9"/>
     </row>
     <row r="678" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B678" s="15"/>
+      <c r="B678" s="9"/>
     </row>
     <row r="679" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B679" s="15"/>
+      <c r="B679" s="9"/>
     </row>
     <row r="680" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B680" s="15"/>
+      <c r="B680" s="9"/>
     </row>
     <row r="681" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B681" s="15"/>
+      <c r="B681" s="9"/>
     </row>
     <row r="682" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B682" s="15"/>
+      <c r="B682" s="9"/>
     </row>
     <row r="683" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B683" s="15"/>
+      <c r="B683" s="9"/>
     </row>
     <row r="684" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B684" s="15"/>
+      <c r="B684" s="9"/>
     </row>
     <row r="685" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B685" s="15"/>
+      <c r="B685" s="9"/>
     </row>
     <row r="686" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B686" s="15"/>
+      <c r="B686" s="9"/>
     </row>
     <row r="687" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B687" s="15"/>
+      <c r="B687" s="9"/>
     </row>
     <row r="688" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B688" s="15"/>
+      <c r="B688" s="9"/>
     </row>
     <row r="689" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B689" s="15"/>
+      <c r="B689" s="9"/>
     </row>
     <row r="690" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B690" s="15"/>
+      <c r="B690" s="9"/>
     </row>
     <row r="691" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B691" s="15"/>
+      <c r="B691" s="9"/>
     </row>
     <row r="692" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B692" s="15"/>
+      <c r="B692" s="9"/>
     </row>
     <row r="693" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B693" s="15"/>
+      <c r="B693" s="9"/>
     </row>
     <row r="694" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B694" s="15"/>
+      <c r="B694" s="9"/>
     </row>
     <row r="695" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B695" s="15"/>
+      <c r="B695" s="9"/>
     </row>
     <row r="696" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B696" s="15"/>
+      <c r="B696" s="9"/>
     </row>
     <row r="697" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B697" s="15"/>
+      <c r="B697" s="9"/>
     </row>
     <row r="698" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B698" s="15"/>
+      <c r="B698" s="9"/>
     </row>
     <row r="699" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B699" s="15"/>
+      <c r="B699" s="9"/>
     </row>
     <row r="700" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B700" s="15"/>
+      <c r="B700" s="9"/>
     </row>
     <row r="701" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B701" s="15"/>
+      <c r="B701" s="9"/>
     </row>
     <row r="702" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B702" s="15"/>
+      <c r="B702" s="9"/>
     </row>
     <row r="703" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B703" s="15"/>
+      <c r="B703" s="9"/>
     </row>
     <row r="704" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B704" s="15"/>
+      <c r="B704" s="9"/>
     </row>
     <row r="705" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B705" s="15"/>
+      <c r="B705" s="9"/>
     </row>
     <row r="706" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B706" s="15"/>
+      <c r="B706" s="9"/>
     </row>
     <row r="707" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B707" s="15"/>
+      <c r="B707" s="9"/>
     </row>
     <row r="708" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B708" s="15"/>
+      <c r="B708" s="9"/>
     </row>
     <row r="709" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B709" s="15"/>
+      <c r="B709" s="9"/>
     </row>
     <row r="710" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B710" s="15"/>
+      <c r="B710" s="9"/>
     </row>
     <row r="711" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B711" s="15"/>
+      <c r="B711" s="9"/>
     </row>
     <row r="712" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B712" s="15"/>
+      <c r="B712" s="9"/>
     </row>
     <row r="713" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B713" s="15"/>
+      <c r="B713" s="9"/>
     </row>
     <row r="714" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B714" s="15"/>
+      <c r="B714" s="9"/>
     </row>
     <row r="715" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B715" s="15"/>
+      <c r="B715" s="9"/>
     </row>
     <row r="716" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B716" s="15"/>
+      <c r="B716" s="9"/>
     </row>
     <row r="717" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B717" s="15"/>
+      <c r="B717" s="9"/>
     </row>
     <row r="718" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B718" s="15"/>
+      <c r="B718" s="9"/>
     </row>
     <row r="719" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B719" s="15"/>
+      <c r="B719" s="9"/>
     </row>
     <row r="720" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B720" s="15"/>
+      <c r="B720" s="9"/>
     </row>
     <row r="721" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B721" s="15"/>
+      <c r="B721" s="9"/>
     </row>
     <row r="722" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B722" s="15"/>
+      <c r="B722" s="9"/>
     </row>
     <row r="723" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B723" s="15"/>
+      <c r="B723" s="9"/>
     </row>
     <row r="724" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B724" s="15"/>
+      <c r="B724" s="9"/>
     </row>
     <row r="725" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B725" s="15"/>
+      <c r="B725" s="9"/>
     </row>
     <row r="726" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B726" s="15"/>
+      <c r="B726" s="9"/>
     </row>
     <row r="727" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B727" s="15"/>
+      <c r="B727" s="9"/>
     </row>
     <row r="728" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B728" s="15"/>
+      <c r="B728" s="9"/>
     </row>
     <row r="729" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B729" s="15"/>
+      <c r="B729" s="9"/>
     </row>
     <row r="730" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B730" s="15"/>
+      <c r="B730" s="9"/>
     </row>
     <row r="731" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B731" s="15"/>
+      <c r="B731" s="9"/>
     </row>
     <row r="732" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B732" s="15"/>
+      <c r="B732" s="9"/>
     </row>
     <row r="733" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B733" s="15"/>
+      <c r="B733" s="9"/>
     </row>
     <row r="734" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B734" s="15"/>
+      <c r="B734" s="9"/>
     </row>
     <row r="735" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B735" s="15"/>
+      <c r="B735" s="9"/>
     </row>
     <row r="736" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B736" s="15"/>
+      <c r="B736" s="9"/>
     </row>
     <row r="737" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B737" s="15"/>
+      <c r="B737" s="9"/>
     </row>
     <row r="738" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B738" s="15"/>
+      <c r="B738" s="9"/>
     </row>
     <row r="739" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B739" s="15"/>
+      <c r="B739" s="9"/>
     </row>
     <row r="740" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B740" s="15"/>
+      <c r="B740" s="9"/>
     </row>
     <row r="741" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B741" s="15"/>
+      <c r="B741" s="9"/>
     </row>
     <row r="742" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B742" s="15"/>
+      <c r="B742" s="9"/>
     </row>
     <row r="743" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B743" s="15"/>
+      <c r="B743" s="9"/>
     </row>
     <row r="744" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B744" s="15"/>
+      <c r="B744" s="9"/>
     </row>
     <row r="745" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B745" s="15"/>
+      <c r="B745" s="9"/>
     </row>
     <row r="746" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B746" s="15"/>
+      <c r="B746" s="9"/>
     </row>
     <row r="747" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B747" s="15"/>
+      <c r="B747" s="9"/>
     </row>
     <row r="748" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B748" s="15"/>
+      <c r="B748" s="9"/>
     </row>
     <row r="749" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B749" s="15"/>
+      <c r="B749" s="9"/>
     </row>
     <row r="750" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B750" s="15"/>
+      <c r="B750" s="9"/>
     </row>
     <row r="751" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B751" s="15"/>
+      <c r="B751" s="9"/>
     </row>
     <row r="752" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B752" s="15"/>
+      <c r="B752" s="9"/>
     </row>
     <row r="753" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B753" s="15"/>
+      <c r="B753" s="9"/>
     </row>
     <row r="754" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B754" s="15"/>
+      <c r="B754" s="9"/>
     </row>
     <row r="755" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B755" s="15"/>
+      <c r="B755" s="9"/>
     </row>
     <row r="756" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B756" s="15"/>
+      <c r="B756" s="9"/>
     </row>
     <row r="757" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B757" s="15"/>
+      <c r="B757" s="9"/>
     </row>
     <row r="758" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B758" s="15"/>
+      <c r="B758" s="9"/>
     </row>
     <row r="759" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B759" s="15"/>
+      <c r="B759" s="9"/>
     </row>
     <row r="760" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B760" s="15"/>
+      <c r="B760" s="9"/>
     </row>
     <row r="761" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B761" s="15"/>
+      <c r="B761" s="9"/>
     </row>
     <row r="762" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B762" s="15"/>
+      <c r="B762" s="9"/>
     </row>
     <row r="763" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B763" s="15"/>
+      <c r="B763" s="9"/>
     </row>
     <row r="764" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B764" s="15"/>
+      <c r="B764" s="9"/>
     </row>
     <row r="765" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B765" s="15"/>
+      <c r="B765" s="9"/>
     </row>
     <row r="766" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B766" s="15"/>
+      <c r="B766" s="9"/>
     </row>
     <row r="767" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B767" s="15"/>
+      <c r="B767" s="9"/>
     </row>
     <row r="768" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B768" s="15"/>
+      <c r="B768" s="9"/>
     </row>
     <row r="769" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B769" s="15"/>
+      <c r="B769" s="9"/>
     </row>
     <row r="770" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B770" s="15"/>
+      <c r="B770" s="9"/>
     </row>
     <row r="771" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B771" s="15"/>
+      <c r="B771" s="9"/>
     </row>
     <row r="772" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B772" s="15"/>
+      <c r="B772" s="9"/>
     </row>
     <row r="773" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B773" s="15"/>
+      <c r="B773" s="9"/>
     </row>
     <row r="774" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B774" s="15"/>
+      <c r="B774" s="9"/>
     </row>
     <row r="775" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B775" s="15"/>
+      <c r="B775" s="9"/>
     </row>
     <row r="776" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B776" s="15"/>
+      <c r="B776" s="9"/>
     </row>
     <row r="777" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B777" s="15"/>
+      <c r="B777" s="9"/>
     </row>
     <row r="778" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B778" s="15"/>
+      <c r="B778" s="9"/>
     </row>
     <row r="779" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B779" s="15"/>
+      <c r="B779" s="9"/>
     </row>
     <row r="780" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B780" s="15"/>
+      <c r="B780" s="9"/>
     </row>
     <row r="781" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B781" s="15"/>
+      <c r="B781" s="9"/>
     </row>
     <row r="782" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B782" s="15"/>
+      <c r="B782" s="9"/>
     </row>
     <row r="783" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B783" s="15"/>
+      <c r="B783" s="9"/>
     </row>
     <row r="784" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B784" s="15"/>
+      <c r="B784" s="9"/>
     </row>
     <row r="785" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B785" s="15"/>
+      <c r="B785" s="9"/>
     </row>
     <row r="786" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B786" s="15"/>
+      <c r="B786" s="9"/>
     </row>
     <row r="787" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B787" s="15"/>
+      <c r="B787" s="9"/>
     </row>
     <row r="788" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B788" s="15"/>
+      <c r="B788" s="9"/>
     </row>
     <row r="789" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B789" s="15"/>
+      <c r="B789" s="9"/>
     </row>
     <row r="790" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B790" s="15"/>
+      <c r="B790" s="9"/>
     </row>
     <row r="791" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B791" s="15"/>
+      <c r="B791" s="9"/>
     </row>
     <row r="792" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B792" s="15"/>
+      <c r="B792" s="9"/>
     </row>
     <row r="793" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B793" s="15"/>
+      <c r="B793" s="9"/>
     </row>
     <row r="794" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B794" s="15"/>
+      <c r="B794" s="9"/>
     </row>
     <row r="795" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B795" s="15"/>
+      <c r="B795" s="9"/>
     </row>
     <row r="796" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B796" s="15"/>
+      <c r="B796" s="9"/>
     </row>
     <row r="797" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B797" s="15"/>
+      <c r="B797" s="9"/>
     </row>
     <row r="798" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B798" s="15"/>
+      <c r="B798" s="9"/>
     </row>
     <row r="799" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B799" s="15"/>
+      <c r="B799" s="9"/>
     </row>
     <row r="800" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B800" s="15"/>
+      <c r="B800" s="9"/>
     </row>
     <row r="801" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B801" s="15"/>
+      <c r="B801" s="9"/>
     </row>
     <row r="802" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B802" s="15"/>
+      <c r="B802" s="9"/>
     </row>
     <row r="803" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B803" s="15"/>
+      <c r="B803" s="9"/>
     </row>
     <row r="804" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B804" s="15"/>
+      <c r="B804" s="9"/>
     </row>
     <row r="805" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B805" s="15"/>
+      <c r="B805" s="9"/>
     </row>
     <row r="806" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B806" s="15"/>
+      <c r="B806" s="9"/>
     </row>
     <row r="807" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B807" s="15"/>
+      <c r="B807" s="9"/>
     </row>
     <row r="808" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B808" s="15"/>
+      <c r="B808" s="9"/>
     </row>
     <row r="809" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B809" s="15"/>
+      <c r="B809" s="9"/>
     </row>
     <row r="810" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B810" s="15"/>
+      <c r="B810" s="9"/>
     </row>
     <row r="811" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B811" s="15"/>
+      <c r="B811" s="9"/>
     </row>
     <row r="812" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B812" s="15"/>
+      <c r="B812" s="9"/>
     </row>
     <row r="813" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B813" s="15"/>
+      <c r="B813" s="9"/>
     </row>
     <row r="814" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B814" s="15"/>
+      <c r="B814" s="9"/>
     </row>
     <row r="815" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B815" s="15"/>
+      <c r="B815" s="9"/>
     </row>
     <row r="816" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B816" s="15"/>
+      <c r="B816" s="9"/>
     </row>
     <row r="817" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B817" s="15"/>
+      <c r="B817" s="9"/>
     </row>
     <row r="818" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B818" s="15"/>
+      <c r="B818" s="9"/>
     </row>
     <row r="819" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B819" s="15"/>
+      <c r="B819" s="9"/>
     </row>
     <row r="820" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B820" s="15"/>
+      <c r="B820" s="9"/>
     </row>
     <row r="821" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B821" s="15"/>
+      <c r="B821" s="9"/>
     </row>
     <row r="822" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B822" s="15"/>
+      <c r="B822" s="9"/>
     </row>
     <row r="823" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B823" s="15"/>
+      <c r="B823" s="9"/>
     </row>
     <row r="824" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B824" s="15"/>
+      <c r="B824" s="9"/>
     </row>
     <row r="825" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B825" s="15"/>
+      <c r="B825" s="9"/>
     </row>
     <row r="826" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B826" s="15"/>
+      <c r="B826" s="9"/>
     </row>
     <row r="827" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B827" s="15"/>
+      <c r="B827" s="9"/>
     </row>
     <row r="828" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B828" s="15"/>
+      <c r="B828" s="9"/>
     </row>
     <row r="829" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B829" s="15"/>
+      <c r="B829" s="9"/>
     </row>
     <row r="830" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B830" s="15"/>
+      <c r="B830" s="9"/>
     </row>
     <row r="831" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B831" s="15"/>
+      <c r="B831" s="9"/>
     </row>
     <row r="832" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B832" s="15"/>
+      <c r="B832" s="9"/>
     </row>
     <row r="833" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B833" s="15"/>
+      <c r="B833" s="9"/>
     </row>
     <row r="834" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B834" s="15"/>
+      <c r="B834" s="9"/>
     </row>
     <row r="835" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B835" s="15"/>
+      <c r="B835" s="9"/>
     </row>
     <row r="836" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B836" s="15"/>
+      <c r="B836" s="9"/>
     </row>
     <row r="837" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B837" s="15"/>
+      <c r="B837" s="9"/>
     </row>
     <row r="838" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B838" s="15"/>
+      <c r="B838" s="9"/>
     </row>
     <row r="839" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B839" s="15"/>
+      <c r="B839" s="9"/>
     </row>
     <row r="840" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B840" s="15"/>
+      <c r="B840" s="9"/>
     </row>
     <row r="841" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B841" s="15"/>
+      <c r="B841" s="9"/>
     </row>
     <row r="842" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B842" s="15"/>
+      <c r="B842" s="9"/>
     </row>
     <row r="843" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B843" s="15"/>
+      <c r="B843" s="9"/>
     </row>
     <row r="844" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B844" s="15"/>
+      <c r="B844" s="9"/>
     </row>
     <row r="845" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B845" s="15"/>
+      <c r="B845" s="9"/>
     </row>
     <row r="846" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B846" s="15"/>
+      <c r="B846" s="9"/>
     </row>
     <row r="847" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B847" s="15"/>
+      <c r="B847" s="9"/>
     </row>
     <row r="848" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B848" s="15"/>
+      <c r="B848" s="9"/>
     </row>
     <row r="849" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B849" s="15"/>
+      <c r="B849" s="9"/>
     </row>
     <row r="850" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B850" s="15"/>
+      <c r="B850" s="9"/>
     </row>
     <row r="851" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B851" s="15"/>
+      <c r="B851" s="9"/>
     </row>
     <row r="852" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B852" s="15"/>
+      <c r="B852" s="9"/>
     </row>
     <row r="853" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B853" s="15"/>
+      <c r="B853" s="9"/>
     </row>
     <row r="854" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B854" s="15"/>
+      <c r="B854" s="9"/>
     </row>
     <row r="855" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B855" s="15"/>
+      <c r="B855" s="9"/>
     </row>
     <row r="856" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B856" s="15"/>
+      <c r="B856" s="9"/>
     </row>
     <row r="857" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B857" s="15"/>
+      <c r="B857" s="9"/>
     </row>
     <row r="858" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B858" s="15"/>
+      <c r="B858" s="9"/>
     </row>
     <row r="859" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B859" s="15"/>
+      <c r="B859" s="9"/>
     </row>
     <row r="860" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B860" s="15"/>
+      <c r="B860" s="9"/>
     </row>
     <row r="861" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B861" s="15"/>
+      <c r="B861" s="9"/>
     </row>
     <row r="862" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B862" s="15"/>
+      <c r="B862" s="9"/>
     </row>
     <row r="863" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B863" s="15"/>
+      <c r="B863" s="9"/>
     </row>
     <row r="864" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B864" s="15"/>
+      <c r="B864" s="9"/>
     </row>
     <row r="865" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B865" s="15"/>
+      <c r="B865" s="9"/>
     </row>
     <row r="866" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B866" s="15"/>
+      <c r="B866" s="9"/>
     </row>
     <row r="867" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B867" s="15"/>
+      <c r="B867" s="9"/>
     </row>
     <row r="868" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B868" s="15"/>
+      <c r="B868" s="9"/>
     </row>
     <row r="869" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B869" s="15"/>
+      <c r="B869" s="9"/>
     </row>
     <row r="870" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B870" s="15"/>
+      <c r="B870" s="9"/>
     </row>
     <row r="871" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B871" s="15"/>
+      <c r="B871" s="9"/>
     </row>
     <row r="872" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B872" s="15"/>
+      <c r="B872" s="9"/>
     </row>
     <row r="873" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B873" s="15"/>
+      <c r="B873" s="9"/>
     </row>
     <row r="874" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B874" s="15"/>
+      <c r="B874" s="9"/>
     </row>
     <row r="875" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B875" s="15"/>
+      <c r="B875" s="9"/>
     </row>
     <row r="876" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B876" s="15"/>
+      <c r="B876" s="9"/>
     </row>
     <row r="877" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B877" s="15"/>
+      <c r="B877" s="9"/>
     </row>
     <row r="878" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B878" s="15"/>
+      <c r="B878" s="9"/>
     </row>
     <row r="879" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B879" s="15"/>
+      <c r="B879" s="9"/>
     </row>
     <row r="880" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B880" s="15"/>
+      <c r="B880" s="9"/>
     </row>
     <row r="881" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B881" s="15"/>
+      <c r="B881" s="9"/>
     </row>
     <row r="882" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B882" s="15"/>
+      <c r="B882" s="9"/>
     </row>
     <row r="883" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B883" s="15"/>
+      <c r="B883" s="9"/>
     </row>
     <row r="884" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B884" s="15"/>
+      <c r="B884" s="9"/>
     </row>
     <row r="885" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B885" s="15"/>
+      <c r="B885" s="9"/>
     </row>
     <row r="886" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B886" s="15"/>
+      <c r="B886" s="9"/>
     </row>
     <row r="887" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B887" s="15"/>
+      <c r="B887" s="9"/>
     </row>
     <row r="888" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B888" s="15"/>
+      <c r="B888" s="9"/>
     </row>
     <row r="889" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B889" s="15"/>
+      <c r="B889" s="9"/>
     </row>
     <row r="890" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B890" s="15"/>
+      <c r="B890" s="9"/>
     </row>
     <row r="891" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B891" s="15"/>
+      <c r="B891" s="9"/>
     </row>
     <row r="892" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B892" s="15"/>
+      <c r="B892" s="9"/>
     </row>
     <row r="893" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B893" s="15"/>
+      <c r="B893" s="9"/>
     </row>
     <row r="894" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B894" s="15"/>
+      <c r="B894" s="9"/>
     </row>
     <row r="895" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B895" s="15"/>
+      <c r="B895" s="9"/>
     </row>
     <row r="896" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B896" s="15"/>
+      <c r="B896" s="9"/>
     </row>
     <row r="897" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B897" s="15"/>
+      <c r="B897" s="9"/>
     </row>
     <row r="898" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B898" s="15"/>
+      <c r="B898" s="9"/>
     </row>
     <row r="899" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B899" s="15"/>
+      <c r="B899" s="9"/>
     </row>
     <row r="900" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B900" s="15"/>
+      <c r="B900" s="9"/>
     </row>
     <row r="901" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B901" s="15"/>
+      <c r="B901" s="9"/>
     </row>
     <row r="902" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B902" s="15"/>
+      <c r="B902" s="9"/>
     </row>
     <row r="903" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B903" s="15"/>
+      <c r="B903" s="9"/>
     </row>
     <row r="904" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B904" s="15"/>
+      <c r="B904" s="9"/>
     </row>
     <row r="905" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B905" s="15"/>
+      <c r="B905" s="9"/>
     </row>
     <row r="906" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B906" s="15"/>
+      <c r="B906" s="9"/>
     </row>
     <row r="907" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B907" s="15"/>
+      <c r="B907" s="9"/>
     </row>
     <row r="908" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B908" s="15"/>
+      <c r="B908" s="9"/>
     </row>
     <row r="909" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B909" s="15"/>
+      <c r="B909" s="9"/>
     </row>
     <row r="910" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B910" s="15"/>
+      <c r="B910" s="9"/>
     </row>
     <row r="911" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B911" s="15"/>
+      <c r="B911" s="9"/>
     </row>
     <row r="912" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B912" s="15"/>
+      <c r="B912" s="9"/>
     </row>
     <row r="913" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B913" s="15"/>
+      <c r="B913" s="9"/>
     </row>
     <row r="914" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B914" s="15"/>
+      <c r="B914" s="9"/>
     </row>
     <row r="915" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B915" s="15"/>
+      <c r="B915" s="9"/>
     </row>
     <row r="916" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B916" s="15"/>
+      <c r="B916" s="9"/>
     </row>
     <row r="917" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B917" s="15"/>
+      <c r="B917" s="9"/>
     </row>
     <row r="918" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B918" s="15"/>
+      <c r="B918" s="9"/>
     </row>
     <row r="919" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B919" s="15"/>
+      <c r="B919" s="9"/>
     </row>
     <row r="920" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B920" s="15"/>
+      <c r="B920" s="9"/>
     </row>
     <row r="921" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B921" s="15"/>
+      <c r="B921" s="9"/>
     </row>
     <row r="922" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B922" s="15"/>
+      <c r="B922" s="9"/>
     </row>
     <row r="923" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B923" s="15"/>
+      <c r="B923" s="9"/>
     </row>
     <row r="924" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B924" s="15"/>
+      <c r="B924" s="9"/>
     </row>
     <row r="925" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B925" s="15"/>
+      <c r="B925" s="9"/>
     </row>
     <row r="926" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B926" s="15"/>
+      <c r="B926" s="9"/>
     </row>
     <row r="927" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B927" s="15"/>
+      <c r="B927" s="9"/>
     </row>
     <row r="928" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B928" s="15"/>
+      <c r="B928" s="9"/>
     </row>
     <row r="929" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B929" s="15"/>
+      <c r="B929" s="9"/>
     </row>
     <row r="930" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B930" s="15"/>
+      <c r="B930" s="9"/>
     </row>
     <row r="931" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B931" s="15"/>
+      <c r="B931" s="9"/>
     </row>
     <row r="932" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B932" s="15"/>
+      <c r="B932" s="9"/>
     </row>
     <row r="933" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B933" s="15"/>
+      <c r="B933" s="9"/>
     </row>
     <row r="934" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B934" s="15"/>
+      <c r="B934" s="9"/>
     </row>
     <row r="935" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B935" s="15"/>
+      <c r="B935" s="9"/>
     </row>
     <row r="936" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B936" s="15"/>
+      <c r="B936" s="9"/>
     </row>
     <row r="937" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B937" s="15"/>
+      <c r="B937" s="9"/>
     </row>
     <row r="938" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B938" s="15"/>
+      <c r="B938" s="9"/>
     </row>
     <row r="939" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B939" s="15"/>
+      <c r="B939" s="9"/>
     </row>
     <row r="940" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B940" s="15"/>
+      <c r="B940" s="9"/>
     </row>
     <row r="941" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B941" s="15"/>
+      <c r="B941" s="9"/>
     </row>
     <row r="942" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B942" s="15"/>
+      <c r="B942" s="9"/>
     </row>
     <row r="943" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B943" s="15"/>
+      <c r="B943" s="9"/>
     </row>
     <row r="944" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B944" s="15"/>
+      <c r="B944" s="9"/>
     </row>
     <row r="945" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B945" s="15"/>
+      <c r="B945" s="9"/>
     </row>
     <row r="946" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B946" s="15"/>
+      <c r="B946" s="9"/>
     </row>
     <row r="947" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B947" s="15"/>
+      <c r="B947" s="9"/>
     </row>
     <row r="948" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B948" s="15"/>
+      <c r="B948" s="9"/>
     </row>
     <row r="949" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B949" s="15"/>
+      <c r="B949" s="9"/>
     </row>
     <row r="950" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B950" s="15"/>
+      <c r="B950" s="9"/>
     </row>
     <row r="951" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B951" s="15"/>
+      <c r="B951" s="9"/>
     </row>
     <row r="952" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B952" s="15"/>
+      <c r="B952" s="9"/>
     </row>
     <row r="953" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B953" s="15"/>
+      <c r="B953" s="9"/>
     </row>
     <row r="954" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B954" s="15"/>
+      <c r="B954" s="9"/>
     </row>
     <row r="955" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B955" s="15"/>
+      <c r="B955" s="9"/>
     </row>
     <row r="956" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B956" s="15"/>
+      <c r="B956" s="9"/>
     </row>
     <row r="957" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B957" s="15"/>
+      <c r="B957" s="9"/>
     </row>
     <row r="958" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B958" s="15"/>
+      <c r="B958" s="9"/>
     </row>
     <row r="959" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B959" s="15"/>
+      <c r="B959" s="9"/>
     </row>
     <row r="960" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B960" s="15"/>
+      <c r="B960" s="9"/>
     </row>
     <row r="961" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B961" s="15"/>
+      <c r="B961" s="9"/>
     </row>
     <row r="962" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B962" s="15"/>
+      <c r="B962" s="9"/>
     </row>
     <row r="963" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B963" s="15"/>
+      <c r="B963" s="9"/>
     </row>
     <row r="964" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B964" s="15"/>
+      <c r="B964" s="9"/>
     </row>
     <row r="965" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B965" s="15"/>
+      <c r="B965" s="9"/>
     </row>
     <row r="966" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B966" s="15"/>
+      <c r="B966" s="9"/>
     </row>
     <row r="967" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B967" s="15"/>
+      <c r="B967" s="9"/>
     </row>
     <row r="968" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B968" s="15"/>
+      <c r="B968" s="9"/>
     </row>
     <row r="969" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B969" s="15"/>
+      <c r="B969" s="9"/>
     </row>
     <row r="970" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B970" s="15"/>
+      <c r="B970" s="9"/>
     </row>
     <row r="971" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B971" s="15"/>
+      <c r="B971" s="9"/>
     </row>
     <row r="972" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B972" s="15"/>
+      <c r="B972" s="9"/>
     </row>
     <row r="973" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B973" s="15"/>
+      <c r="B973" s="9"/>
     </row>
     <row r="974" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B974" s="15"/>
+      <c r="B974" s="9"/>
     </row>
     <row r="975" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B975" s="15"/>
+      <c r="B975" s="9"/>
     </row>
     <row r="976" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B976" s="15"/>
+      <c r="B976" s="9"/>
     </row>
     <row r="977" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B977" s="15"/>
+      <c r="B977" s="9"/>
     </row>
     <row r="978" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B978" s="15"/>
+      <c r="B978" s="9"/>
     </row>
     <row r="979" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B979" s="15"/>
+      <c r="B979" s="9"/>
     </row>
     <row r="980" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B980" s="15"/>
+      <c r="B980" s="9"/>
     </row>
     <row r="981" spans="2:2" ht="13" x14ac:dyDescent="0.15">
-      <c r="B981" s="15"/>
+      <c r="B981" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{0cf7ac0a-4681-4823-ab0b-04ef02c5f873}" enabled="1" method="Standard" siteId="{42f7676c-f455-423c-82f6-dc2d99791af7}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>